--- a/research/traditional_assets/database/data/indonesia/indonesia_aerospace_defense.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_aerospace_defense.xlsx
@@ -587,23 +587,26 @@
           <t>Aerospace/Defense</t>
         </is>
       </c>
+      <c r="D2">
+        <v>-0.145</v>
+      </c>
       <c r="G2">
-        <v>-0.5782761653474054</v>
+        <v>-0.3852835973428718</v>
       </c>
       <c r="H2">
-        <v>-0.5782761653474054</v>
+        <v>-0.3852835973428718</v>
       </c>
       <c r="I2">
-        <v>-0.008135444151275286</v>
+        <v>-0.3765968318855391</v>
       </c>
       <c r="J2">
-        <v>-0.008135444151275286</v>
+        <v>-0.3765968318855391</v>
       </c>
       <c r="K2">
-        <v>-207.1</v>
+        <v>-106.3</v>
       </c>
       <c r="L2">
-        <v>-0.9107299912049251</v>
+        <v>-0.5431783341849771</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>7.41</v>
+        <v>6.05</v>
       </c>
       <c r="V2">
-        <v>0.05068399452804378</v>
+        <v>0.05071248952221291</v>
       </c>
       <c r="W2">
-        <v>-4.521834061135372</v>
+        <v>0.4240127642600718</v>
       </c>
       <c r="X2">
-        <v>0.212211879599852</v>
+        <v>0.4451709407365354</v>
       </c>
       <c r="Y2">
-        <v>-4.734045940735223</v>
+        <v>-0.02115817647646362</v>
       </c>
       <c r="Z2">
-        <v>0.5044365572315883</v>
+        <v>1.004671697725756</v>
       </c>
       <c r="AA2">
-        <v>-0.004103815439219166</v>
+        <v>-0.3783561784485857</v>
       </c>
       <c r="AB2">
-        <v>0.07348621248393181</v>
+        <v>0.1415367700074502</v>
       </c>
       <c r="AC2">
-        <v>-0.07759002792315098</v>
+        <v>-0.519892948456036</v>
       </c>
       <c r="AD2">
-        <v>452.9</v>
+        <v>444.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>452.9</v>
+        <v>444.3</v>
       </c>
       <c r="AG2">
-        <v>445.49</v>
+        <v>438.25</v>
       </c>
       <c r="AH2">
-        <v>0.755967284259723</v>
+        <v>0.7883250532292406</v>
       </c>
       <c r="AI2">
-        <v>2.237648221343874</v>
+        <v>4.877058177826563</v>
       </c>
       <c r="AJ2">
-        <v>0.7529111527996079</v>
+        <v>0.7860281589095149</v>
       </c>
       <c r="AK2">
-        <v>2.284681265705934</v>
+        <v>5.152851263962375</v>
       </c>
       <c r="AL2">
-        <v>25.6</v>
+        <v>18.8</v>
       </c>
       <c r="AM2">
-        <v>25.517</v>
+        <v>18.686</v>
       </c>
       <c r="AN2">
-        <v>29.79605263157895</v>
+        <v>-7.454697986577181</v>
       </c>
       <c r="AO2">
-        <v>-0.072265625</v>
+        <v>-3.920212765957447</v>
       </c>
       <c r="AP2">
-        <v>29.30855263157894</v>
+        <v>-7.353187919463087</v>
       </c>
       <c r="AQ2">
-        <v>-0.07250068581729827</v>
+        <v>-3.944129294659103</v>
       </c>
     </row>
     <row r="3">
@@ -712,23 +715,26 @@
           <t>Aerospace/Defense</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.145</v>
+      </c>
       <c r="G3">
-        <v>-0.5782761653474054</v>
+        <v>-0.3852835973428718</v>
       </c>
       <c r="H3">
-        <v>-0.5782761653474054</v>
+        <v>-0.3852835973428718</v>
       </c>
       <c r="I3">
-        <v>-0.008135444151275286</v>
+        <v>-0.3765968318855391</v>
       </c>
       <c r="J3">
-        <v>-0.008135444151275286</v>
+        <v>-0.3765968318855391</v>
       </c>
       <c r="K3">
-        <v>-207.1</v>
+        <v>-106.3</v>
       </c>
       <c r="L3">
-        <v>-0.9107299912049251</v>
+        <v>-0.5431783341849771</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>7.41</v>
+        <v>6.05</v>
       </c>
       <c r="V3">
-        <v>0.05068399452804378</v>
+        <v>0.05071248952221291</v>
       </c>
       <c r="W3">
-        <v>-4.521834061135372</v>
+        <v>0.4240127642600718</v>
       </c>
       <c r="X3">
-        <v>0.212211879599852</v>
+        <v>0.4451709407365354</v>
       </c>
       <c r="Y3">
-        <v>-4.734045940735223</v>
+        <v>-0.02115817647646362</v>
       </c>
       <c r="Z3">
-        <v>0.5044365572315883</v>
+        <v>1.004671697725756</v>
       </c>
       <c r="AA3">
-        <v>-0.004103815439219166</v>
+        <v>-0.3783561784485857</v>
       </c>
       <c r="AB3">
-        <v>0.07348621248393181</v>
+        <v>0.1415367700074502</v>
       </c>
       <c r="AC3">
-        <v>-0.07759002792315098</v>
+        <v>-0.519892948456036</v>
       </c>
       <c r="AD3">
-        <v>452.9</v>
+        <v>444.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>452.9</v>
+        <v>444.3</v>
       </c>
       <c r="AG3">
-        <v>445.49</v>
+        <v>438.25</v>
       </c>
       <c r="AH3">
-        <v>0.755967284259723</v>
+        <v>0.7883250532292406</v>
       </c>
       <c r="AI3">
-        <v>2.237648221343874</v>
+        <v>4.877058177826563</v>
       </c>
       <c r="AJ3">
-        <v>0.7529111527996079</v>
+        <v>0.7860281589095149</v>
       </c>
       <c r="AK3">
-        <v>2.284681265705934</v>
+        <v>5.152851263962375</v>
       </c>
       <c r="AL3">
-        <v>25.6</v>
+        <v>18.8</v>
       </c>
       <c r="AM3">
-        <v>25.517</v>
+        <v>18.686</v>
       </c>
       <c r="AN3">
-        <v>29.79605263157895</v>
+        <v>-7.454697986577181</v>
       </c>
       <c r="AO3">
-        <v>-0.072265625</v>
+        <v>-3.920212765957447</v>
       </c>
       <c r="AP3">
-        <v>29.30855263157894</v>
+        <v>-7.353187919463087</v>
       </c>
       <c r="AQ3">
-        <v>-0.07250068581729827</v>
+        <v>-3.944129294659103</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/indonesia/indonesia_aerospace_defense.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_aerospace_defense.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="idx_gmfi" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.145</v>
+        <v>-0.0611</v>
+      </c>
+      <c r="E2">
+        <v>-0.08929999999999999</v>
       </c>
       <c r="G2">
-        <v>-0.3852835973428718</v>
+        <v>0.1227447500739426</v>
       </c>
       <c r="H2">
-        <v>-0.3852835973428718</v>
+        <v>0.1227447500739426</v>
       </c>
       <c r="I2">
-        <v>-0.3765968318855391</v>
+        <v>0.1549837326234842</v>
       </c>
       <c r="J2">
-        <v>-0.3765968318855391</v>
+        <v>0.1139130434782609</v>
       </c>
       <c r="K2">
-        <v>-106.3</v>
+        <v>24.9</v>
       </c>
       <c r="L2">
-        <v>-0.5431783341849771</v>
+        <v>0.07364685004436557</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>6.05</v>
+        <v>18.6</v>
       </c>
       <c r="V2">
-        <v>0.05071248952221291</v>
+        <v>0.1267029972752044</v>
       </c>
       <c r="W2">
-        <v>0.4240127642600718</v>
+        <v>-0.07043847241867043</v>
       </c>
       <c r="X2">
-        <v>0.4451709407365354</v>
+        <v>0.2659063719471578</v>
       </c>
       <c r="Y2">
-        <v>-0.02115817647646362</v>
+        <v>-0.3363448443658282</v>
       </c>
       <c r="Z2">
-        <v>1.004671697725756</v>
+        <v>3.989380530973451</v>
       </c>
       <c r="AA2">
-        <v>-0.3783561784485857</v>
+        <v>0.4544424778761061</v>
       </c>
       <c r="AB2">
-        <v>0.1415367700074502</v>
+        <v>0.1081111531314909</v>
       </c>
       <c r="AC2">
-        <v>-0.519892948456036</v>
+        <v>0.3463313247446151</v>
       </c>
       <c r="AD2">
-        <v>444.3</v>
+        <v>461.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>444.3</v>
+        <v>461.6</v>
       </c>
       <c r="AG2">
-        <v>438.25</v>
+        <v>443</v>
       </c>
       <c r="AH2">
-        <v>0.7883250532292406</v>
+        <v>0.7587113740959894</v>
       </c>
       <c r="AI2">
-        <v>4.877058177826563</v>
+        <v>3.411677753141168</v>
       </c>
       <c r="AJ2">
-        <v>0.7860281589095149</v>
+        <v>0.7511020684977959</v>
       </c>
       <c r="AK2">
-        <v>5.152851263962375</v>
+        <v>3.796058269065981</v>
       </c>
       <c r="AL2">
-        <v>18.8</v>
+        <v>23.7</v>
       </c>
       <c r="AM2">
-        <v>18.686</v>
+        <v>22.877</v>
       </c>
       <c r="AN2">
-        <v>-7.454697986577181</v>
+        <v>6.86904761904762</v>
       </c>
       <c r="AO2">
-        <v>-3.920212765957447</v>
+        <v>2.210970464135021</v>
       </c>
       <c r="AP2">
-        <v>-7.353187919463087</v>
+        <v>6.592261904761904</v>
       </c>
       <c r="AQ2">
-        <v>-3.944129294659103</v>
+        <v>2.290510119333829</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.145</v>
+        <v>-0.0611</v>
+      </c>
+      <c r="E3">
+        <v>-0.08929999999999999</v>
       </c>
       <c r="G3">
-        <v>-0.3852835973428718</v>
+        <v>0.1227447500739426</v>
       </c>
       <c r="H3">
-        <v>-0.3852835973428718</v>
+        <v>0.1227447500739426</v>
       </c>
       <c r="I3">
-        <v>-0.3765968318855391</v>
+        <v>0.1549837326234842</v>
       </c>
       <c r="J3">
-        <v>-0.3765968318855391</v>
+        <v>0.1139130434782609</v>
       </c>
       <c r="K3">
-        <v>-106.3</v>
+        <v>24.9</v>
       </c>
       <c r="L3">
-        <v>-0.5431783341849771</v>
+        <v>0.07364685004436557</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +760,8848 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>6.05</v>
+        <v>18.6</v>
       </c>
       <c r="V3">
-        <v>0.05071248952221291</v>
+        <v>0.1267029972752044</v>
       </c>
       <c r="W3">
-        <v>0.4240127642600718</v>
+        <v>-0.07043847241867043</v>
       </c>
       <c r="X3">
-        <v>0.4451709407365354</v>
+        <v>0.2659063719471578</v>
       </c>
       <c r="Y3">
-        <v>-0.02115817647646362</v>
+        <v>-0.3363448443658282</v>
       </c>
       <c r="Z3">
-        <v>1.004671697725756</v>
+        <v>3.989380530973451</v>
       </c>
       <c r="AA3">
-        <v>-0.3783561784485857</v>
+        <v>0.4544424778761061</v>
       </c>
       <c r="AB3">
-        <v>0.1415367700074502</v>
+        <v>0.1081111531314909</v>
       </c>
       <c r="AC3">
-        <v>-0.519892948456036</v>
+        <v>0.3463313247446151</v>
       </c>
       <c r="AD3">
-        <v>444.3</v>
+        <v>461.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>444.3</v>
+        <v>461.6</v>
       </c>
       <c r="AG3">
-        <v>438.25</v>
+        <v>443</v>
       </c>
       <c r="AH3">
-        <v>0.7883250532292406</v>
+        <v>0.7587113740959894</v>
       </c>
       <c r="AI3">
-        <v>4.877058177826563</v>
+        <v>3.411677753141168</v>
       </c>
       <c r="AJ3">
-        <v>0.7860281589095149</v>
+        <v>0.7511020684977959</v>
       </c>
       <c r="AK3">
-        <v>5.152851263962375</v>
+        <v>3.796058269065981</v>
       </c>
       <c r="AL3">
-        <v>18.8</v>
+        <v>23.7</v>
       </c>
       <c r="AM3">
-        <v>18.686</v>
+        <v>22.877</v>
       </c>
       <c r="AN3">
-        <v>-7.454697986577181</v>
+        <v>6.86904761904762</v>
       </c>
       <c r="AO3">
-        <v>-3.920212765957447</v>
+        <v>2.210970464135021</v>
       </c>
       <c r="AP3">
-        <v>-7.353187919463087</v>
+        <v>6.592261904761904</v>
       </c>
       <c r="AQ3">
-        <v>-3.944129294659103</v>
+        <v>2.290510119333829</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PT Garuda Maintenance Facility Aero Asia Tbk (IDX:GMFI)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IDX:GMFI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Aerospace/Defense</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1.89873417721519</v>
+      </c>
+      <c r="F2">
+        <v>4.53553800992217</v>
+      </c>
+      <c r="G2">
+        <v>6.86904761904762</v>
+      </c>
+      <c r="H2">
+        <v>3.98357142857143</v>
+      </c>
+      <c r="I2">
+        <v>0.758711374095989</v>
+      </c>
+      <c r="J2">
+        <v>0.44</v>
+      </c>
+      <c r="K2">
+        <v>146.8</v>
+      </c>
+      <c r="L2">
+        <v>408.086471540896</v>
+      </c>
+      <c r="M2">
+        <v>589.8</v>
+      </c>
+      <c r="N2">
+        <v>657.182471540896</v>
+      </c>
+      <c r="O2">
+        <v>461.6</v>
+      </c>
+      <c r="P2">
+        <v>267.696</v>
+      </c>
+      <c r="Q2">
+        <v>0.108111153131491</v>
+      </c>
+      <c r="R2">
+        <v>0.09860715556771341</v>
+      </c>
+      <c r="S2">
+        <v>0.0579284448946194</v>
+      </c>
+      <c r="T2">
+        <v>0.039702</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.265906371947158</v>
+      </c>
+      <c r="X2">
+        <v>0.144889777799488</v>
+      </c>
+      <c r="Y2">
+        <v>3.07538259811358</v>
+      </c>
+      <c r="Z2">
+        <v>1.43662484537509</v>
+      </c>
+      <c r="AA2">
+        <v>461.6</v>
+      </c>
+      <c r="AB2">
+        <v>0.07426723704438384</v>
+      </c>
+      <c r="AC2">
+        <v>1.89873417721519</v>
+      </c>
+      <c r="AD2">
+        <v>461.6</v>
+      </c>
+      <c r="AE2">
+        <v>23.7</v>
+      </c>
+      <c r="AF2">
+        <v>22.2</v>
+      </c>
+      <c r="AG2">
+        <v>67.2</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>146.8</v>
+      </c>
+      <c r="AK2">
+        <v>0.07384654256887045</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.22</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>3.460000000000004</v>
+      </c>
+      <c r="AR2">
+        <v>23.7</v>
+      </c>
+      <c r="AT2">
+        <v>18.6</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1045775415940139</v>
+      </c>
+      <c r="C2">
+        <v>631.7753510340139</v>
+      </c>
+      <c r="D2">
+        <v>613.1753510340138</v>
+      </c>
+      <c r="E2">
+        <v>-461.6</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>18.6</v>
+      </c>
+      <c r="H2">
+        <v>146.8</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>84</v>
+      </c>
+      <c r="K2">
+        <v>22.2</v>
+      </c>
+      <c r="L2">
+        <v>61.8</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>61.8</v>
+      </c>
+      <c r="O2">
+        <v>13.596</v>
+      </c>
+      <c r="P2">
+        <v>48.20399999999999</v>
+      </c>
+      <c r="Q2">
+        <v>70.404</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1045775415940139</v>
+      </c>
+      <c r="T2">
+        <v>0.890732853642657</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.22</v>
+      </c>
+      <c r="W2">
+        <v>0.034866</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1043934910025071</v>
+      </c>
+      <c r="C3">
+        <v>626.9597442587934</v>
+      </c>
+      <c r="D3">
+        <v>614.4437442587933</v>
+      </c>
+      <c r="E3">
+        <v>-455.516</v>
+      </c>
+      <c r="F3">
+        <v>6.084000000000001</v>
+      </c>
+      <c r="G3">
+        <v>18.6</v>
+      </c>
+      <c r="H3">
+        <v>146.8</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>84</v>
+      </c>
+      <c r="K3">
+        <v>22.2</v>
+      </c>
+      <c r="L3">
+        <v>61.8</v>
+      </c>
+      <c r="M3">
+        <v>0.2719548000000001</v>
+      </c>
+      <c r="N3">
+        <v>61.52804519999999</v>
+      </c>
+      <c r="O3">
+        <v>13.536169944</v>
+      </c>
+      <c r="P3">
+        <v>47.99187525599999</v>
+      </c>
+      <c r="Q3">
+        <v>70.19187525599999</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1050957888914213</v>
+      </c>
+      <c r="T3">
+        <v>0.8977507488531749</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.22</v>
+      </c>
+      <c r="W3">
+        <v>0.034866</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>227.2436448998141</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1042094404110003</v>
+      </c>
+      <c r="C4">
+        <v>622.1493958691888</v>
+      </c>
+      <c r="D4">
+        <v>615.7173958691887</v>
+      </c>
+      <c r="E4">
+        <v>-449.432</v>
+      </c>
+      <c r="F4">
+        <v>12.168</v>
+      </c>
+      <c r="G4">
+        <v>18.6</v>
+      </c>
+      <c r="H4">
+        <v>146.8</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>84</v>
+      </c>
+      <c r="K4">
+        <v>22.2</v>
+      </c>
+      <c r="L4">
+        <v>61.8</v>
+      </c>
+      <c r="M4">
+        <v>0.5439096000000002</v>
+      </c>
+      <c r="N4">
+        <v>61.2560904</v>
+      </c>
+      <c r="O4">
+        <v>13.476339888</v>
+      </c>
+      <c r="P4">
+        <v>47.779750512</v>
+      </c>
+      <c r="Q4">
+        <v>69.979750512</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.105624612664286</v>
+      </c>
+      <c r="T4">
+        <v>0.9049118664149278</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.22</v>
+      </c>
+      <c r="W4">
+        <v>0.034866</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>113.6218224499071</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1040253898194934</v>
+      </c>
+      <c r="C5">
+        <v>617.3443386327053</v>
+      </c>
+      <c r="D5">
+        <v>616.9963386327053</v>
+      </c>
+      <c r="E5">
+        <v>-443.348</v>
+      </c>
+      <c r="F5">
+        <v>18.252</v>
+      </c>
+      <c r="G5">
+        <v>18.6</v>
+      </c>
+      <c r="H5">
+        <v>146.8</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>84</v>
+      </c>
+      <c r="K5">
+        <v>22.2</v>
+      </c>
+      <c r="L5">
+        <v>61.8</v>
+      </c>
+      <c r="M5">
+        <v>0.8158644000000002</v>
+      </c>
+      <c r="N5">
+        <v>60.98413559999999</v>
+      </c>
+      <c r="O5">
+        <v>13.416509832</v>
+      </c>
+      <c r="P5">
+        <v>47.567625768</v>
+      </c>
+      <c r="Q5">
+        <v>69.767625768</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1061643400200963</v>
+      </c>
+      <c r="T5">
+        <v>0.9122206358851705</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.22</v>
+      </c>
+      <c r="W5">
+        <v>0.034866</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>75.74788163327139</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1038413392279866</v>
+      </c>
+      <c r="C6">
+        <v>612.5446055896672</v>
+      </c>
+      <c r="D6">
+        <v>618.2806055896672</v>
+      </c>
+      <c r="E6">
+        <v>-437.264</v>
+      </c>
+      <c r="F6">
+        <v>24.33600000000001</v>
+      </c>
+      <c r="G6">
+        <v>18.6</v>
+      </c>
+      <c r="H6">
+        <v>146.8</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>84</v>
+      </c>
+      <c r="K6">
+        <v>22.2</v>
+      </c>
+      <c r="L6">
+        <v>61.8</v>
+      </c>
+      <c r="M6">
+        <v>1.0878192</v>
+      </c>
+      <c r="N6">
+        <v>60.7121808</v>
+      </c>
+      <c r="O6">
+        <v>13.356679776</v>
+      </c>
+      <c r="P6">
+        <v>47.355501024</v>
+      </c>
+      <c r="Q6">
+        <v>69.55550102399999</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1067153116958194</v>
+      </c>
+      <c r="T6">
+        <v>0.9196816713860433</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.22</v>
+      </c>
+      <c r="W6">
+        <v>0.034866</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>56.81091122495354</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1036572886364798</v>
+      </c>
+      <c r="C7">
+        <v>607.7502300560642</v>
+      </c>
+      <c r="D7">
+        <v>619.5702300560641</v>
+      </c>
+      <c r="E7">
+        <v>-431.18</v>
+      </c>
+      <c r="F7">
+        <v>30.42000000000001</v>
+      </c>
+      <c r="G7">
+        <v>18.6</v>
+      </c>
+      <c r="H7">
+        <v>146.8</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>84</v>
+      </c>
+      <c r="K7">
+        <v>22.2</v>
+      </c>
+      <c r="L7">
+        <v>61.8</v>
+      </c>
+      <c r="M7">
+        <v>1.359774</v>
+      </c>
+      <c r="N7">
+        <v>60.440226</v>
+      </c>
+      <c r="O7">
+        <v>13.29684972</v>
+      </c>
+      <c r="P7">
+        <v>47.14337628</v>
+      </c>
+      <c r="Q7">
+        <v>69.34337628</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1072778827752419</v>
+      </c>
+      <c r="T7">
+        <v>0.9272997813185135</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.22</v>
+      </c>
+      <c r="W7">
+        <v>0.034866</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>45.44872897996284</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1034732380449729</v>
+      </c>
+      <c r="C8">
+        <v>602.9612456264331</v>
+      </c>
+      <c r="D8">
+        <v>620.8652456264331</v>
+      </c>
+      <c r="E8">
+        <v>-425.096</v>
+      </c>
+      <c r="F8">
+        <v>36.504</v>
+      </c>
+      <c r="G8">
+        <v>18.6</v>
+      </c>
+      <c r="H8">
+        <v>146.8</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>84</v>
+      </c>
+      <c r="K8">
+        <v>22.2</v>
+      </c>
+      <c r="L8">
+        <v>61.8</v>
+      </c>
+      <c r="M8">
+        <v>1.6317288</v>
+      </c>
+      <c r="N8">
+        <v>60.1682712</v>
+      </c>
+      <c r="O8">
+        <v>13.237019664</v>
+      </c>
+      <c r="P8">
+        <v>46.931251536</v>
+      </c>
+      <c r="Q8">
+        <v>69.13125153599999</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1078524234520989</v>
+      </c>
+      <c r="T8">
+        <v>0.9350799786963552</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.22</v>
+      </c>
+      <c r="W8">
+        <v>0.034866</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>37.8739408166357</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1032891874534661</v>
+      </c>
+      <c r="C9">
+        <v>598.1776861767723</v>
+      </c>
+      <c r="D9">
+        <v>622.1656861767723</v>
+      </c>
+      <c r="E9">
+        <v>-419.012</v>
+      </c>
+      <c r="F9">
+        <v>42.58800000000001</v>
+      </c>
+      <c r="G9">
+        <v>18.6</v>
+      </c>
+      <c r="H9">
+        <v>146.8</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>84</v>
+      </c>
+      <c r="K9">
+        <v>22.2</v>
+      </c>
+      <c r="L9">
+        <v>61.8</v>
+      </c>
+      <c r="M9">
+        <v>1.903683600000001</v>
+      </c>
+      <c r="N9">
+        <v>59.8963164</v>
+      </c>
+      <c r="O9">
+        <v>13.177189608</v>
+      </c>
+      <c r="P9">
+        <v>46.719126792</v>
+      </c>
+      <c r="Q9">
+        <v>68.919126792</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1084393198424367</v>
+      </c>
+      <c r="T9">
+        <v>0.9430274921468389</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.22</v>
+      </c>
+      <c r="W9">
+        <v>0.034866</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>32.4633778428306</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1031051368619593</v>
+      </c>
+      <c r="C10">
+        <v>593.399585867499</v>
+      </c>
+      <c r="D10">
+        <v>623.471585867499</v>
+      </c>
+      <c r="E10">
+        <v>-412.928</v>
+      </c>
+      <c r="F10">
+        <v>48.67200000000001</v>
+      </c>
+      <c r="G10">
+        <v>18.6</v>
+      </c>
+      <c r="H10">
+        <v>146.8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>84</v>
+      </c>
+      <c r="K10">
+        <v>22.2</v>
+      </c>
+      <c r="L10">
+        <v>61.8</v>
+      </c>
+      <c r="M10">
+        <v>2.175638400000001</v>
+      </c>
+      <c r="N10">
+        <v>59.62436159999999</v>
+      </c>
+      <c r="O10">
+        <v>13.117359552</v>
+      </c>
+      <c r="P10">
+        <v>46.507002048</v>
+      </c>
+      <c r="Q10">
+        <v>68.70700204799999</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1090389748499557</v>
+      </c>
+      <c r="T10">
+        <v>0.9511477776288545</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.22</v>
+      </c>
+      <c r="W10">
+        <v>0.034866</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>28.40545561247676</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1029210862704525</v>
+      </c>
+      <c r="C11">
+        <v>588.6269791464381</v>
+      </c>
+      <c r="D11">
+        <v>624.782979146438</v>
+      </c>
+      <c r="E11">
+        <v>-406.844</v>
+      </c>
+      <c r="F11">
+        <v>54.75600000000001</v>
+      </c>
+      <c r="G11">
+        <v>18.6</v>
+      </c>
+      <c r="H11">
+        <v>146.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>84</v>
+      </c>
+      <c r="K11">
+        <v>22.2</v>
+      </c>
+      <c r="L11">
+        <v>61.8</v>
+      </c>
+      <c r="M11">
+        <v>2.4475932</v>
+      </c>
+      <c r="N11">
+        <v>59.3524068</v>
+      </c>
+      <c r="O11">
+        <v>13.057529496</v>
+      </c>
+      <c r="P11">
+        <v>46.294877304</v>
+      </c>
+      <c r="Q11">
+        <v>68.494877304</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1096518090884093</v>
+      </c>
+      <c r="T11">
+        <v>0.9594465309236619</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.22</v>
+      </c>
+      <c r="W11">
+        <v>0.034866</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>25.24929387775713</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1027370356789456</v>
+      </c>
+      <c r="C12">
+        <v>583.8599007518515</v>
+      </c>
+      <c r="D12">
+        <v>626.0999007518515</v>
+      </c>
+      <c r="E12">
+        <v>-400.76</v>
+      </c>
+      <c r="F12">
+        <v>60.84000000000001</v>
+      </c>
+      <c r="G12">
+        <v>18.6</v>
+      </c>
+      <c r="H12">
+        <v>146.8</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>84</v>
+      </c>
+      <c r="K12">
+        <v>22.2</v>
+      </c>
+      <c r="L12">
+        <v>61.8</v>
+      </c>
+      <c r="M12">
+        <v>2.719548000000001</v>
+      </c>
+      <c r="N12">
+        <v>59.08045199999999</v>
+      </c>
+      <c r="O12">
+        <v>12.99769944</v>
+      </c>
+      <c r="P12">
+        <v>46.08275256</v>
+      </c>
+      <c r="Q12">
+        <v>68.28275255999999</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1102782618654951</v>
+      </c>
+      <c r="T12">
+        <v>0.967929700958354</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.22</v>
+      </c>
+      <c r="W12">
+        <v>0.034866</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>22.72436448998142</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1025529850874388</v>
+      </c>
+      <c r="C13">
+        <v>579.0983857155067</v>
+      </c>
+      <c r="D13">
+        <v>627.4223857155066</v>
+      </c>
+      <c r="E13">
+        <v>-394.676</v>
+      </c>
+      <c r="F13">
+        <v>66.92400000000001</v>
+      </c>
+      <c r="G13">
+        <v>18.6</v>
+      </c>
+      <c r="H13">
+        <v>146.8</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>84</v>
+      </c>
+      <c r="K13">
+        <v>22.2</v>
+      </c>
+      <c r="L13">
+        <v>61.8</v>
+      </c>
+      <c r="M13">
+        <v>2.991502800000001</v>
+      </c>
+      <c r="N13">
+        <v>58.8084972</v>
+      </c>
+      <c r="O13">
+        <v>12.937869384</v>
+      </c>
+      <c r="P13">
+        <v>45.870627816</v>
+      </c>
+      <c r="Q13">
+        <v>68.070627816</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1109187922330773</v>
+      </c>
+      <c r="T13">
+        <v>0.9766035040275335</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.22</v>
+      </c>
+      <c r="W13">
+        <v>0.034866</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>20.65851317271038</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.102368934495932</v>
+      </c>
+      <c r="C14">
+        <v>574.3424693657817</v>
+      </c>
+      <c r="D14">
+        <v>628.7504693657817</v>
+      </c>
+      <c r="E14">
+        <v>-388.592</v>
+      </c>
+      <c r="F14">
+        <v>73.00800000000001</v>
+      </c>
+      <c r="G14">
+        <v>18.6</v>
+      </c>
+      <c r="H14">
+        <v>146.8</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>84</v>
+      </c>
+      <c r="K14">
+        <v>22.2</v>
+      </c>
+      <c r="L14">
+        <v>61.8</v>
+      </c>
+      <c r="M14">
+        <v>3.263457600000001</v>
+      </c>
+      <c r="N14">
+        <v>58.53654239999999</v>
+      </c>
+      <c r="O14">
+        <v>12.878039328</v>
+      </c>
+      <c r="P14">
+        <v>45.65850307199999</v>
+      </c>
+      <c r="Q14">
+        <v>67.85850307199999</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1115738801090136</v>
+      </c>
+      <c r="T14">
+        <v>0.9854744389846487</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.22</v>
+      </c>
+      <c r="W14">
+        <v>0.034866</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>18.93697040831785</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1021848839044251</v>
+      </c>
+      <c r="C15">
+        <v>569.592187330812</v>
+      </c>
+      <c r="D15">
+        <v>630.0841873308119</v>
+      </c>
+      <c r="E15">
+        <v>-382.508</v>
+      </c>
+      <c r="F15">
+        <v>79.09200000000001</v>
+      </c>
+      <c r="G15">
+        <v>18.6</v>
+      </c>
+      <c r="H15">
+        <v>146.8</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>84</v>
+      </c>
+      <c r="K15">
+        <v>22.2</v>
+      </c>
+      <c r="L15">
+        <v>61.8</v>
+      </c>
+      <c r="M15">
+        <v>3.535412400000001</v>
+      </c>
+      <c r="N15">
+        <v>58.2645876</v>
+      </c>
+      <c r="O15">
+        <v>12.818209272</v>
+      </c>
+      <c r="P15">
+        <v>45.446378328</v>
+      </c>
+      <c r="Q15">
+        <v>67.646378328</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1122440274763507</v>
+      </c>
+      <c r="T15">
+        <v>0.994549303481008</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.22</v>
+      </c>
+      <c r="W15">
+        <v>0.034866</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>17.48028037690878</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1020008333129183</v>
+      </c>
+      <c r="C16">
+        <v>564.8475755416756</v>
+      </c>
+      <c r="D16">
+        <v>631.4235755416756</v>
+      </c>
+      <c r="E16">
+        <v>-376.424</v>
+      </c>
+      <c r="F16">
+        <v>85.17600000000002</v>
+      </c>
+      <c r="G16">
+        <v>18.6</v>
+      </c>
+      <c r="H16">
+        <v>146.8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>84</v>
+      </c>
+      <c r="K16">
+        <v>22.2</v>
+      </c>
+      <c r="L16">
+        <v>61.8</v>
+      </c>
+      <c r="M16">
+        <v>3.807367200000001</v>
+      </c>
+      <c r="N16">
+        <v>57.9926328</v>
+      </c>
+      <c r="O16">
+        <v>12.758379216</v>
+      </c>
+      <c r="P16">
+        <v>45.23425358399999</v>
+      </c>
+      <c r="Q16">
+        <v>67.43425358399999</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1129297596661841</v>
+      </c>
+      <c r="T16">
+        <v>1.003835211337748</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.22</v>
+      </c>
+      <c r="W16">
+        <v>0.034866</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>16.2316889214153</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1018167827214115</v>
+      </c>
+      <c r="C17">
+        <v>560.108670235621</v>
+      </c>
+      <c r="D17">
+        <v>632.768670235621</v>
+      </c>
+      <c r="E17">
+        <v>-370.34</v>
+      </c>
+      <c r="F17">
+        <v>91.26000000000001</v>
+      </c>
+      <c r="G17">
+        <v>18.6</v>
+      </c>
+      <c r="H17">
+        <v>146.8</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>84</v>
+      </c>
+      <c r="K17">
+        <v>22.2</v>
+      </c>
+      <c r="L17">
+        <v>61.8</v>
+      </c>
+      <c r="M17">
+        <v>4.079322</v>
+      </c>
+      <c r="N17">
+        <v>57.720678</v>
+      </c>
+      <c r="O17">
+        <v>12.69854916</v>
+      </c>
+      <c r="P17">
+        <v>45.02212884</v>
+      </c>
+      <c r="Q17">
+        <v>67.22212884</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1136316267310723</v>
+      </c>
+      <c r="T17">
+        <v>1.013339611144058</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.22</v>
+      </c>
+      <c r="W17">
+        <v>0.034866</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>15.14957632665428</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1016327321299046</v>
+      </c>
+      <c r="C18">
+        <v>555.3755079593336</v>
+      </c>
+      <c r="D18">
+        <v>634.1195079593336</v>
+      </c>
+      <c r="E18">
+        <v>-364.256</v>
+      </c>
+      <c r="F18">
+        <v>97.34400000000002</v>
+      </c>
+      <c r="G18">
+        <v>18.6</v>
+      </c>
+      <c r="H18">
+        <v>146.8</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>84</v>
+      </c>
+      <c r="K18">
+        <v>22.2</v>
+      </c>
+      <c r="L18">
+        <v>61.8</v>
+      </c>
+      <c r="M18">
+        <v>4.351276800000002</v>
+      </c>
+      <c r="N18">
+        <v>57.4487232</v>
+      </c>
+      <c r="O18">
+        <v>12.638719104</v>
+      </c>
+      <c r="P18">
+        <v>44.810004096</v>
+      </c>
+      <c r="Q18">
+        <v>67.010004096</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1143502049165531</v>
+      </c>
+      <c r="T18">
+        <v>1.023070306183852</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.22</v>
+      </c>
+      <c r="W18">
+        <v>0.034866</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>14.20272780623838</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1014486815383978</v>
+      </c>
+      <c r="C19">
+        <v>550.6481255722476</v>
+      </c>
+      <c r="D19">
+        <v>635.4761255722476</v>
+      </c>
+      <c r="E19">
+        <v>-358.172</v>
+      </c>
+      <c r="F19">
+        <v>103.428</v>
+      </c>
+      <c r="G19">
+        <v>18.6</v>
+      </c>
+      <c r="H19">
+        <v>146.8</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>84</v>
+      </c>
+      <c r="K19">
+        <v>22.2</v>
+      </c>
+      <c r="L19">
+        <v>61.8</v>
+      </c>
+      <c r="M19">
+        <v>4.623231600000001</v>
+      </c>
+      <c r="N19">
+        <v>57.17676839999999</v>
+      </c>
+      <c r="O19">
+        <v>12.578889048</v>
+      </c>
+      <c r="P19">
+        <v>44.59787935199999</v>
+      </c>
+      <c r="Q19">
+        <v>66.797879352</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1150860982390335</v>
+      </c>
+      <c r="T19">
+        <v>1.033035475802918</v>
+      </c>
+      <c r="U19">
+        <v>0.0447</v>
+      </c>
+      <c r="V19">
+        <v>0.22</v>
+      </c>
+      <c r="W19">
+        <v>0.034866</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>13.36727322940083</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.101419070946891</v>
+      </c>
+      <c r="C20">
+        <v>544.7829243776969</v>
+      </c>
+      <c r="D20">
+        <v>635.6949243776969</v>
+      </c>
+      <c r="E20">
+        <v>-352.088</v>
+      </c>
+      <c r="F20">
+        <v>109.512</v>
+      </c>
+      <c r="G20">
+        <v>18.6</v>
+      </c>
+      <c r="H20">
+        <v>146.8</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>84</v>
+      </c>
+      <c r="K20">
+        <v>22.2</v>
+      </c>
+      <c r="L20">
+        <v>61.8</v>
+      </c>
+      <c r="M20">
+        <v>5.015649600000001</v>
+      </c>
+      <c r="N20">
+        <v>56.78435039999999</v>
+      </c>
+      <c r="O20">
+        <v>12.492557088</v>
+      </c>
+      <c r="P20">
+        <v>44.291793312</v>
+      </c>
+      <c r="Q20">
+        <v>66.491793312</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1158399401791353</v>
+      </c>
+      <c r="T20">
+        <v>1.043243698339522</v>
+      </c>
+      <c r="U20">
+        <v>0.0458</v>
+      </c>
+      <c r="V20">
+        <v>0.22</v>
+      </c>
+      <c r="W20">
+        <v>0.035724</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>12.32143489449502</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1012436003553841</v>
+      </c>
+      <c r="C21">
+        <v>539.9986112221023</v>
+      </c>
+      <c r="D21">
+        <v>636.9946112221023</v>
+      </c>
+      <c r="E21">
+        <v>-346.004</v>
+      </c>
+      <c r="F21">
+        <v>115.596</v>
+      </c>
+      <c r="G21">
+        <v>18.6</v>
+      </c>
+      <c r="H21">
+        <v>146.8</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>84</v>
+      </c>
+      <c r="K21">
+        <v>22.2</v>
+      </c>
+      <c r="L21">
+        <v>61.8</v>
+      </c>
+      <c r="M21">
+        <v>5.294296800000001</v>
+      </c>
+      <c r="N21">
+        <v>56.5057032</v>
+      </c>
+      <c r="O21">
+        <v>12.431254704</v>
+      </c>
+      <c r="P21">
+        <v>44.074448496</v>
+      </c>
+      <c r="Q21">
+        <v>66.27444849600001</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1166123955004742</v>
+      </c>
+      <c r="T21">
+        <v>1.053703975753573</v>
+      </c>
+      <c r="U21">
+        <v>0.0458</v>
+      </c>
+      <c r="V21">
+        <v>0.22</v>
+      </c>
+      <c r="W21">
+        <v>0.035724</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>11.67293832110055</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1010681297638773</v>
+      </c>
+      <c r="C22">
+        <v>535.2196234087977</v>
+      </c>
+      <c r="D22">
+        <v>638.2996234087977</v>
+      </c>
+      <c r="E22">
+        <v>-339.92</v>
+      </c>
+      <c r="F22">
+        <v>121.68</v>
+      </c>
+      <c r="G22">
+        <v>18.6</v>
+      </c>
+      <c r="H22">
+        <v>146.8</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>84</v>
+      </c>
+      <c r="K22">
+        <v>22.2</v>
+      </c>
+      <c r="L22">
+        <v>61.8</v>
+      </c>
+      <c r="M22">
+        <v>5.572944000000001</v>
+      </c>
+      <c r="N22">
+        <v>56.227056</v>
+      </c>
+      <c r="O22">
+        <v>12.36995232</v>
+      </c>
+      <c r="P22">
+        <v>43.85710367999999</v>
+      </c>
+      <c r="Q22">
+        <v>66.05710368</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1174041622048466</v>
+      </c>
+      <c r="T22">
+        <v>1.064425760102975</v>
+      </c>
+      <c r="U22">
+        <v>0.0458</v>
+      </c>
+      <c r="V22">
+        <v>0.22</v>
+      </c>
+      <c r="W22">
+        <v>0.035724</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>11.08929140504552</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1008926591723705</v>
+      </c>
+      <c r="C23">
+        <v>530.4459937350949</v>
+      </c>
+      <c r="D23">
+        <v>639.6099937350949</v>
+      </c>
+      <c r="E23">
+        <v>-333.836</v>
+      </c>
+      <c r="F23">
+        <v>127.764</v>
+      </c>
+      <c r="G23">
+        <v>18.6</v>
+      </c>
+      <c r="H23">
+        <v>146.8</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>84</v>
+      </c>
+      <c r="K23">
+        <v>22.2</v>
+      </c>
+      <c r="L23">
+        <v>61.8</v>
+      </c>
+      <c r="M23">
+        <v>5.851591200000001</v>
+      </c>
+      <c r="N23">
+        <v>55.9484088</v>
+      </c>
+      <c r="O23">
+        <v>12.308649936</v>
+      </c>
+      <c r="P23">
+        <v>43.639758864</v>
+      </c>
+      <c r="Q23">
+        <v>65.839758864</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.118215973635912</v>
+      </c>
+      <c r="T23">
+        <v>1.075418982030843</v>
+      </c>
+      <c r="U23">
+        <v>0.0458</v>
+      </c>
+      <c r="V23">
+        <v>0.22</v>
+      </c>
+      <c r="W23">
+        <v>0.035724</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>10.56122990956716</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1007171885808636</v>
+      </c>
+      <c r="C24">
+        <v>525.6777552681783</v>
+      </c>
+      <c r="D24">
+        <v>640.9257552681782</v>
+      </c>
+      <c r="E24">
+        <v>-327.752</v>
+      </c>
+      <c r="F24">
+        <v>133.848</v>
+      </c>
+      <c r="G24">
+        <v>18.6</v>
+      </c>
+      <c r="H24">
+        <v>146.8</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>84</v>
+      </c>
+      <c r="K24">
+        <v>22.2</v>
+      </c>
+      <c r="L24">
+        <v>61.8</v>
+      </c>
+      <c r="M24">
+        <v>6.130238400000001</v>
+      </c>
+      <c r="N24">
+        <v>55.66976159999999</v>
+      </c>
+      <c r="O24">
+        <v>12.247347552</v>
+      </c>
+      <c r="P24">
+        <v>43.42241404799999</v>
+      </c>
+      <c r="Q24">
+        <v>65.622414048</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.119048600744697</v>
+      </c>
+      <c r="T24">
+        <v>1.086694081444042</v>
+      </c>
+      <c r="U24">
+        <v>0.0458</v>
+      </c>
+      <c r="V24">
+        <v>0.22</v>
+      </c>
+      <c r="W24">
+        <v>0.035724</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>10.08117400458683</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1009363979893568</v>
+      </c>
+      <c r="C25">
+        <v>517.9508600886686</v>
+      </c>
+      <c r="D25">
+        <v>639.2828600886686</v>
+      </c>
+      <c r="E25">
+        <v>-321.668</v>
+      </c>
+      <c r="F25">
+        <v>139.932</v>
+      </c>
+      <c r="G25">
+        <v>18.6</v>
+      </c>
+      <c r="H25">
+        <v>146.8</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>84</v>
+      </c>
+      <c r="K25">
+        <v>22.2</v>
+      </c>
+      <c r="L25">
+        <v>61.8</v>
+      </c>
+      <c r="M25">
+        <v>6.716736000000001</v>
+      </c>
+      <c r="N25">
+        <v>55.083264</v>
+      </c>
+      <c r="O25">
+        <v>12.11831808</v>
+      </c>
+      <c r="P25">
+        <v>42.96494592</v>
+      </c>
+      <c r="Q25">
+        <v>65.16494591999999</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1199028545316322</v>
+      </c>
+      <c r="T25">
+        <v>1.098262040582258</v>
+      </c>
+      <c r="U25">
+        <v>0.048</v>
+      </c>
+      <c r="V25">
+        <v>0.22</v>
+      </c>
+      <c r="W25">
+        <v>0.03744</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>9.200897578824</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.10077808739785</v>
+      </c>
+      <c r="C26">
+        <v>513.0524941947458</v>
+      </c>
+      <c r="D26">
+        <v>640.4684941947457</v>
+      </c>
+      <c r="E26">
+        <v>-315.584</v>
+      </c>
+      <c r="F26">
+        <v>146.016</v>
+      </c>
+      <c r="G26">
+        <v>18.6</v>
+      </c>
+      <c r="H26">
+        <v>146.8</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>84</v>
+      </c>
+      <c r="K26">
+        <v>22.2</v>
+      </c>
+      <c r="L26">
+        <v>61.8</v>
+      </c>
+      <c r="M26">
+        <v>7.008768000000001</v>
+      </c>
+      <c r="N26">
+        <v>54.79123199999999</v>
+      </c>
+      <c r="O26">
+        <v>12.05407104</v>
+      </c>
+      <c r="P26">
+        <v>42.73716096</v>
+      </c>
+      <c r="Q26">
+        <v>64.93716096</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1207795886813816</v>
+      </c>
+      <c r="T26">
+        <v>1.110134419697796</v>
+      </c>
+      <c r="U26">
+        <v>0.048</v>
+      </c>
+      <c r="V26">
+        <v>0.22</v>
+      </c>
+      <c r="W26">
+        <v>0.03744</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>8.817526846372999</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1006197768063432</v>
+      </c>
+      <c r="C27">
+        <v>508.1585343009629</v>
+      </c>
+      <c r="D27">
+        <v>641.6585343009629</v>
+      </c>
+      <c r="E27">
+        <v>-309.5</v>
+      </c>
+      <c r="F27">
+        <v>152.1</v>
+      </c>
+      <c r="G27">
+        <v>18.6</v>
+      </c>
+      <c r="H27">
+        <v>146.8</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>84</v>
+      </c>
+      <c r="K27">
+        <v>22.2</v>
+      </c>
+      <c r="L27">
+        <v>61.8</v>
+      </c>
+      <c r="M27">
+        <v>7.300800000000002</v>
+      </c>
+      <c r="N27">
+        <v>54.49919999999999</v>
+      </c>
+      <c r="O27">
+        <v>11.989824</v>
+      </c>
+      <c r="P27">
+        <v>42.509376</v>
+      </c>
+      <c r="Q27">
+        <v>64.70937599999999</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1216797024084575</v>
+      </c>
+      <c r="T27">
+        <v>1.122323395589748</v>
+      </c>
+      <c r="U27">
+        <v>0.048</v>
+      </c>
+      <c r="V27">
+        <v>0.22</v>
+      </c>
+      <c r="W27">
+        <v>0.03744</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>8.464825772518079</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1004614662148363</v>
+      </c>
+      <c r="C28">
+        <v>503.2690050131087</v>
+      </c>
+      <c r="D28">
+        <v>642.8530050131087</v>
+      </c>
+      <c r="E28">
+        <v>-303.416</v>
+      </c>
+      <c r="F28">
+        <v>158.184</v>
+      </c>
+      <c r="G28">
+        <v>18.6</v>
+      </c>
+      <c r="H28">
+        <v>146.8</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>84</v>
+      </c>
+      <c r="K28">
+        <v>22.2</v>
+      </c>
+      <c r="L28">
+        <v>61.8</v>
+      </c>
+      <c r="M28">
+        <v>7.592832000000001</v>
+      </c>
+      <c r="N28">
+        <v>54.207168</v>
+      </c>
+      <c r="O28">
+        <v>11.92557696</v>
+      </c>
+      <c r="P28">
+        <v>42.28159104</v>
+      </c>
+      <c r="Q28">
+        <v>64.48159104</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1226041435335626</v>
+      </c>
+      <c r="T28">
+        <v>1.134841803262564</v>
+      </c>
+      <c r="U28">
+        <v>0.048</v>
+      </c>
+      <c r="V28">
+        <v>0.22</v>
+      </c>
+      <c r="W28">
+        <v>0.03744</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>8.139255550498152</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1003031556233295</v>
+      </c>
+      <c r="C29">
+        <v>498.383931120532</v>
+      </c>
+      <c r="D29">
+        <v>644.051931120532</v>
+      </c>
+      <c r="E29">
+        <v>-297.332</v>
+      </c>
+      <c r="F29">
+        <v>164.268</v>
+      </c>
+      <c r="G29">
+        <v>18.6</v>
+      </c>
+      <c r="H29">
+        <v>146.8</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>84</v>
+      </c>
+      <c r="K29">
+        <v>22.2</v>
+      </c>
+      <c r="L29">
+        <v>61.8</v>
+      </c>
+      <c r="M29">
+        <v>7.884864000000001</v>
+      </c>
+      <c r="N29">
+        <v>53.915136</v>
+      </c>
+      <c r="O29">
+        <v>11.86132992</v>
+      </c>
+      <c r="P29">
+        <v>42.05380608</v>
+      </c>
+      <c r="Q29">
+        <v>64.25380608</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1235539118127801</v>
+      </c>
+      <c r="T29">
+        <v>1.147703181008607</v>
+      </c>
+      <c r="U29">
+        <v>0.048</v>
+      </c>
+      <c r="V29">
+        <v>0.22</v>
+      </c>
+      <c r="W29">
+        <v>0.03744</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>7.837801641220443</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1004724450318227</v>
+      </c>
+      <c r="C30">
+        <v>491.0180251487984</v>
+      </c>
+      <c r="D30">
+        <v>642.7700251487984</v>
+      </c>
+      <c r="E30">
+        <v>-291.248</v>
+      </c>
+      <c r="F30">
+        <v>170.352</v>
+      </c>
+      <c r="G30">
+        <v>18.6</v>
+      </c>
+      <c r="H30">
+        <v>146.8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>84</v>
+      </c>
+      <c r="K30">
+        <v>22.2</v>
+      </c>
+      <c r="L30">
+        <v>61.8</v>
+      </c>
+      <c r="M30">
+        <v>8.432424000000003</v>
+      </c>
+      <c r="N30">
+        <v>53.36757599999999</v>
+      </c>
+      <c r="O30">
+        <v>11.74086672</v>
+      </c>
+      <c r="P30">
+        <v>41.62670927999999</v>
+      </c>
+      <c r="Q30">
+        <v>63.82670927999999</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1245300625441982</v>
+      </c>
+      <c r="T30">
+        <v>1.160921819247596</v>
+      </c>
+      <c r="U30">
+        <v>0.0495</v>
+      </c>
+      <c r="V30">
+        <v>0.22</v>
+      </c>
+      <c r="W30">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>7.328853482699634</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1003258344403158</v>
+      </c>
+      <c r="C31">
+        <v>486.0439043506907</v>
+      </c>
+      <c r="D31">
+        <v>643.8799043506907</v>
+      </c>
+      <c r="E31">
+        <v>-285.164</v>
+      </c>
+      <c r="F31">
+        <v>176.436</v>
+      </c>
+      <c r="G31">
+        <v>18.6</v>
+      </c>
+      <c r="H31">
+        <v>146.8</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>84</v>
+      </c>
+      <c r="K31">
+        <v>22.2</v>
+      </c>
+      <c r="L31">
+        <v>61.8</v>
+      </c>
+      <c r="M31">
+        <v>8.733582</v>
+      </c>
+      <c r="N31">
+        <v>53.066418</v>
+      </c>
+      <c r="O31">
+        <v>11.67461196</v>
+      </c>
+      <c r="P31">
+        <v>41.39180604</v>
+      </c>
+      <c r="Q31">
+        <v>63.59180603999999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1255337104793181</v>
+      </c>
+      <c r="T31">
+        <v>1.174512813493318</v>
+      </c>
+      <c r="U31">
+        <v>0.0495</v>
+      </c>
+      <c r="V31">
+        <v>0.22</v>
+      </c>
+      <c r="W31">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>7.076134397089304</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.100179223848809</v>
+      </c>
+      <c r="C32">
+        <v>481.0736230674744</v>
+      </c>
+      <c r="D32">
+        <v>644.9936230674743</v>
+      </c>
+      <c r="E32">
+        <v>-279.08</v>
+      </c>
+      <c r="F32">
+        <v>182.52</v>
+      </c>
+      <c r="G32">
+        <v>18.6</v>
+      </c>
+      <c r="H32">
+        <v>146.8</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>84</v>
+      </c>
+      <c r="K32">
+        <v>22.2</v>
+      </c>
+      <c r="L32">
+        <v>61.8</v>
+      </c>
+      <c r="M32">
+        <v>9.034740000000001</v>
+      </c>
+      <c r="N32">
+        <v>52.76526</v>
+      </c>
+      <c r="O32">
+        <v>11.6083572</v>
+      </c>
+      <c r="P32">
+        <v>41.1569028</v>
+      </c>
+      <c r="Q32">
+        <v>63.3569028</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1265660340697272</v>
+      </c>
+      <c r="T32">
+        <v>1.188492121860345</v>
+      </c>
+      <c r="U32">
+        <v>0.0495</v>
+      </c>
+      <c r="V32">
+        <v>0.22</v>
+      </c>
+      <c r="W32">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>6.840263250519659</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1000326132573022</v>
+      </c>
+      <c r="C33">
+        <v>476.1072012572914</v>
+      </c>
+      <c r="D33">
+        <v>646.1112012572914</v>
+      </c>
+      <c r="E33">
+        <v>-272.996</v>
+      </c>
+      <c r="F33">
+        <v>188.604</v>
+      </c>
+      <c r="G33">
+        <v>18.6</v>
+      </c>
+      <c r="H33">
+        <v>146.8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>84</v>
+      </c>
+      <c r="K33">
+        <v>22.2</v>
+      </c>
+      <c r="L33">
+        <v>61.8</v>
+      </c>
+      <c r="M33">
+        <v>9.335898</v>
+      </c>
+      <c r="N33">
+        <v>52.464102</v>
+      </c>
+      <c r="O33">
+        <v>11.54210244</v>
+      </c>
+      <c r="P33">
+        <v>40.92199956</v>
+      </c>
+      <c r="Q33">
+        <v>63.12199955999999</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1276282800830466</v>
+      </c>
+      <c r="T33">
+        <v>1.202876627571345</v>
+      </c>
+      <c r="U33">
+        <v>0.0495</v>
+      </c>
+      <c r="V33">
+        <v>0.22</v>
+      </c>
+      <c r="W33">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>6.619609597277091</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.09988600266579534</v>
+      </c>
+      <c r="C34">
+        <v>471.1446590168495</v>
+      </c>
+      <c r="D34">
+        <v>647.2326590168495</v>
+      </c>
+      <c r="E34">
+        <v>-266.912</v>
+      </c>
+      <c r="F34">
+        <v>194.688</v>
+      </c>
+      <c r="G34">
+        <v>18.6</v>
+      </c>
+      <c r="H34">
+        <v>146.8</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>84</v>
+      </c>
+      <c r="K34">
+        <v>22.2</v>
+      </c>
+      <c r="L34">
+        <v>61.8</v>
+      </c>
+      <c r="M34">
+        <v>9.637056000000003</v>
+      </c>
+      <c r="N34">
+        <v>52.162944</v>
+      </c>
+      <c r="O34">
+        <v>11.47584768</v>
+      </c>
+      <c r="P34">
+        <v>40.68709631999999</v>
+      </c>
+      <c r="Q34">
+        <v>62.88709632</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1287217686261696</v>
+      </c>
+      <c r="T34">
+        <v>1.217684206979726</v>
+      </c>
+      <c r="U34">
+        <v>0.0495</v>
+      </c>
+      <c r="V34">
+        <v>0.22</v>
+      </c>
+      <c r="W34">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>6.41274679736218</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.0997393920742885</v>
+      </c>
+      <c r="C35">
+        <v>466.1860165826267</v>
+      </c>
+      <c r="D35">
+        <v>648.3580165826268</v>
+      </c>
+      <c r="E35">
+        <v>-260.828</v>
+      </c>
+      <c r="F35">
+        <v>200.772</v>
+      </c>
+      <c r="G35">
+        <v>18.6</v>
+      </c>
+      <c r="H35">
+        <v>146.8</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>84</v>
+      </c>
+      <c r="K35">
+        <v>22.2</v>
+      </c>
+      <c r="L35">
+        <v>61.8</v>
+      </c>
+      <c r="M35">
+        <v>9.938214000000002</v>
+      </c>
+      <c r="N35">
+        <v>51.861786</v>
+      </c>
+      <c r="O35">
+        <v>11.40959292</v>
+      </c>
+      <c r="P35">
+        <v>40.45219307999999</v>
+      </c>
+      <c r="Q35">
+        <v>62.65219307999999</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1298478986183411</v>
+      </c>
+      <c r="T35">
+        <v>1.232933803683881</v>
+      </c>
+      <c r="U35">
+        <v>0.0495</v>
+      </c>
+      <c r="V35">
+        <v>0.22</v>
+      </c>
+      <c r="W35">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>6.218421136836054</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.09996406148278167</v>
+      </c>
+      <c r="C36">
+        <v>458.379085236009</v>
+      </c>
+      <c r="D36">
+        <v>646.635085236009</v>
+      </c>
+      <c r="E36">
+        <v>-254.744</v>
+      </c>
+      <c r="F36">
+        <v>206.8560000000001</v>
+      </c>
+      <c r="G36">
+        <v>18.6</v>
+      </c>
+      <c r="H36">
+        <v>146.8</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>84</v>
+      </c>
+      <c r="K36">
+        <v>22.2</v>
+      </c>
+      <c r="L36">
+        <v>61.8</v>
+      </c>
+      <c r="M36">
+        <v>10.5289704</v>
+      </c>
+      <c r="N36">
+        <v>51.27102959999999</v>
+      </c>
+      <c r="O36">
+        <v>11.279626512</v>
+      </c>
+      <c r="P36">
+        <v>39.99140308799999</v>
+      </c>
+      <c r="Q36">
+        <v>62.19140308799999</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1310081537617904</v>
+      </c>
+      <c r="T36">
+        <v>1.24864550937907</v>
+      </c>
+      <c r="U36">
+        <v>0.0509</v>
+      </c>
+      <c r="V36">
+        <v>0.22</v>
+      </c>
+      <c r="W36">
+        <v>0.039702</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>5.869519777546338</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.09982837089127485</v>
+      </c>
+      <c r="C37">
+        <v>453.3345642429434</v>
+      </c>
+      <c r="D37">
+        <v>647.6745642429435</v>
+      </c>
+      <c r="E37">
+        <v>-248.66</v>
+      </c>
+      <c r="F37">
+        <v>212.9400000000001</v>
+      </c>
+      <c r="G37">
+        <v>18.6</v>
+      </c>
+      <c r="H37">
+        <v>146.8</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>84</v>
+      </c>
+      <c r="K37">
+        <v>22.2</v>
+      </c>
+      <c r="L37">
+        <v>61.8</v>
+      </c>
+      <c r="M37">
+        <v>10.838646</v>
+      </c>
+      <c r="N37">
+        <v>50.96135399999999</v>
+      </c>
+      <c r="O37">
+        <v>11.21149788</v>
+      </c>
+      <c r="P37">
+        <v>39.74985612</v>
+      </c>
+      <c r="Q37">
+        <v>61.94985611999999</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1322041090634998</v>
+      </c>
+      <c r="T37">
+        <v>1.264840652172573</v>
+      </c>
+      <c r="U37">
+        <v>0.0509</v>
+      </c>
+      <c r="V37">
+        <v>0.22</v>
+      </c>
+      <c r="W37">
+        <v>0.039702</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>5.701819212473586</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.09969268029976802</v>
+      </c>
+      <c r="C38">
+        <v>448.2933905979557</v>
+      </c>
+      <c r="D38">
+        <v>648.7173905979557</v>
+      </c>
+      <c r="E38">
+        <v>-242.576</v>
+      </c>
+      <c r="F38">
+        <v>219.024</v>
+      </c>
+      <c r="G38">
+        <v>18.6</v>
+      </c>
+      <c r="H38">
+        <v>146.8</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>84</v>
+      </c>
+      <c r="K38">
+        <v>22.2</v>
+      </c>
+      <c r="L38">
+        <v>61.8</v>
+      </c>
+      <c r="M38">
+        <v>11.1483216</v>
+      </c>
+      <c r="N38">
+        <v>50.65167839999999</v>
+      </c>
+      <c r="O38">
+        <v>11.143369248</v>
+      </c>
+      <c r="P38">
+        <v>39.508309152</v>
+      </c>
+      <c r="Q38">
+        <v>61.708309152</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1334374379683875</v>
+      </c>
+      <c r="T38">
+        <v>1.281541893178373</v>
+      </c>
+      <c r="U38">
+        <v>0.0509</v>
+      </c>
+      <c r="V38">
+        <v>0.22</v>
+      </c>
+      <c r="W38">
+        <v>0.039702</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>5.543435345460431</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.09955698970826118</v>
+      </c>
+      <c r="C39">
+        <v>443.255580495903</v>
+      </c>
+      <c r="D39">
+        <v>649.7635804959031</v>
+      </c>
+      <c r="E39">
+        <v>-236.492</v>
+      </c>
+      <c r="F39">
+        <v>225.108</v>
+      </c>
+      <c r="G39">
+        <v>18.6</v>
+      </c>
+      <c r="H39">
+        <v>146.8</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>84</v>
+      </c>
+      <c r="K39">
+        <v>22.2</v>
+      </c>
+      <c r="L39">
+        <v>61.8</v>
+      </c>
+      <c r="M39">
+        <v>11.4579972</v>
+      </c>
+      <c r="N39">
+        <v>50.3420028</v>
+      </c>
+      <c r="O39">
+        <v>11.075240616</v>
+      </c>
+      <c r="P39">
+        <v>39.266762184</v>
+      </c>
+      <c r="Q39">
+        <v>61.466762184</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1347099201718432</v>
+      </c>
+      <c r="T39">
+        <v>1.298773332311341</v>
+      </c>
+      <c r="U39">
+        <v>0.0509</v>
+      </c>
+      <c r="V39">
+        <v>0.22</v>
+      </c>
+      <c r="W39">
+        <v>0.039702</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>5.393612768556095</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.09942129911675435</v>
+      </c>
+      <c r="C40">
+        <v>438.221150236281</v>
+      </c>
+      <c r="D40">
+        <v>650.813150236281</v>
+      </c>
+      <c r="E40">
+        <v>-230.408</v>
+      </c>
+      <c r="F40">
+        <v>231.192</v>
+      </c>
+      <c r="G40">
+        <v>18.6</v>
+      </c>
+      <c r="H40">
+        <v>146.8</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>84</v>
+      </c>
+      <c r="K40">
+        <v>22.2</v>
+      </c>
+      <c r="L40">
+        <v>61.8</v>
+      </c>
+      <c r="M40">
+        <v>11.7676728</v>
+      </c>
+      <c r="N40">
+        <v>50.0323272</v>
+      </c>
+      <c r="O40">
+        <v>11.007111984</v>
+      </c>
+      <c r="P40">
+        <v>39.025215216</v>
+      </c>
+      <c r="Q40">
+        <v>61.225215216</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1360234501883135</v>
+      </c>
+      <c r="T40">
+        <v>1.316560624319566</v>
+      </c>
+      <c r="U40">
+        <v>0.0509</v>
+      </c>
+      <c r="V40">
+        <v>0.22</v>
+      </c>
+      <c r="W40">
+        <v>0.039702</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>5.251675590436198</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.09928560852524754</v>
+      </c>
+      <c r="C41">
+        <v>433.1901162240699</v>
+      </c>
+      <c r="D41">
+        <v>651.86611622407</v>
+      </c>
+      <c r="E41">
+        <v>-224.324</v>
+      </c>
+      <c r="F41">
+        <v>237.276</v>
+      </c>
+      <c r="G41">
+        <v>18.6</v>
+      </c>
+      <c r="H41">
+        <v>146.8</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>84</v>
+      </c>
+      <c r="K41">
+        <v>22.2</v>
+      </c>
+      <c r="L41">
+        <v>61.8</v>
+      </c>
+      <c r="M41">
+        <v>12.0773484</v>
+      </c>
+      <c r="N41">
+        <v>49.72265159999999</v>
+      </c>
+      <c r="O41">
+        <v>10.938983352</v>
+      </c>
+      <c r="P41">
+        <v>38.783668248</v>
+      </c>
+      <c r="Q41">
+        <v>60.983668248</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1373800467627009</v>
+      </c>
+      <c r="T41">
+        <v>1.3349311062297</v>
+      </c>
+      <c r="U41">
+        <v>0.0509</v>
+      </c>
+      <c r="V41">
+        <v>0.22</v>
+      </c>
+      <c r="W41">
+        <v>0.039702</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>5.117017241963475</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.09914991793374069</v>
+      </c>
+      <c r="C42">
+        <v>428.162494970592</v>
+      </c>
+      <c r="D42">
+        <v>652.922494970592</v>
+      </c>
+      <c r="E42">
+        <v>-218.24</v>
+      </c>
+      <c r="F42">
+        <v>243.36</v>
+      </c>
+      <c r="G42">
+        <v>18.6</v>
+      </c>
+      <c r="H42">
+        <v>146.8</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>84</v>
+      </c>
+      <c r="K42">
+        <v>22.2</v>
+      </c>
+      <c r="L42">
+        <v>61.8</v>
+      </c>
+      <c r="M42">
+        <v>12.387024</v>
+      </c>
+      <c r="N42">
+        <v>49.41297599999999</v>
+      </c>
+      <c r="O42">
+        <v>10.87085472</v>
+      </c>
+      <c r="P42">
+        <v>38.54212128</v>
+      </c>
+      <c r="Q42">
+        <v>60.74212127999999</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1387818632229011</v>
+      </c>
+      <c r="T42">
+        <v>1.353913937536839</v>
+      </c>
+      <c r="U42">
+        <v>0.0509</v>
+      </c>
+      <c r="V42">
+        <v>0.22</v>
+      </c>
+      <c r="W42">
+        <v>0.039702</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>4.989091810914388</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.09901422734223386</v>
+      </c>
+      <c r="C43">
+        <v>423.1383030943706</v>
+      </c>
+      <c r="D43">
+        <v>653.9823030943706</v>
+      </c>
+      <c r="E43">
+        <v>-212.156</v>
+      </c>
+      <c r="F43">
+        <v>249.444</v>
+      </c>
+      <c r="G43">
+        <v>18.6</v>
+      </c>
+      <c r="H43">
+        <v>146.8</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>84</v>
+      </c>
+      <c r="K43">
+        <v>22.2</v>
+      </c>
+      <c r="L43">
+        <v>61.8</v>
+      </c>
+      <c r="M43">
+        <v>12.6966996</v>
+      </c>
+      <c r="N43">
+        <v>49.10330039999999</v>
+      </c>
+      <c r="O43">
+        <v>10.802726088</v>
+      </c>
+      <c r="P43">
+        <v>38.30057431199999</v>
+      </c>
+      <c r="Q43">
+        <v>60.500574312</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1402311988851422</v>
+      </c>
+      <c r="T43">
+        <v>1.373540254650999</v>
+      </c>
+      <c r="U43">
+        <v>0.0509</v>
+      </c>
+      <c r="V43">
+        <v>0.22</v>
+      </c>
+      <c r="W43">
+        <v>0.039702</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>4.867406644794524</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.09887853675072704</v>
+      </c>
+      <c r="C44">
+        <v>418.1175573220047</v>
+      </c>
+      <c r="D44">
+        <v>655.0455573220047</v>
+      </c>
+      <c r="E44">
+        <v>-206.072</v>
+      </c>
+      <c r="F44">
+        <v>255.528</v>
+      </c>
+      <c r="G44">
+        <v>18.6</v>
+      </c>
+      <c r="H44">
+        <v>146.8</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>84</v>
+      </c>
+      <c r="K44">
+        <v>22.2</v>
+      </c>
+      <c r="L44">
+        <v>61.8</v>
+      </c>
+      <c r="M44">
+        <v>13.0063752</v>
+      </c>
+      <c r="N44">
+        <v>48.7936248</v>
+      </c>
+      <c r="O44">
+        <v>10.734597456</v>
+      </c>
+      <c r="P44">
+        <v>38.059027344</v>
+      </c>
+      <c r="Q44">
+        <v>60.259027344</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1417305116391845</v>
+      </c>
+      <c r="T44">
+        <v>1.39384334132082</v>
+      </c>
+      <c r="U44">
+        <v>0.0509</v>
+      </c>
+      <c r="V44">
+        <v>0.22</v>
+      </c>
+      <c r="W44">
+        <v>0.039702</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>4.751516010394656</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.09874284615922022</v>
+      </c>
+      <c r="C45">
+        <v>413.1002744890479</v>
+      </c>
+      <c r="D45">
+        <v>656.1122744890479</v>
+      </c>
+      <c r="E45">
+        <v>-199.988</v>
+      </c>
+      <c r="F45">
+        <v>261.612</v>
+      </c>
+      <c r="G45">
+        <v>18.6</v>
+      </c>
+      <c r="H45">
+        <v>146.8</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>84</v>
+      </c>
+      <c r="K45">
+        <v>22.2</v>
+      </c>
+      <c r="L45">
+        <v>61.8</v>
+      </c>
+      <c r="M45">
+        <v>13.3160508</v>
+      </c>
+      <c r="N45">
+        <v>48.4839492</v>
+      </c>
+      <c r="O45">
+        <v>10.666468824</v>
+      </c>
+      <c r="P45">
+        <v>37.817480376</v>
+      </c>
+      <c r="Q45">
+        <v>60.01748037599999</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1432824318582811</v>
+      </c>
+      <c r="T45">
+        <v>1.414858816996599</v>
+      </c>
+      <c r="U45">
+        <v>0.0509</v>
+      </c>
+      <c r="V45">
+        <v>0.22</v>
+      </c>
+      <c r="W45">
+        <v>0.039702</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>4.641015638059896</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.09860715556771341</v>
+      </c>
+      <c r="C46">
+        <v>408.0864715408962</v>
+      </c>
+      <c r="D46">
+        <v>657.1824715408962</v>
+      </c>
+      <c r="E46">
+        <v>-193.904</v>
+      </c>
+      <c r="F46">
+        <v>267.696</v>
+      </c>
+      <c r="G46">
+        <v>18.6</v>
+      </c>
+      <c r="H46">
+        <v>146.8</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>84</v>
+      </c>
+      <c r="K46">
+        <v>22.2</v>
+      </c>
+      <c r="L46">
+        <v>61.8</v>
+      </c>
+      <c r="M46">
+        <v>13.6257264</v>
+      </c>
+      <c r="N46">
+        <v>48.17427359999999</v>
+      </c>
+      <c r="O46">
+        <v>10.598340192</v>
+      </c>
+      <c r="P46">
+        <v>37.575933408</v>
+      </c>
+      <c r="Q46">
+        <v>59.775933408</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1448897777994882</v>
+      </c>
+      <c r="T46">
+        <v>1.436624845375085</v>
+      </c>
+      <c r="U46">
+        <v>0.0509</v>
+      </c>
+      <c r="V46">
+        <v>0.22</v>
+      </c>
+      <c r="W46">
+        <v>0.039702</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>4.53553800992217</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.09938406497620657</v>
+      </c>
+      <c r="C47">
+        <v>395.9217502828733</v>
+      </c>
+      <c r="D47">
+        <v>651.1017502828734</v>
+      </c>
+      <c r="E47">
+        <v>-187.82</v>
+      </c>
+      <c r="F47">
+        <v>273.78</v>
+      </c>
+      <c r="G47">
+        <v>18.6</v>
+      </c>
+      <c r="H47">
+        <v>146.8</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>84</v>
+      </c>
+      <c r="K47">
+        <v>22.2</v>
+      </c>
+      <c r="L47">
+        <v>61.8</v>
+      </c>
+      <c r="M47">
+        <v>14.64723</v>
+      </c>
+      <c r="N47">
+        <v>47.15277</v>
+      </c>
+      <c r="O47">
+        <v>10.3736094</v>
+      </c>
+      <c r="P47">
+        <v>36.7791606</v>
+      </c>
+      <c r="Q47">
+        <v>58.9791606</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1465555726840119</v>
+      </c>
+      <c r="T47">
+        <v>1.459182365694607</v>
+      </c>
+      <c r="U47">
+        <v>0.0535</v>
+      </c>
+      <c r="V47">
+        <v>0.22</v>
+      </c>
+      <c r="W47">
+        <v>0.04173</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>4.219227799385958</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.09926865438469971</v>
+      </c>
+      <c r="C48">
+        <v>390.7339207361111</v>
+      </c>
+      <c r="D48">
+        <v>651.9979207361112</v>
+      </c>
+      <c r="E48">
+        <v>-181.736</v>
+      </c>
+      <c r="F48">
+        <v>279.864</v>
+      </c>
+      <c r="G48">
+        <v>18.6</v>
+      </c>
+      <c r="H48">
+        <v>146.8</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>84</v>
+      </c>
+      <c r="K48">
+        <v>22.2</v>
+      </c>
+      <c r="L48">
+        <v>61.8</v>
+      </c>
+      <c r="M48">
+        <v>14.972724</v>
+      </c>
+      <c r="N48">
+        <v>46.827276</v>
+      </c>
+      <c r="O48">
+        <v>10.30200072</v>
+      </c>
+      <c r="P48">
+        <v>36.52527528</v>
+      </c>
+      <c r="Q48">
+        <v>58.72527528000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1482830636753698</v>
+      </c>
+      <c r="T48">
+        <v>1.482575349729667</v>
+      </c>
+      <c r="U48">
+        <v>0.0535</v>
+      </c>
+      <c r="V48">
+        <v>0.22</v>
+      </c>
+      <c r="W48">
+        <v>0.04173</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>4.127505455921046</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.0991532437931929</v>
+      </c>
+      <c r="C49">
+        <v>385.5485615510501</v>
+      </c>
+      <c r="D49">
+        <v>652.8965615510501</v>
+      </c>
+      <c r="E49">
+        <v>-175.652</v>
+      </c>
+      <c r="F49">
+        <v>285.948</v>
+      </c>
+      <c r="G49">
+        <v>18.6</v>
+      </c>
+      <c r="H49">
+        <v>146.8</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>84</v>
+      </c>
+      <c r="K49">
+        <v>22.2</v>
+      </c>
+      <c r="L49">
+        <v>61.8</v>
+      </c>
+      <c r="M49">
+        <v>15.298218</v>
+      </c>
+      <c r="N49">
+        <v>46.50178199999999</v>
+      </c>
+      <c r="O49">
+        <v>10.23039204</v>
+      </c>
+      <c r="P49">
+        <v>36.27138995999999</v>
+      </c>
+      <c r="Q49">
+        <v>58.47138996</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1500757430060243</v>
+      </c>
+      <c r="T49">
+        <v>1.506851087879257</v>
+      </c>
+      <c r="U49">
+        <v>0.0535</v>
+      </c>
+      <c r="V49">
+        <v>0.22</v>
+      </c>
+      <c r="W49">
+        <v>0.04173</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>4.039686190901449</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1000487132016861</v>
+      </c>
+      <c r="C50">
+        <v>372.5562858939115</v>
+      </c>
+      <c r="D50">
+        <v>645.9882858939116</v>
+      </c>
+      <c r="E50">
+        <v>-169.568</v>
+      </c>
+      <c r="F50">
+        <v>292.032</v>
+      </c>
+      <c r="G50">
+        <v>18.6</v>
+      </c>
+      <c r="H50">
+        <v>146.8</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>84</v>
+      </c>
+      <c r="K50">
+        <v>22.2</v>
+      </c>
+      <c r="L50">
+        <v>61.8</v>
+      </c>
+      <c r="M50">
+        <v>16.4121984</v>
+      </c>
+      <c r="N50">
+        <v>45.3878016</v>
+      </c>
+      <c r="O50">
+        <v>9.985316352</v>
+      </c>
+      <c r="P50">
+        <v>35.402485248</v>
+      </c>
+      <c r="Q50">
+        <v>57.60248524799999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1519373715417039</v>
+      </c>
+      <c r="T50">
+        <v>1.53206050826537</v>
+      </c>
+      <c r="U50">
+        <v>0.0562</v>
+      </c>
+      <c r="V50">
+        <v>0.22</v>
+      </c>
+      <c r="W50">
+        <v>0.043836</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>3.765491891689537</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.09995436261017923</v>
+      </c>
+      <c r="C51">
+        <v>367.1932742312626</v>
+      </c>
+      <c r="D51">
+        <v>646.7092742312626</v>
+      </c>
+      <c r="E51">
+        <v>-163.484</v>
+      </c>
+      <c r="F51">
+        <v>298.116</v>
+      </c>
+      <c r="G51">
+        <v>18.6</v>
+      </c>
+      <c r="H51">
+        <v>146.8</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>84</v>
+      </c>
+      <c r="K51">
+        <v>22.2</v>
+      </c>
+      <c r="L51">
+        <v>61.8</v>
+      </c>
+      <c r="M51">
+        <v>16.7541192</v>
+      </c>
+      <c r="N51">
+        <v>45.04588079999999</v>
+      </c>
+      <c r="O51">
+        <v>9.910093775999998</v>
+      </c>
+      <c r="P51">
+        <v>35.135787024</v>
+      </c>
+      <c r="Q51">
+        <v>57.335787024</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1538720051179985</v>
+      </c>
+      <c r="T51">
+        <v>1.558258533372507</v>
+      </c>
+      <c r="U51">
+        <v>0.0562</v>
+      </c>
+      <c r="V51">
+        <v>0.22</v>
+      </c>
+      <c r="W51">
+        <v>0.043836</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>3.68864511838975</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.09986001201867239</v>
+      </c>
+      <c r="C52">
+        <v>361.8318737588432</v>
+      </c>
+      <c r="D52">
+        <v>647.4318737588433</v>
+      </c>
+      <c r="E52">
+        <v>-157.4</v>
+      </c>
+      <c r="F52">
+        <v>304.2</v>
+      </c>
+      <c r="G52">
+        <v>18.6</v>
+      </c>
+      <c r="H52">
+        <v>146.8</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>84</v>
+      </c>
+      <c r="K52">
+        <v>22.2</v>
+      </c>
+      <c r="L52">
+        <v>61.8</v>
+      </c>
+      <c r="M52">
+        <v>17.09604</v>
+      </c>
+      <c r="N52">
+        <v>44.70396</v>
+      </c>
+      <c r="O52">
+        <v>9.834871199999998</v>
+      </c>
+      <c r="P52">
+        <v>34.8690888</v>
+      </c>
+      <c r="Q52">
+        <v>57.0690888</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1558840240373448</v>
+      </c>
+      <c r="T52">
+        <v>1.585504479483929</v>
+      </c>
+      <c r="U52">
+        <v>0.0562</v>
+      </c>
+      <c r="V52">
+        <v>0.22</v>
+      </c>
+      <c r="W52">
+        <v>0.043836</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>3.614872216021956</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.09976566142716556</v>
+      </c>
+      <c r="C53">
+        <v>356.4720898834766</v>
+      </c>
+      <c r="D53">
+        <v>648.1560898834766</v>
+      </c>
+      <c r="E53">
+        <v>-151.316</v>
+      </c>
+      <c r="F53">
+        <v>310.284</v>
+      </c>
+      <c r="G53">
+        <v>18.6</v>
+      </c>
+      <c r="H53">
+        <v>146.8</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>84</v>
+      </c>
+      <c r="K53">
+        <v>22.2</v>
+      </c>
+      <c r="L53">
+        <v>61.8</v>
+      </c>
+      <c r="M53">
+        <v>17.4379608</v>
+      </c>
+      <c r="N53">
+        <v>44.3620392</v>
+      </c>
+      <c r="O53">
+        <v>9.759648624</v>
+      </c>
+      <c r="P53">
+        <v>34.602390576</v>
+      </c>
+      <c r="Q53">
+        <v>56.80239057599999</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1579781661778889</v>
+      </c>
+      <c r="T53">
+        <v>1.613862505028471</v>
+      </c>
+      <c r="U53">
+        <v>0.0562</v>
+      </c>
+      <c r="V53">
+        <v>0.22</v>
+      </c>
+      <c r="W53">
+        <v>0.043836</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>3.543992368648976</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1015776308356587</v>
+      </c>
+      <c r="C54">
+        <v>336.7570459674977</v>
+      </c>
+      <c r="D54">
+        <v>634.5250459674977</v>
+      </c>
+      <c r="E54">
+        <v>-145.232</v>
+      </c>
+      <c r="F54">
+        <v>316.3680000000001</v>
+      </c>
+      <c r="G54">
+        <v>18.6</v>
+      </c>
+      <c r="H54">
+        <v>146.8</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>84</v>
+      </c>
+      <c r="K54">
+        <v>22.2</v>
+      </c>
+      <c r="L54">
+        <v>61.8</v>
+      </c>
+      <c r="M54">
+        <v>19.2668112</v>
+      </c>
+      <c r="N54">
+        <v>42.53318879999999</v>
+      </c>
+      <c r="O54">
+        <v>9.357301535999998</v>
+      </c>
+      <c r="P54">
+        <v>33.175887264</v>
+      </c>
+      <c r="Q54">
+        <v>55.375887264</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1601595642409557</v>
+      </c>
+      <c r="T54">
+        <v>1.643402114970702</v>
+      </c>
+      <c r="U54">
+        <v>0.0609</v>
+      </c>
+      <c r="V54">
+        <v>0.22</v>
+      </c>
+      <c r="W54">
+        <v>0.047502</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>3.207588394284986</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1015199402441519</v>
+      </c>
+      <c r="C55">
+        <v>331.0981970645517</v>
+      </c>
+      <c r="D55">
+        <v>634.9501970645517</v>
+      </c>
+      <c r="E55">
+        <v>-139.148</v>
+      </c>
+      <c r="F55">
+        <v>322.4520000000001</v>
+      </c>
+      <c r="G55">
+        <v>18.6</v>
+      </c>
+      <c r="H55">
+        <v>146.8</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>84</v>
+      </c>
+      <c r="K55">
+        <v>22.2</v>
+      </c>
+      <c r="L55">
+        <v>61.8</v>
+      </c>
+      <c r="M55">
+        <v>19.6373268</v>
+      </c>
+      <c r="N55">
+        <v>42.16267319999999</v>
+      </c>
+      <c r="O55">
+        <v>9.275788103999998</v>
+      </c>
+      <c r="P55">
+        <v>32.88688509599999</v>
+      </c>
+      <c r="Q55">
+        <v>55.08688509599999</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1624337877535147</v>
+      </c>
+      <c r="T55">
+        <v>1.674198729591326</v>
+      </c>
+      <c r="U55">
+        <v>0.0609</v>
+      </c>
+      <c r="V55">
+        <v>0.22</v>
+      </c>
+      <c r="W55">
+        <v>0.047502</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>3.14706785854376</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1014622496526451</v>
+      </c>
+      <c r="C56">
+        <v>325.4399182719518</v>
+      </c>
+      <c r="D56">
+        <v>635.3759182719518</v>
+      </c>
+      <c r="E56">
+        <v>-133.064</v>
+      </c>
+      <c r="F56">
+        <v>328.5360000000001</v>
+      </c>
+      <c r="G56">
+        <v>18.6</v>
+      </c>
+      <c r="H56">
+        <v>146.8</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>84</v>
+      </c>
+      <c r="K56">
+        <v>22.2</v>
+      </c>
+      <c r="L56">
+        <v>61.8</v>
+      </c>
+      <c r="M56">
+        <v>20.0078424</v>
+      </c>
+      <c r="N56">
+        <v>41.7921576</v>
+      </c>
+      <c r="O56">
+        <v>9.194274671999999</v>
+      </c>
+      <c r="P56">
+        <v>32.597882928</v>
+      </c>
+      <c r="Q56">
+        <v>54.79788292799999</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1648068905492284</v>
+      </c>
+      <c r="T56">
+        <v>1.706334327456325</v>
+      </c>
+      <c r="U56">
+        <v>0.0609</v>
+      </c>
+      <c r="V56">
+        <v>0.22</v>
+      </c>
+      <c r="W56">
+        <v>0.047502</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>3.088788824126283</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1014045590611382</v>
+      </c>
+      <c r="C57">
+        <v>319.7822107372099</v>
+      </c>
+      <c r="D57">
+        <v>635.80221073721</v>
+      </c>
+      <c r="E57">
+        <v>-126.98</v>
+      </c>
+      <c r="F57">
+        <v>334.6200000000001</v>
+      </c>
+      <c r="G57">
+        <v>18.6</v>
+      </c>
+      <c r="H57">
+        <v>146.8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>84</v>
+      </c>
+      <c r="K57">
+        <v>22.2</v>
+      </c>
+      <c r="L57">
+        <v>61.8</v>
+      </c>
+      <c r="M57">
+        <v>20.37835800000001</v>
+      </c>
+      <c r="N57">
+        <v>41.42164199999999</v>
+      </c>
+      <c r="O57">
+        <v>9.112761239999998</v>
+      </c>
+      <c r="P57">
+        <v>32.30888075999999</v>
+      </c>
+      <c r="Q57">
+        <v>54.50888076</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1672854645803072</v>
+      </c>
+      <c r="T57">
+        <v>1.739898174115323</v>
+      </c>
+      <c r="U57">
+        <v>0.0609</v>
+      </c>
+      <c r="V57">
+        <v>0.22</v>
+      </c>
+      <c r="W57">
+        <v>0.047502</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>3.032629027323987</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1054091084696314</v>
+      </c>
+      <c r="C58">
+        <v>285.4052457197305</v>
+      </c>
+      <c r="D58">
+        <v>607.5092457197305</v>
+      </c>
+      <c r="E58">
+        <v>-120.896</v>
+      </c>
+      <c r="F58">
+        <v>340.7040000000001</v>
+      </c>
+      <c r="G58">
+        <v>18.6</v>
+      </c>
+      <c r="H58">
+        <v>146.8</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>84</v>
+      </c>
+      <c r="K58">
+        <v>22.2</v>
+      </c>
+      <c r="L58">
+        <v>61.8</v>
+      </c>
+      <c r="M58">
+        <v>23.91742080000001</v>
+      </c>
+      <c r="N58">
+        <v>37.8825792</v>
+      </c>
+      <c r="O58">
+        <v>8.334167423999999</v>
+      </c>
+      <c r="P58">
+        <v>29.54841177599999</v>
+      </c>
+      <c r="Q58">
+        <v>51.748411776</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1698767010673441</v>
+      </c>
+      <c r="T58">
+        <v>1.774987650167913</v>
+      </c>
+      <c r="U58">
+        <v>0.0702</v>
+      </c>
+      <c r="V58">
+        <v>0.22</v>
+      </c>
+      <c r="W58">
+        <v>0.054756</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>2.583890650951794</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1054239578781246</v>
+      </c>
+      <c r="C59">
+        <v>279.2210167741487</v>
+      </c>
+      <c r="D59">
+        <v>607.4090167741488</v>
+      </c>
+      <c r="E59">
+        <v>-114.812</v>
+      </c>
+      <c r="F59">
+        <v>346.7880000000001</v>
+      </c>
+      <c r="G59">
+        <v>18.6</v>
+      </c>
+      <c r="H59">
+        <v>146.8</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>84</v>
+      </c>
+      <c r="K59">
+        <v>22.2</v>
+      </c>
+      <c r="L59">
+        <v>61.8</v>
+      </c>
+      <c r="M59">
+        <v>24.3445176</v>
+      </c>
+      <c r="N59">
+        <v>37.45548239999999</v>
+      </c>
+      <c r="O59">
+        <v>8.240206127999999</v>
+      </c>
+      <c r="P59">
+        <v>29.215276272</v>
+      </c>
+      <c r="Q59">
+        <v>51.415276272</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1725884601816851</v>
+      </c>
+      <c r="T59">
+        <v>1.811709194874111</v>
+      </c>
+      <c r="U59">
+        <v>0.0702</v>
+      </c>
+      <c r="V59">
+        <v>0.22</v>
+      </c>
+      <c r="W59">
+        <v>0.054756</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>2.538559236022816</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1075650872866177</v>
+      </c>
+      <c r="C60">
+        <v>259.0231875747878</v>
+      </c>
+      <c r="D60">
+        <v>593.2951875747877</v>
+      </c>
+      <c r="E60">
+        <v>-108.728</v>
+      </c>
+      <c r="F60">
+        <v>352.872</v>
+      </c>
+      <c r="G60">
+        <v>18.6</v>
+      </c>
+      <c r="H60">
+        <v>146.8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>84</v>
+      </c>
+      <c r="K60">
+        <v>22.2</v>
+      </c>
+      <c r="L60">
+        <v>61.8</v>
+      </c>
+      <c r="M60">
+        <v>26.4301128</v>
+      </c>
+      <c r="N60">
+        <v>35.36988719999999</v>
+      </c>
+      <c r="O60">
+        <v>7.781375183999999</v>
+      </c>
+      <c r="P60">
+        <v>27.588512016</v>
+      </c>
+      <c r="Q60">
+        <v>49.788512016</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1754293506824232</v>
+      </c>
+      <c r="T60">
+        <v>1.850179384566319</v>
+      </c>
+      <c r="U60">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V60">
+        <v>0.22</v>
+      </c>
+      <c r="W60">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>2.338242007048869</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1076165966951109</v>
+      </c>
+      <c r="C61">
+        <v>252.6077243170905</v>
+      </c>
+      <c r="D61">
+        <v>592.9637243170905</v>
+      </c>
+      <c r="E61">
+        <v>-102.644</v>
+      </c>
+      <c r="F61">
+        <v>358.956</v>
+      </c>
+      <c r="G61">
+        <v>18.6</v>
+      </c>
+      <c r="H61">
+        <v>146.8</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>84</v>
+      </c>
+      <c r="K61">
+        <v>22.2</v>
+      </c>
+      <c r="L61">
+        <v>61.8</v>
+      </c>
+      <c r="M61">
+        <v>26.8858044</v>
+      </c>
+      <c r="N61">
+        <v>34.9141956</v>
+      </c>
+      <c r="O61">
+        <v>7.681123031999999</v>
+      </c>
+      <c r="P61">
+        <v>27.233072568</v>
+      </c>
+      <c r="Q61">
+        <v>49.433072568</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1784088212075876</v>
+      </c>
+      <c r="T61">
+        <v>1.890526168877658</v>
+      </c>
+      <c r="U61">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V61">
+        <v>0.22</v>
+      </c>
+      <c r="W61">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>2.298610786590413</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1076681061036041</v>
+      </c>
+      <c r="C62">
+        <v>246.1926312176099</v>
+      </c>
+      <c r="D62">
+        <v>592.6326312176099</v>
+      </c>
+      <c r="E62">
+        <v>-96.56</v>
+      </c>
+      <c r="F62">
+        <v>365.04</v>
+      </c>
+      <c r="G62">
+        <v>18.6</v>
+      </c>
+      <c r="H62">
+        <v>146.8</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>84</v>
+      </c>
+      <c r="K62">
+        <v>22.2</v>
+      </c>
+      <c r="L62">
+        <v>61.8</v>
+      </c>
+      <c r="M62">
+        <v>27.341496</v>
+      </c>
+      <c r="N62">
+        <v>34.458504</v>
+      </c>
+      <c r="O62">
+        <v>7.58087088</v>
+      </c>
+      <c r="P62">
+        <v>26.87763312</v>
+      </c>
+      <c r="Q62">
+        <v>49.07763312</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1815372652590102</v>
+      </c>
+      <c r="T62">
+        <v>1.932890292404566</v>
+      </c>
+      <c r="U62">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V62">
+        <v>0.22</v>
+      </c>
+      <c r="W62">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>2.260300606813907</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1077196155120972</v>
+      </c>
+      <c r="C63">
+        <v>239.7779076566362</v>
+      </c>
+      <c r="D63">
+        <v>592.3019076566362</v>
+      </c>
+      <c r="E63">
+        <v>-90.476</v>
+      </c>
+      <c r="F63">
+        <v>371.124</v>
+      </c>
+      <c r="G63">
+        <v>18.6</v>
+      </c>
+      <c r="H63">
+        <v>146.8</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>84</v>
+      </c>
+      <c r="K63">
+        <v>22.2</v>
+      </c>
+      <c r="L63">
+        <v>61.8</v>
+      </c>
+      <c r="M63">
+        <v>27.7971876</v>
+      </c>
+      <c r="N63">
+        <v>34.0028124</v>
+      </c>
+      <c r="O63">
+        <v>7.480618728</v>
+      </c>
+      <c r="P63">
+        <v>26.522193672</v>
+      </c>
+      <c r="Q63">
+        <v>48.722193672</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1848261423387109</v>
+      </c>
+      <c r="T63">
+        <v>1.977426935086698</v>
+      </c>
+      <c r="U63">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V63">
+        <v>0.22</v>
+      </c>
+      <c r="W63">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>2.223246498505482</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1077711249205904</v>
+      </c>
+      <c r="C64">
+        <v>233.3635530158427</v>
+      </c>
+      <c r="D64">
+        <v>591.9715530158427</v>
+      </c>
+      <c r="E64">
+        <v>-84.392</v>
+      </c>
+      <c r="F64">
+        <v>377.208</v>
+      </c>
+      <c r="G64">
+        <v>18.6</v>
+      </c>
+      <c r="H64">
+        <v>146.8</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>84</v>
+      </c>
+      <c r="K64">
+        <v>22.2</v>
+      </c>
+      <c r="L64">
+        <v>61.8</v>
+      </c>
+      <c r="M64">
+        <v>28.2528792</v>
+      </c>
+      <c r="N64">
+        <v>33.5471208</v>
+      </c>
+      <c r="O64">
+        <v>7.380366576</v>
+      </c>
+      <c r="P64">
+        <v>26.166754224</v>
+      </c>
+      <c r="Q64">
+        <v>48.366754224</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1882881182120801</v>
+      </c>
+      <c r="T64">
+        <v>2.024307611594207</v>
+      </c>
+      <c r="U64">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V64">
+        <v>0.22</v>
+      </c>
+      <c r="W64">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>2.187387684013458</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1078226343290836</v>
+      </c>
+      <c r="C65">
+        <v>226.9495666782806</v>
+      </c>
+      <c r="D65">
+        <v>591.6415666782807</v>
+      </c>
+      <c r="E65">
+        <v>-78.30799999999994</v>
+      </c>
+      <c r="F65">
+        <v>383.2920000000001</v>
+      </c>
+      <c r="G65">
+        <v>18.6</v>
+      </c>
+      <c r="H65">
+        <v>146.8</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>84</v>
+      </c>
+      <c r="K65">
+        <v>22.2</v>
+      </c>
+      <c r="L65">
+        <v>61.8</v>
+      </c>
+      <c r="M65">
+        <v>28.7085708</v>
+      </c>
+      <c r="N65">
+        <v>33.09142919999999</v>
+      </c>
+      <c r="O65">
+        <v>7.280114423999999</v>
+      </c>
+      <c r="P65">
+        <v>25.811314776</v>
+      </c>
+      <c r="Q65">
+        <v>48.01131477599999</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1919372279164422</v>
+      </c>
+      <c r="T65">
+        <v>2.073722378723743</v>
+      </c>
+      <c r="U65">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V65">
+        <v>0.22</v>
+      </c>
+      <c r="W65">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>2.152667244584673</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1078741437375768</v>
+      </c>
+      <c r="C66">
+        <v>220.5359480283769</v>
+      </c>
+      <c r="D66">
+        <v>591.3119480283769</v>
+      </c>
+      <c r="E66">
+        <v>-72.22399999999993</v>
+      </c>
+      <c r="F66">
+        <v>389.3760000000001</v>
+      </c>
+      <c r="G66">
+        <v>18.6</v>
+      </c>
+      <c r="H66">
+        <v>146.8</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>84</v>
+      </c>
+      <c r="K66">
+        <v>22.2</v>
+      </c>
+      <c r="L66">
+        <v>61.8</v>
+      </c>
+      <c r="M66">
+        <v>29.16426240000001</v>
+      </c>
+      <c r="N66">
+        <v>32.63573759999999</v>
+      </c>
+      <c r="O66">
+        <v>7.179862271999998</v>
+      </c>
+      <c r="P66">
+        <v>25.45587532799999</v>
+      </c>
+      <c r="Q66">
+        <v>47.65587532799999</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1957890659377133</v>
+      </c>
+      <c r="T66">
+        <v>2.125882410693808</v>
+      </c>
+      <c r="U66">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V66">
+        <v>0.22</v>
+      </c>
+      <c r="W66">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>2.119031818888037</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1079256531460699</v>
+      </c>
+      <c r="C67">
+        <v>214.122696451929</v>
+      </c>
+      <c r="D67">
+        <v>590.9826964519291</v>
+      </c>
+      <c r="E67">
+        <v>-66.13999999999993</v>
+      </c>
+      <c r="F67">
+        <v>395.4600000000001</v>
+      </c>
+      <c r="G67">
+        <v>18.6</v>
+      </c>
+      <c r="H67">
+        <v>146.8</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>84</v>
+      </c>
+      <c r="K67">
+        <v>22.2</v>
+      </c>
+      <c r="L67">
+        <v>61.8</v>
+      </c>
+      <c r="M67">
+        <v>29.619954</v>
+      </c>
+      <c r="N67">
+        <v>32.18004599999999</v>
+      </c>
+      <c r="O67">
+        <v>7.079610119999998</v>
+      </c>
+      <c r="P67">
+        <v>25.10043587999999</v>
+      </c>
+      <c r="Q67">
+        <v>47.30043587999999</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1998610089887712</v>
+      </c>
+      <c r="T67">
+        <v>2.181023015919306</v>
+      </c>
+      <c r="U67">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V67">
+        <v>0.22</v>
+      </c>
+      <c r="W67">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>2.086431329366683</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1079771625545631</v>
+      </c>
+      <c r="C68">
+        <v>207.7098113361014</v>
+      </c>
+      <c r="D68">
+        <v>590.6538113361015</v>
+      </c>
+      <c r="E68">
+        <v>-60.05599999999993</v>
+      </c>
+      <c r="F68">
+        <v>401.5440000000001</v>
+      </c>
+      <c r="G68">
+        <v>18.6</v>
+      </c>
+      <c r="H68">
+        <v>146.8</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>84</v>
+      </c>
+      <c r="K68">
+        <v>22.2</v>
+      </c>
+      <c r="L68">
+        <v>61.8</v>
+      </c>
+      <c r="M68">
+        <v>30.0756456</v>
+      </c>
+      <c r="N68">
+        <v>31.72435439999999</v>
+      </c>
+      <c r="O68">
+        <v>6.979357967999999</v>
+      </c>
+      <c r="P68">
+        <v>24.74499643199999</v>
+      </c>
+      <c r="Q68">
+        <v>46.944996432</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2041724781016562</v>
+      </c>
+      <c r="T68">
+        <v>2.239407186158068</v>
+      </c>
+      <c r="U68">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V68">
+        <v>0.22</v>
+      </c>
+      <c r="W68">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>2.054818733467187</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1080286719630563</v>
+      </c>
+      <c r="C69">
+        <v>201.297292069423</v>
+      </c>
+      <c r="D69">
+        <v>590.3252920694231</v>
+      </c>
+      <c r="E69">
+        <v>-53.97199999999992</v>
+      </c>
+      <c r="F69">
+        <v>407.6280000000001</v>
+      </c>
+      <c r="G69">
+        <v>18.6</v>
+      </c>
+      <c r="H69">
+        <v>146.8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>84</v>
+      </c>
+      <c r="K69">
+        <v>22.2</v>
+      </c>
+      <c r="L69">
+        <v>61.8</v>
+      </c>
+      <c r="M69">
+        <v>30.53133720000001</v>
+      </c>
+      <c r="N69">
+        <v>31.26866279999999</v>
+      </c>
+      <c r="O69">
+        <v>6.879105815999998</v>
+      </c>
+      <c r="P69">
+        <v>24.38955698399999</v>
+      </c>
+      <c r="Q69">
+        <v>46.58955698399999</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2087452483728978</v>
+      </c>
+      <c r="T69">
+        <v>2.301329790956756</v>
+      </c>
+      <c r="U69">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V69">
+        <v>0.22</v>
+      </c>
+      <c r="W69">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>2.024149797146781</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1167257013715495</v>
+      </c>
+      <c r="C70">
+        <v>144.5349992634802</v>
+      </c>
+      <c r="D70">
+        <v>539.6469992634803</v>
+      </c>
+      <c r="E70">
+        <v>-47.88799999999992</v>
+      </c>
+      <c r="F70">
+        <v>413.7120000000001</v>
+      </c>
+      <c r="G70">
+        <v>18.6</v>
+      </c>
+      <c r="H70">
+        <v>146.8</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>84</v>
+      </c>
+      <c r="K70">
+        <v>22.2</v>
+      </c>
+      <c r="L70">
+        <v>61.8</v>
+      </c>
+      <c r="M70">
+        <v>37.73053440000001</v>
+      </c>
+      <c r="N70">
+        <v>24.06946559999999</v>
+      </c>
+      <c r="O70">
+        <v>5.295282431999997</v>
+      </c>
+      <c r="P70">
+        <v>18.77418316799999</v>
+      </c>
+      <c r="Q70">
+        <v>40.97418316799999</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2136038167860921</v>
+      </c>
+      <c r="T70">
+        <v>2.367122558555362</v>
+      </c>
+      <c r="U70">
+        <v>0.0912</v>
+      </c>
+      <c r="V70">
+        <v>0.22</v>
+      </c>
+      <c r="W70">
+        <v>0.071136</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>1.63793068353678</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1169043507800426</v>
+      </c>
+      <c r="C71">
+        <v>137.5010381727101</v>
+      </c>
+      <c r="D71">
+        <v>538.6970381727102</v>
+      </c>
+      <c r="E71">
+        <v>-41.80399999999992</v>
+      </c>
+      <c r="F71">
+        <v>419.7960000000001</v>
+      </c>
+      <c r="G71">
+        <v>18.6</v>
+      </c>
+      <c r="H71">
+        <v>146.8</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>84</v>
+      </c>
+      <c r="K71">
+        <v>22.2</v>
+      </c>
+      <c r="L71">
+        <v>61.8</v>
+      </c>
+      <c r="M71">
+        <v>38.28539520000001</v>
+      </c>
+      <c r="N71">
+        <v>23.51460479999999</v>
+      </c>
+      <c r="O71">
+        <v>5.173213055999997</v>
+      </c>
+      <c r="P71">
+        <v>18.34139174399999</v>
+      </c>
+      <c r="Q71">
+        <v>40.54139174399999</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.218775841225944</v>
+      </c>
+      <c r="T71">
+        <v>2.437160020837748</v>
+      </c>
+      <c r="U71">
+        <v>0.0912</v>
+      </c>
+      <c r="V71">
+        <v>0.22</v>
+      </c>
+      <c r="W71">
+        <v>0.071136</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>1.614192557688421</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1170830001885358</v>
+      </c>
+      <c r="C72">
+        <v>130.4704157099391</v>
+      </c>
+      <c r="D72">
+        <v>537.7504157099391</v>
+      </c>
+      <c r="E72">
+        <v>-35.71999999999991</v>
+      </c>
+      <c r="F72">
+        <v>425.8800000000001</v>
+      </c>
+      <c r="G72">
+        <v>18.6</v>
+      </c>
+      <c r="H72">
+        <v>146.8</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>84</v>
+      </c>
+      <c r="K72">
+        <v>22.2</v>
+      </c>
+      <c r="L72">
+        <v>61.8</v>
+      </c>
+      <c r="M72">
+        <v>38.84025600000001</v>
+      </c>
+      <c r="N72">
+        <v>22.95974399999999</v>
+      </c>
+      <c r="O72">
+        <v>5.051143679999997</v>
+      </c>
+      <c r="P72">
+        <v>17.90860031999999</v>
+      </c>
+      <c r="Q72">
+        <v>40.10860031999999</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2242926672951193</v>
+      </c>
+      <c r="T72">
+        <v>2.511866647272293</v>
+      </c>
+      <c r="U72">
+        <v>0.0912</v>
+      </c>
+      <c r="V72">
+        <v>0.22</v>
+      </c>
+      <c r="W72">
+        <v>0.071136</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>1.591132664007157</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1172616495970289</v>
+      </c>
+      <c r="C73">
+        <v>123.4431143056827</v>
+      </c>
+      <c r="D73">
+        <v>536.8071143056827</v>
+      </c>
+      <c r="E73">
+        <v>-29.63599999999997</v>
+      </c>
+      <c r="F73">
+        <v>431.9640000000001</v>
+      </c>
+      <c r="G73">
+        <v>18.6</v>
+      </c>
+      <c r="H73">
+        <v>146.8</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>84</v>
+      </c>
+      <c r="K73">
+        <v>22.2</v>
+      </c>
+      <c r="L73">
+        <v>61.8</v>
+      </c>
+      <c r="M73">
+        <v>39.3951168</v>
+      </c>
+      <c r="N73">
+        <v>22.40488319999999</v>
+      </c>
+      <c r="O73">
+        <v>4.929074303999998</v>
+      </c>
+      <c r="P73">
+        <v>17.475808896</v>
+      </c>
+      <c r="Q73">
+        <v>39.67580889599999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.230189964127686</v>
+      </c>
+      <c r="T73">
+        <v>2.591725454840255</v>
+      </c>
+      <c r="U73">
+        <v>0.0912</v>
+      </c>
+      <c r="V73">
+        <v>0.22</v>
+      </c>
+      <c r="W73">
+        <v>0.071136</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>1.568722344795789</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1174402990055221</v>
+      </c>
+      <c r="C74">
+        <v>116.4191165135196</v>
+      </c>
+      <c r="D74">
+        <v>535.8671165135196</v>
+      </c>
+      <c r="E74">
+        <v>-23.55199999999996</v>
+      </c>
+      <c r="F74">
+        <v>438.0480000000001</v>
+      </c>
+      <c r="G74">
+        <v>18.6</v>
+      </c>
+      <c r="H74">
+        <v>146.8</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>84</v>
+      </c>
+      <c r="K74">
+        <v>22.2</v>
+      </c>
+      <c r="L74">
+        <v>61.8</v>
+      </c>
+      <c r="M74">
+        <v>39.9499776</v>
+      </c>
+      <c r="N74">
+        <v>21.85002239999999</v>
+      </c>
+      <c r="O74">
+        <v>4.807004927999999</v>
+      </c>
+      <c r="P74">
+        <v>17.043017472</v>
+      </c>
+      <c r="Q74">
+        <v>39.24301747199999</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2365084964482933</v>
+      </c>
+      <c r="T74">
+        <v>2.677288462948786</v>
+      </c>
+      <c r="U74">
+        <v>0.0912</v>
+      </c>
+      <c r="V74">
+        <v>0.22</v>
+      </c>
+      <c r="W74">
+        <v>0.071136</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>1.546934534451403</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1176189484140153</v>
+      </c>
+      <c r="C75">
+        <v>109.3984050090163</v>
+      </c>
+      <c r="D75">
+        <v>534.9304050090163</v>
+      </c>
+      <c r="E75">
+        <v>-17.46799999999996</v>
+      </c>
+      <c r="F75">
+        <v>444.1320000000001</v>
+      </c>
+      <c r="G75">
+        <v>18.6</v>
+      </c>
+      <c r="H75">
+        <v>146.8</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>84</v>
+      </c>
+      <c r="K75">
+        <v>22.2</v>
+      </c>
+      <c r="L75">
+        <v>61.8</v>
+      </c>
+      <c r="M75">
+        <v>40.5048384</v>
+      </c>
+      <c r="N75">
+        <v>21.29516159999999</v>
+      </c>
+      <c r="O75">
+        <v>4.684935551999999</v>
+      </c>
+      <c r="P75">
+        <v>16.61022604799999</v>
+      </c>
+      <c r="Q75">
+        <v>38.81022604799999</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2432950682000566</v>
+      </c>
+      <c r="T75">
+        <v>2.769189471657949</v>
+      </c>
+      <c r="U75">
+        <v>0.0912</v>
+      </c>
+      <c r="V75">
+        <v>0.22</v>
+      </c>
+      <c r="W75">
+        <v>0.071136</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>1.525743650417823</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1177975978225085</v>
+      </c>
+      <c r="C76">
+        <v>102.3809625886622</v>
+      </c>
+      <c r="D76">
+        <v>533.9969625886622</v>
+      </c>
+      <c r="E76">
+        <v>-11.38399999999996</v>
+      </c>
+      <c r="F76">
+        <v>450.2160000000001</v>
+      </c>
+      <c r="G76">
+        <v>18.6</v>
+      </c>
+      <c r="H76">
+        <v>146.8</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>84</v>
+      </c>
+      <c r="K76">
+        <v>22.2</v>
+      </c>
+      <c r="L76">
+        <v>61.8</v>
+      </c>
+      <c r="M76">
+        <v>41.0596992</v>
+      </c>
+      <c r="N76">
+        <v>20.74030079999999</v>
+      </c>
+      <c r="O76">
+        <v>4.562866175999998</v>
+      </c>
+      <c r="P76">
+        <v>16.17743462399999</v>
+      </c>
+      <c r="Q76">
+        <v>38.37743462399999</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2506036839327248</v>
+      </c>
+      <c r="T76">
+        <v>2.868159788729355</v>
+      </c>
+      <c r="U76">
+        <v>0.0912</v>
+      </c>
+      <c r="V76">
+        <v>0.22</v>
+      </c>
+      <c r="W76">
+        <v>0.071136</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>1.505125492979744</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1611938119412071</v>
+      </c>
+      <c r="C77">
+        <v>-62.6699086095623</v>
+      </c>
+      <c r="D77">
+        <v>375.0300913904377</v>
+      </c>
+      <c r="E77">
+        <v>-5.299999999999955</v>
+      </c>
+      <c r="F77">
+        <v>456.3000000000001</v>
+      </c>
+      <c r="G77">
+        <v>18.6</v>
+      </c>
+      <c r="H77">
+        <v>146.8</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>84</v>
+      </c>
+      <c r="K77">
+        <v>22.2</v>
+      </c>
+      <c r="L77">
+        <v>61.8</v>
+      </c>
+      <c r="M77">
+        <v>71.45658000000002</v>
+      </c>
+      <c r="N77">
+        <v>-9.656580000000019</v>
+      </c>
+      <c r="O77">
+        <v>-2.124447600000004</v>
+      </c>
+      <c r="P77">
+        <v>-7.532132400000015</v>
+      </c>
+      <c r="Q77">
+        <v>14.66786759999998</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2643638079226195</v>
+      </c>
+      <c r="T77">
+        <v>3.054493820238844</v>
+      </c>
+      <c r="U77">
+        <v>0.1566</v>
+      </c>
+      <c r="V77">
+        <v>0.190269391566179</v>
+      </c>
+      <c r="W77">
+        <v>0.1268038132807364</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.8648608707553591</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1623718119412071</v>
+      </c>
+      <c r="C78">
+        <v>-71.76020644270682</v>
+      </c>
+      <c r="D78">
+        <v>372.0237935572932</v>
+      </c>
+      <c r="E78">
+        <v>0.7840000000000487</v>
+      </c>
+      <c r="F78">
+        <v>462.3840000000001</v>
+      </c>
+      <c r="G78">
+        <v>18.6</v>
+      </c>
+      <c r="H78">
+        <v>146.8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>84</v>
+      </c>
+      <c r="K78">
+        <v>22.2</v>
+      </c>
+      <c r="L78">
+        <v>61.8</v>
+      </c>
+      <c r="M78">
+        <v>72.40933440000002</v>
+      </c>
+      <c r="N78">
+        <v>-10.60933440000002</v>
+      </c>
+      <c r="O78">
+        <v>-2.334053568000005</v>
+      </c>
+      <c r="P78">
+        <v>-8.275280832000018</v>
+      </c>
+      <c r="Q78">
+        <v>13.92471916799998</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2737622999193953</v>
+      </c>
+      <c r="T78">
+        <v>3.181764396082129</v>
+      </c>
+      <c r="U78">
+        <v>0.1566</v>
+      </c>
+      <c r="V78">
+        <v>0.1877658469403082</v>
+      </c>
+      <c r="W78">
+        <v>0.1271958683691477</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.8534811224559465</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1635498119412072</v>
+      </c>
+      <c r="C79">
+        <v>-80.80268969017021</v>
+      </c>
+      <c r="D79">
+        <v>369.0653103098298</v>
+      </c>
+      <c r="E79">
+        <v>6.868000000000052</v>
+      </c>
+      <c r="F79">
+        <v>468.4680000000001</v>
+      </c>
+      <c r="G79">
+        <v>18.6</v>
+      </c>
+      <c r="H79">
+        <v>146.8</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>84</v>
+      </c>
+      <c r="K79">
+        <v>22.2</v>
+      </c>
+      <c r="L79">
+        <v>61.8</v>
+      </c>
+      <c r="M79">
+        <v>73.36208880000002</v>
+      </c>
+      <c r="N79">
+        <v>-11.56208880000003</v>
+      </c>
+      <c r="O79">
+        <v>-2.543659536000006</v>
+      </c>
+      <c r="P79">
+        <v>-9.018429264000021</v>
+      </c>
+      <c r="Q79">
+        <v>13.18157073599998</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2839780520898039</v>
+      </c>
+      <c r="T79">
+        <v>3.320101978520483</v>
+      </c>
+      <c r="U79">
+        <v>0.1566</v>
+      </c>
+      <c r="V79">
+        <v>0.1853273294475769</v>
+      </c>
+      <c r="W79">
+        <v>0.1275777402085095</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.8423969520344406</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1647278119412072</v>
+      </c>
+      <c r="C80">
+        <v>-89.79849007464543</v>
+      </c>
+      <c r="D80">
+        <v>366.1535099253546</v>
+      </c>
+      <c r="E80">
+        <v>12.95200000000006</v>
+      </c>
+      <c r="F80">
+        <v>474.5520000000001</v>
+      </c>
+      <c r="G80">
+        <v>18.6</v>
+      </c>
+      <c r="H80">
+        <v>146.8</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>84</v>
+      </c>
+      <c r="K80">
+        <v>22.2</v>
+      </c>
+      <c r="L80">
+        <v>61.8</v>
+      </c>
+      <c r="M80">
+        <v>74.31484320000003</v>
+      </c>
+      <c r="N80">
+        <v>-12.51484320000003</v>
+      </c>
+      <c r="O80">
+        <v>-2.753265504000006</v>
+      </c>
+      <c r="P80">
+        <v>-9.761577696000023</v>
+      </c>
+      <c r="Q80">
+        <v>12.43842230399998</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2951225090029768</v>
+      </c>
+      <c r="T80">
+        <v>3.471015704816868</v>
+      </c>
+      <c r="U80">
+        <v>0.1566</v>
+      </c>
+      <c r="V80">
+        <v>0.1829513380444029</v>
+      </c>
+      <c r="W80">
+        <v>0.1279498204622465</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.8315969911109222</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1659058119412072</v>
+      </c>
+      <c r="C81">
+        <v>-98.74870388276815</v>
+      </c>
+      <c r="D81">
+        <v>363.2872961172319</v>
+      </c>
+      <c r="E81">
+        <v>19.03600000000006</v>
+      </c>
+      <c r="F81">
+        <v>480.6360000000001</v>
+      </c>
+      <c r="G81">
+        <v>18.6</v>
+      </c>
+      <c r="H81">
+        <v>146.8</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>84</v>
+      </c>
+      <c r="K81">
+        <v>22.2</v>
+      </c>
+      <c r="L81">
+        <v>61.8</v>
+      </c>
+      <c r="M81">
+        <v>75.26759760000002</v>
+      </c>
+      <c r="N81">
+        <v>-13.46759760000002</v>
+      </c>
+      <c r="O81">
+        <v>-2.962871472000004</v>
+      </c>
+      <c r="P81">
+        <v>-10.50472612800002</v>
+      </c>
+      <c r="Q81">
+        <v>11.69527387199998</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3073283427650233</v>
+      </c>
+      <c r="T81">
+        <v>3.636302166951006</v>
+      </c>
+      <c r="U81">
+        <v>0.1566</v>
+      </c>
+      <c r="V81">
+        <v>0.1806354983223219</v>
+      </c>
+      <c r="W81">
+        <v>0.1283124809627244</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.8210704469196448</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1670838119412072</v>
+      </c>
+      <c r="C82">
+        <v>-107.6543933412936</v>
+      </c>
+      <c r="D82">
+        <v>360.4656066587065</v>
+      </c>
+      <c r="E82">
+        <v>25.12000000000006</v>
+      </c>
+      <c r="F82">
+        <v>486.7200000000001</v>
+      </c>
+      <c r="G82">
+        <v>18.6</v>
+      </c>
+      <c r="H82">
+        <v>146.8</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>84</v>
+      </c>
+      <c r="K82">
+        <v>22.2</v>
+      </c>
+      <c r="L82">
+        <v>61.8</v>
+      </c>
+      <c r="M82">
+        <v>76.22035200000002</v>
+      </c>
+      <c r="N82">
+        <v>-14.42035200000002</v>
+      </c>
+      <c r="O82">
+        <v>-3.172477440000005</v>
+      </c>
+      <c r="P82">
+        <v>-11.24787456000002</v>
+      </c>
+      <c r="Q82">
+        <v>10.95212543999998</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3207547599032745</v>
+      </c>
+      <c r="T82">
+        <v>3.818117275298555</v>
+      </c>
+      <c r="U82">
+        <v>0.1566</v>
+      </c>
+      <c r="V82">
+        <v>0.1783775545932928</v>
+      </c>
+      <c r="W82">
+        <v>0.1286660749506904</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.8108070663331493</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1682618119412072</v>
+      </c>
+      <c r="C83">
+        <v>-116.5165879296355</v>
+      </c>
+      <c r="D83">
+        <v>357.6874120703646</v>
+      </c>
+      <c r="E83">
+        <v>31.20400000000006</v>
+      </c>
+      <c r="F83">
+        <v>492.8040000000001</v>
+      </c>
+      <c r="G83">
+        <v>18.6</v>
+      </c>
+      <c r="H83">
+        <v>146.8</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>84</v>
+      </c>
+      <c r="K83">
+        <v>22.2</v>
+      </c>
+      <c r="L83">
+        <v>61.8</v>
+      </c>
+      <c r="M83">
+        <v>77.17310640000002</v>
+      </c>
+      <c r="N83">
+        <v>-15.37310640000003</v>
+      </c>
+      <c r="O83">
+        <v>-3.382083408000006</v>
+      </c>
+      <c r="P83">
+        <v>-11.99102299200002</v>
+      </c>
+      <c r="Q83">
+        <v>10.20897700799998</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.33559448410871</v>
+      </c>
+      <c r="T83">
+        <v>4.019070816103743</v>
+      </c>
+      <c r="U83">
+        <v>0.1566</v>
+      </c>
+      <c r="V83">
+        <v>0.1761753625612769</v>
+      </c>
+      <c r="W83">
+        <v>0.129010938222904</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.8007971025512585</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2145904593445469</v>
+      </c>
+      <c r="C84">
+        <v>-205.8009208168356</v>
+      </c>
+      <c r="D84">
+        <v>274.4870791831644</v>
+      </c>
+      <c r="E84">
+        <v>37.28800000000007</v>
+      </c>
+      <c r="F84">
+        <v>498.8880000000001</v>
+      </c>
+      <c r="G84">
+        <v>18.6</v>
+      </c>
+      <c r="H84">
+        <v>146.8</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>84</v>
+      </c>
+      <c r="K84">
+        <v>22.2</v>
+      </c>
+      <c r="L84">
+        <v>61.8</v>
+      </c>
+      <c r="M84">
+        <v>104.1678144</v>
+      </c>
+      <c r="N84">
+        <v>-42.36781440000003</v>
+      </c>
+      <c r="O84">
+        <v>-9.320919168000007</v>
+      </c>
+      <c r="P84">
+        <v>-33.04689523200003</v>
+      </c>
+      <c r="Q84">
+        <v>-10.84689523200003</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3651199965777481</v>
+      </c>
+      <c r="T84">
+        <v>4.418893359474709</v>
+      </c>
+      <c r="U84">
+        <v>0.2088</v>
+      </c>
+      <c r="V84">
+        <v>0.1305201618975313</v>
+      </c>
+      <c r="W84">
+        <v>0.1815473901957955</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.5932734631705969</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2162904593445469</v>
+      </c>
+      <c r="C85">
+        <v>-214.2079330345842</v>
+      </c>
+      <c r="D85">
+        <v>272.1640669654159</v>
+      </c>
+      <c r="E85">
+        <v>43.37200000000007</v>
+      </c>
+      <c r="F85">
+        <v>504.9720000000001</v>
+      </c>
+      <c r="G85">
+        <v>18.6</v>
+      </c>
+      <c r="H85">
+        <v>146.8</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>84</v>
+      </c>
+      <c r="K85">
+        <v>22.2</v>
+      </c>
+      <c r="L85">
+        <v>61.8</v>
+      </c>
+      <c r="M85">
+        <v>105.4381536</v>
+      </c>
+      <c r="N85">
+        <v>-43.63815360000002</v>
+      </c>
+      <c r="O85">
+        <v>-9.600393792000006</v>
+      </c>
+      <c r="P85">
+        <v>-34.03775980800002</v>
+      </c>
+      <c r="Q85">
+        <v>-11.83775980800002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3843152904940862</v>
+      </c>
+      <c r="T85">
+        <v>4.678828262973222</v>
+      </c>
+      <c r="U85">
+        <v>0.2088</v>
+      </c>
+      <c r="V85">
+        <v>0.1289476298264767</v>
+      </c>
+      <c r="W85">
+        <v>0.1818757348922317</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.5861255901203488</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2179904593445469</v>
+      </c>
+      <c r="C86">
+        <v>-222.5759554471814</v>
+      </c>
+      <c r="D86">
+        <v>269.8800445528186</v>
+      </c>
+      <c r="E86">
+        <v>49.45600000000002</v>
+      </c>
+      <c r="F86">
+        <v>511.056</v>
+      </c>
+      <c r="G86">
+        <v>18.6</v>
+      </c>
+      <c r="H86">
+        <v>146.8</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>84</v>
+      </c>
+      <c r="K86">
+        <v>22.2</v>
+      </c>
+      <c r="L86">
+        <v>61.8</v>
+      </c>
+      <c r="M86">
+        <v>106.7084928</v>
+      </c>
+      <c r="N86">
+        <v>-44.90849280000002</v>
+      </c>
+      <c r="O86">
+        <v>-9.879868416000004</v>
+      </c>
+      <c r="P86">
+        <v>-35.02862438400001</v>
+      </c>
+      <c r="Q86">
+        <v>-12.82862438400001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4059099961499665</v>
+      </c>
+      <c r="T86">
+        <v>4.971255029409046</v>
+      </c>
+      <c r="U86">
+        <v>0.2088</v>
+      </c>
+      <c r="V86">
+        <v>0.1274125389952092</v>
+      </c>
+      <c r="W86">
+        <v>0.1821962618578003</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.579147904523678</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2196904593445469</v>
+      </c>
+      <c r="C87">
+        <v>-230.9059615019817</v>
+      </c>
+      <c r="D87">
+        <v>267.6340384980184</v>
+      </c>
+      <c r="E87">
+        <v>55.54000000000008</v>
+      </c>
+      <c r="F87">
+        <v>517.1400000000001</v>
+      </c>
+      <c r="G87">
+        <v>18.6</v>
+      </c>
+      <c r="H87">
+        <v>146.8</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>84</v>
+      </c>
+      <c r="K87">
+        <v>22.2</v>
+      </c>
+      <c r="L87">
+        <v>61.8</v>
+      </c>
+      <c r="M87">
+        <v>107.978832</v>
+      </c>
+      <c r="N87">
+        <v>-46.17883200000003</v>
+      </c>
+      <c r="O87">
+        <v>-10.15934304000001</v>
+      </c>
+      <c r="P87">
+        <v>-36.01948896000002</v>
+      </c>
+      <c r="Q87">
+        <v>-13.81948896000002</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4303839958932976</v>
+      </c>
+      <c r="T87">
+        <v>5.302672031369649</v>
+      </c>
+      <c r="U87">
+        <v>0.2088</v>
+      </c>
+      <c r="V87">
+        <v>0.1259135679482067</v>
+      </c>
+      <c r="W87">
+        <v>0.1825092470124144</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.5723343997645759</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2213904593445469</v>
+      </c>
+      <c r="C88">
+        <v>-239.1988925087524</v>
+      </c>
+      <c r="D88">
+        <v>265.4251074912477</v>
+      </c>
+      <c r="E88">
+        <v>61.62400000000002</v>
+      </c>
+      <c r="F88">
+        <v>523.224</v>
+      </c>
+      <c r="G88">
+        <v>18.6</v>
+      </c>
+      <c r="H88">
+        <v>146.8</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>84</v>
+      </c>
+      <c r="K88">
+        <v>22.2</v>
+      </c>
+      <c r="L88">
+        <v>61.8</v>
+      </c>
+      <c r="M88">
+        <v>109.2491712</v>
+      </c>
+      <c r="N88">
+        <v>-47.44917120000002</v>
+      </c>
+      <c r="O88">
+        <v>-10.43881766400001</v>
+      </c>
+      <c r="P88">
+        <v>-37.01035353600002</v>
+      </c>
+      <c r="Q88">
+        <v>-14.81035353600002</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4583542813142474</v>
+      </c>
+      <c r="T88">
+        <v>5.681434319324624</v>
+      </c>
+      <c r="U88">
+        <v>0.2088</v>
+      </c>
+      <c r="V88">
+        <v>0.124449456692995</v>
+      </c>
+      <c r="W88">
+        <v>0.1828149534425026</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.5656793486045227</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2230904593445469</v>
+      </c>
+      <c r="C89">
+        <v>-247.4556589550631</v>
+      </c>
+      <c r="D89">
+        <v>263.2523410449369</v>
+      </c>
+      <c r="E89">
+        <v>67.70800000000008</v>
+      </c>
+      <c r="F89">
+        <v>529.3080000000001</v>
+      </c>
+      <c r="G89">
+        <v>18.6</v>
+      </c>
+      <c r="H89">
+        <v>146.8</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>84</v>
+      </c>
+      <c r="K89">
+        <v>22.2</v>
+      </c>
+      <c r="L89">
+        <v>61.8</v>
+      </c>
+      <c r="M89">
+        <v>110.5195104</v>
+      </c>
+      <c r="N89">
+        <v>-48.71951040000003</v>
+      </c>
+      <c r="O89">
+        <v>-10.71829228800001</v>
+      </c>
+      <c r="P89">
+        <v>-38.00121811200002</v>
+      </c>
+      <c r="Q89">
+        <v>-15.80121811200003</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4906276875691895</v>
+      </c>
+      <c r="T89">
+        <v>6.118467728503441</v>
+      </c>
+      <c r="U89">
+        <v>0.2088</v>
+      </c>
+      <c r="V89">
+        <v>0.1230190031677881</v>
+      </c>
+      <c r="W89">
+        <v>0.1831136321385659</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.5591772871263098</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2247904593445469</v>
+      </c>
+      <c r="C90">
+        <v>-255.6771417575932</v>
+      </c>
+      <c r="D90">
+        <v>261.1148582424068</v>
+      </c>
+      <c r="E90">
+        <v>73.79200000000003</v>
+      </c>
+      <c r="F90">
+        <v>535.3920000000001</v>
+      </c>
+      <c r="G90">
+        <v>18.6</v>
+      </c>
+      <c r="H90">
+        <v>146.8</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>84</v>
+      </c>
+      <c r="K90">
+        <v>22.2</v>
+      </c>
+      <c r="L90">
+        <v>61.8</v>
+      </c>
+      <c r="M90">
+        <v>111.7898496</v>
+      </c>
+      <c r="N90">
+        <v>-49.98984960000003</v>
+      </c>
+      <c r="O90">
+        <v>-10.99776691200001</v>
+      </c>
+      <c r="P90">
+        <v>-38.99208268800002</v>
+      </c>
+      <c r="Q90">
+        <v>-16.79208268800003</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5282799948666219</v>
+      </c>
+      <c r="T90">
+        <v>6.628340039212062</v>
+      </c>
+      <c r="U90">
+        <v>0.2088</v>
+      </c>
+      <c r="V90">
+        <v>0.1216210599499724</v>
+      </c>
+      <c r="W90">
+        <v>0.1834055226824458</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.5528229997726017</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2264904593445469</v>
+      </c>
+      <c r="C91">
+        <v>-263.8641934529705</v>
+      </c>
+      <c r="D91">
+        <v>259.0118065470296</v>
+      </c>
+      <c r="E91">
+        <v>79.87600000000009</v>
+      </c>
+      <c r="F91">
+        <v>541.4760000000001</v>
+      </c>
+      <c r="G91">
+        <v>18.6</v>
+      </c>
+      <c r="H91">
+        <v>146.8</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>84</v>
+      </c>
+      <c r="K91">
+        <v>22.2</v>
+      </c>
+      <c r="L91">
+        <v>61.8</v>
+      </c>
+      <c r="M91">
+        <v>113.0601888</v>
+      </c>
+      <c r="N91">
+        <v>-51.26018880000004</v>
+      </c>
+      <c r="O91">
+        <v>-11.27724153600001</v>
+      </c>
+      <c r="P91">
+        <v>-39.98294726400003</v>
+      </c>
+      <c r="Q91">
+        <v>-17.78294726400003</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.572778176218133</v>
+      </c>
+      <c r="T91">
+        <v>7.230916406413158</v>
+      </c>
+      <c r="U91">
+        <v>0.2088</v>
+      </c>
+      <c r="V91">
+        <v>0.1202545311864895</v>
+      </c>
+      <c r="W91">
+        <v>0.183690853888261</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.5466115053931342</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2281904593445469</v>
+      </c>
+      <c r="C92">
+        <v>-272.017639331521</v>
+      </c>
+      <c r="D92">
+        <v>256.942360668479</v>
+      </c>
+      <c r="E92">
+        <v>85.96000000000004</v>
+      </c>
+      <c r="F92">
+        <v>547.5600000000001</v>
+      </c>
+      <c r="G92">
+        <v>18.6</v>
+      </c>
+      <c r="H92">
+        <v>146.8</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>84</v>
+      </c>
+      <c r="K92">
+        <v>22.2</v>
+      </c>
+      <c r="L92">
+        <v>61.8</v>
+      </c>
+      <c r="M92">
+        <v>114.330528</v>
+      </c>
+      <c r="N92">
+        <v>-52.53052800000002</v>
+      </c>
+      <c r="O92">
+        <v>-11.55671616</v>
+      </c>
+      <c r="P92">
+        <v>-40.97381184000001</v>
+      </c>
+      <c r="Q92">
+        <v>-18.77381184000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6261759938399465</v>
+      </c>
+      <c r="T92">
+        <v>7.954008047054475</v>
+      </c>
+      <c r="U92">
+        <v>0.2088</v>
+      </c>
+      <c r="V92">
+        <v>0.1189183697288619</v>
+      </c>
+      <c r="W92">
+        <v>0.1839698444006136</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.5405380442220995</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2298904593445469</v>
+      </c>
+      <c r="C93">
+        <v>-280.1382785171018</v>
+      </c>
+      <c r="D93">
+        <v>254.9057214828983</v>
+      </c>
+      <c r="E93">
+        <v>92.0440000000001</v>
+      </c>
+      <c r="F93">
+        <v>553.6440000000001</v>
+      </c>
+      <c r="G93">
+        <v>18.6</v>
+      </c>
+      <c r="H93">
+        <v>146.8</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>84</v>
+      </c>
+      <c r="K93">
+        <v>22.2</v>
+      </c>
+      <c r="L93">
+        <v>61.8</v>
+      </c>
+      <c r="M93">
+        <v>115.6008672</v>
+      </c>
+      <c r="N93">
+        <v>-53.80086720000004</v>
+      </c>
+      <c r="O93">
+        <v>-11.83619078400001</v>
+      </c>
+      <c r="P93">
+        <v>-41.96467641600003</v>
+      </c>
+      <c r="Q93">
+        <v>-19.76467641600003</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6914399931554962</v>
+      </c>
+      <c r="T93">
+        <v>8.837786718949419</v>
+      </c>
+      <c r="U93">
+        <v>0.2088</v>
+      </c>
+      <c r="V93">
+        <v>0.1176115744571161</v>
+      </c>
+      <c r="W93">
+        <v>0.1842427032533542</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.5345980657141642</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2315904593445469</v>
+      </c>
+      <c r="C94">
+        <v>-288.2268849959797</v>
+      </c>
+      <c r="D94">
+        <v>252.9011150040204</v>
+      </c>
+      <c r="E94">
+        <v>98.12800000000004</v>
+      </c>
+      <c r="F94">
+        <v>559.7280000000001</v>
+      </c>
+      <c r="G94">
+        <v>18.6</v>
+      </c>
+      <c r="H94">
+        <v>146.8</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>84</v>
+      </c>
+      <c r="K94">
+        <v>22.2</v>
+      </c>
+      <c r="L94">
+        <v>61.8</v>
+      </c>
+      <c r="M94">
+        <v>116.8712064</v>
+      </c>
+      <c r="N94">
+        <v>-55.07120640000002</v>
+      </c>
+      <c r="O94">
+        <v>-12.11566540800001</v>
+      </c>
+      <c r="P94">
+        <v>-42.95554099200002</v>
+      </c>
+      <c r="Q94">
+        <v>-20.75554099200002</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.7730199922999335</v>
+      </c>
+      <c r="T94">
+        <v>9.942510058818099</v>
+      </c>
+      <c r="U94">
+        <v>0.2088</v>
+      </c>
+      <c r="V94">
+        <v>0.1163331877782345</v>
+      </c>
+      <c r="W94">
+        <v>0.1845096303919047</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.5287872171737931</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2332904593445469</v>
+      </c>
+      <c r="C95">
+        <v>-296.2842085975439</v>
+      </c>
+      <c r="D95">
+        <v>250.9277914024563</v>
+      </c>
+      <c r="E95">
+        <v>104.2120000000001</v>
+      </c>
+      <c r="F95">
+        <v>565.8120000000001</v>
+      </c>
+      <c r="G95">
+        <v>18.6</v>
+      </c>
+      <c r="H95">
+        <v>146.8</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>84</v>
+      </c>
+      <c r="K95">
+        <v>22.2</v>
+      </c>
+      <c r="L95">
+        <v>61.8</v>
+      </c>
+      <c r="M95">
+        <v>118.1415456</v>
+      </c>
+      <c r="N95">
+        <v>-56.34154560000003</v>
+      </c>
+      <c r="O95">
+        <v>-12.39514003200001</v>
+      </c>
+      <c r="P95">
+        <v>-43.94640556800002</v>
+      </c>
+      <c r="Q95">
+        <v>-21.74640556800002</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.8779085626284955</v>
+      </c>
+      <c r="T95">
+        <v>11.36286863864926</v>
+      </c>
+      <c r="U95">
+        <v>0.2088</v>
+      </c>
+      <c r="V95">
+        <v>0.1150822932859954</v>
+      </c>
+      <c r="W95">
+        <v>0.1847708171618842</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.5231013331181608</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2349904593445469</v>
+      </c>
+      <c r="C96">
+        <v>-304.3109759294576</v>
+      </c>
+      <c r="D96">
+        <v>248.9850240705425</v>
+      </c>
+      <c r="E96">
+        <v>110.296</v>
+      </c>
+      <c r="F96">
+        <v>571.8960000000001</v>
+      </c>
+      <c r="G96">
+        <v>18.6</v>
+      </c>
+      <c r="H96">
+        <v>146.8</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>84</v>
+      </c>
+      <c r="K96">
+        <v>22.2</v>
+      </c>
+      <c r="L96">
+        <v>61.8</v>
+      </c>
+      <c r="M96">
+        <v>119.4118848</v>
+      </c>
+      <c r="N96">
+        <v>-57.61188480000003</v>
+      </c>
+      <c r="O96">
+        <v>-12.67461465600001</v>
+      </c>
+      <c r="P96">
+        <v>-44.93727014400002</v>
+      </c>
+      <c r="Q96">
+        <v>-22.73727014400002</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.017759989733245</v>
+      </c>
+      <c r="T96">
+        <v>13.25668007842414</v>
+      </c>
+      <c r="U96">
+        <v>0.2088</v>
+      </c>
+      <c r="V96">
+        <v>0.1138580135701869</v>
+      </c>
+      <c r="W96">
+        <v>0.185026446766545</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.5175364253190314</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.236690459344547</v>
+      </c>
+      <c r="C97">
+        <v>-312.3078912697056</v>
+      </c>
+      <c r="D97">
+        <v>247.0721087302945</v>
+      </c>
+      <c r="E97">
+        <v>116.3800000000001</v>
+      </c>
+      <c r="F97">
+        <v>577.9800000000001</v>
+      </c>
+      <c r="G97">
+        <v>18.6</v>
+      </c>
+      <c r="H97">
+        <v>146.8</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>84</v>
+      </c>
+      <c r="K97">
+        <v>22.2</v>
+      </c>
+      <c r="L97">
+        <v>61.8</v>
+      </c>
+      <c r="M97">
+        <v>120.682224</v>
+      </c>
+      <c r="N97">
+        <v>-58.88222400000004</v>
+      </c>
+      <c r="O97">
+        <v>-12.95408928000001</v>
+      </c>
+      <c r="P97">
+        <v>-45.92813472000003</v>
+      </c>
+      <c r="Q97">
+        <v>-23.72813472000003</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.213551987679895</v>
+      </c>
+      <c r="T97">
+        <v>15.90801609410897</v>
+      </c>
+      <c r="U97">
+        <v>0.2088</v>
+      </c>
+      <c r="V97">
+        <v>0.1126595081641849</v>
+      </c>
+      <c r="W97">
+        <v>0.1852766946953182</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.5120886734735679</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2383904593445469</v>
+      </c>
+      <c r="C98">
+        <v>-320.2756374178305</v>
+      </c>
+      <c r="D98">
+        <v>245.1883625821696</v>
+      </c>
+      <c r="E98">
+        <v>122.4640000000001</v>
+      </c>
+      <c r="F98">
+        <v>584.0640000000001</v>
+      </c>
+      <c r="G98">
+        <v>18.6</v>
+      </c>
+      <c r="H98">
+        <v>146.8</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>84</v>
+      </c>
+      <c r="K98">
+        <v>22.2</v>
+      </c>
+      <c r="L98">
+        <v>61.8</v>
+      </c>
+      <c r="M98">
+        <v>121.9525632</v>
+      </c>
+      <c r="N98">
+        <v>-60.15256320000003</v>
+      </c>
+      <c r="O98">
+        <v>-13.23356390400001</v>
+      </c>
+      <c r="P98">
+        <v>-46.91899929600002</v>
+      </c>
+      <c r="Q98">
+        <v>-24.71899929600002</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.507239984599865</v>
+      </c>
+      <c r="T98">
+        <v>19.88502011763617</v>
+      </c>
+      <c r="U98">
+        <v>0.2088</v>
+      </c>
+      <c r="V98">
+        <v>0.111485971620808</v>
+      </c>
+      <c r="W98">
+        <v>0.1855217291255753</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.5067544164582183</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2400904593445469</v>
+      </c>
+      <c r="C99">
+        <v>-328.2148765075268</v>
+      </c>
+      <c r="D99">
+        <v>243.3331234924732</v>
+      </c>
+      <c r="E99">
+        <v>128.548</v>
+      </c>
+      <c r="F99">
+        <v>590.148</v>
+      </c>
+      <c r="G99">
+        <v>18.6</v>
+      </c>
+      <c r="H99">
+        <v>146.8</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>84</v>
+      </c>
+      <c r="K99">
+        <v>22.2</v>
+      </c>
+      <c r="L99">
+        <v>61.8</v>
+      </c>
+      <c r="M99">
+        <v>123.2229024</v>
+      </c>
+      <c r="N99">
+        <v>-61.42290240000001</v>
+      </c>
+      <c r="O99">
+        <v>-13.513038528</v>
+      </c>
+      <c r="P99">
+        <v>-47.90986387200001</v>
+      </c>
+      <c r="Q99">
+        <v>-25.70986387200001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.996719979466486</v>
+      </c>
+      <c r="T99">
+        <v>26.51336015684823</v>
+      </c>
+      <c r="U99">
+        <v>0.2088</v>
+      </c>
+      <c r="V99">
+        <v>0.1103366317071915</v>
+      </c>
+      <c r="W99">
+        <v>0.1857617112995384</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.5015301441235975</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2720748741950518</v>
+      </c>
+      <c r="C100">
+        <v>-364.6229522176516</v>
+      </c>
+      <c r="D100">
+        <v>213.0090477823485</v>
+      </c>
+      <c r="E100">
+        <v>134.6320000000001</v>
+      </c>
+      <c r="F100">
+        <v>596.2320000000001</v>
+      </c>
+      <c r="G100">
+        <v>18.6</v>
+      </c>
+      <c r="H100">
+        <v>146.8</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>84</v>
+      </c>
+      <c r="K100">
+        <v>22.2</v>
+      </c>
+      <c r="L100">
+        <v>61.8</v>
+      </c>
+      <c r="M100">
+        <v>142.3802016</v>
+      </c>
+      <c r="N100">
+        <v>-80.58020160000002</v>
+      </c>
+      <c r="O100">
+        <v>-17.72764435200001</v>
+      </c>
+      <c r="P100">
+        <v>-62.85255724800002</v>
+      </c>
+      <c r="Q100">
+        <v>-40.65255724800002</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.019900711724977</v>
+      </c>
+      <c r="T100">
+        <v>40.36885963814426</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.09549080453050852</v>
+      </c>
+      <c r="W100">
+        <v>0.2159967958781146</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.4340491115023115</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2740748741950518</v>
+      </c>
+      <c r="C101">
+        <v>-372.3539948761786</v>
+      </c>
+      <c r="D101">
+        <v>211.3620051238215</v>
+      </c>
+      <c r="E101">
+        <v>140.716</v>
+      </c>
+      <c r="F101">
+        <v>602.316</v>
+      </c>
+      <c r="G101">
+        <v>18.6</v>
+      </c>
+      <c r="H101">
+        <v>146.8</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>84</v>
+      </c>
+      <c r="K101">
+        <v>22.2</v>
+      </c>
+      <c r="L101">
+        <v>61.8</v>
+      </c>
+      <c r="M101">
+        <v>143.8330608</v>
+      </c>
+      <c r="N101">
+        <v>-82.03306080000003</v>
+      </c>
+      <c r="O101">
+        <v>-18.04727337600001</v>
+      </c>
+      <c r="P101">
+        <v>-63.98578742400002</v>
+      </c>
+      <c r="Q101">
+        <v>-41.78578742400002</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.001001423449953</v>
+      </c>
+      <c r="T101">
+        <v>80.73771927628852</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.09452625094939228</v>
+      </c>
+      <c r="W101">
+        <v>0.2162271312732851</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.4296647770426921</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/indonesia/indonesia_aerospace_defense.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_aerospace_defense.xlsx
@@ -1263,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1400,22 +1400,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1070136266053001</v>
+        <v>0.1068132966267684</v>
       </c>
       <c r="C2">
-        <v>536.4047522462595</v>
+        <v>532.5881165191028</v>
       </c>
       <c r="D2">
-        <v>525.2047522462594</v>
+        <v>526.7191165191027</v>
       </c>
       <c r="E2">
-        <v>-447.3</v>
+        <v>-441.969</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.331</v>
       </c>
       <c r="G2">
         <v>11.2</v>
@@ -1436,28 +1436,28 @@
         <v>52.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2681493</v>
       </c>
       <c r="N2">
-        <v>52.2</v>
+        <v>51.93185070000001</v>
       </c>
       <c r="O2">
-        <v>11.484</v>
+        <v>11.425007154</v>
       </c>
       <c r="P2">
-        <v>40.716</v>
+        <v>40.50684354600001</v>
       </c>
       <c r="Q2">
-        <v>60.01600000000001</v>
+        <v>59.80684354600001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1070136266053001</v>
+        <v>0.1074959157846146</v>
       </c>
       <c r="T2">
-        <v>0.8907328536426569</v>
+        <v>0.8977507488531747</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>194.6676720767125</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1482,22 +1482,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1068132966267684</v>
+        <v>0.1066129666482368</v>
       </c>
       <c r="C3">
-        <v>532.5881165191028</v>
+        <v>528.7802390170482</v>
       </c>
       <c r="D3">
-        <v>526.7191165191027</v>
+        <v>528.2422390170482</v>
       </c>
       <c r="E3">
-        <v>-441.969</v>
+        <v>-436.638</v>
       </c>
       <c r="F3">
-        <v>5.331</v>
+        <v>10.662</v>
       </c>
       <c r="G3">
         <v>11.2</v>
@@ -1518,28 +1518,28 @@
         <v>52.2</v>
       </c>
       <c r="M3">
-        <v>0.2681493</v>
+        <v>0.5362986</v>
       </c>
       <c r="N3">
-        <v>51.93185070000001</v>
+        <v>51.6637014</v>
       </c>
       <c r="O3">
-        <v>11.425007154</v>
+        <v>11.366014308</v>
       </c>
       <c r="P3">
-        <v>40.50684354600001</v>
+        <v>40.297687092</v>
       </c>
       <c r="Q3">
-        <v>59.80684354600001</v>
+        <v>59.597687092</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1074959157846146</v>
+        <v>0.1079880476002416</v>
       </c>
       <c r="T3">
-        <v>0.8977507488531747</v>
+        <v>0.9049118664149277</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>194.6676720767125</v>
+        <v>97.33383603835625</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1564,22 +1564,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1066129666482368</v>
+        <v>0.1064126366697051</v>
       </c>
       <c r="C4">
-        <v>528.7802390170482</v>
+        <v>524.9811959393616</v>
       </c>
       <c r="D4">
-        <v>528.2422390170482</v>
+        <v>529.7741959393616</v>
       </c>
       <c r="E4">
-        <v>-436.638</v>
+        <v>-431.307</v>
       </c>
       <c r="F4">
-        <v>10.662</v>
+        <v>15.993</v>
       </c>
       <c r="G4">
         <v>11.2</v>
@@ -1600,28 +1600,28 @@
         <v>52.2</v>
       </c>
       <c r="M4">
-        <v>0.5362986</v>
+        <v>0.8044479</v>
       </c>
       <c r="N4">
-        <v>51.6637014</v>
+        <v>51.3955521</v>
       </c>
       <c r="O4">
-        <v>11.366014308</v>
+        <v>11.307021462</v>
       </c>
       <c r="P4">
-        <v>40.297687092</v>
+        <v>40.088530638</v>
       </c>
       <c r="Q4">
-        <v>59.597687092</v>
+        <v>59.38853063800001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1079880476002416</v>
+        <v>0.1084903264636135</v>
       </c>
       <c r="T4">
-        <v>0.9049118664149277</v>
+        <v>0.9122206358851704</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>97.33383603835625</v>
+        <v>64.88922402557083</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1646,22 +1646,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1064126366697051</v>
+        <v>0.1062123066911735</v>
       </c>
       <c r="C5">
-        <v>524.9811959393616</v>
+        <v>521.1910643718221</v>
       </c>
       <c r="D5">
-        <v>529.7741959393616</v>
+        <v>531.315064371822</v>
       </c>
       <c r="E5">
-        <v>-431.307</v>
+        <v>-425.976</v>
       </c>
       <c r="F5">
-        <v>15.993</v>
+        <v>21.324</v>
       </c>
       <c r="G5">
         <v>11.2</v>
@@ -1682,28 +1682,28 @@
         <v>52.2</v>
       </c>
       <c r="M5">
-        <v>0.8044479</v>
+        <v>1.0725972</v>
       </c>
       <c r="N5">
-        <v>51.3955521</v>
+        <v>51.12740280000001</v>
       </c>
       <c r="O5">
-        <v>11.307021462</v>
+        <v>11.248028616</v>
       </c>
       <c r="P5">
-        <v>40.088530638</v>
+        <v>39.87937418400001</v>
       </c>
       <c r="Q5">
-        <v>59.38853063800001</v>
+        <v>59.17937418400001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1084903264636135</v>
+        <v>0.1090030694699723</v>
       </c>
       <c r="T5">
-        <v>0.9122206358851704</v>
+        <v>0.9196816713860432</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>64.88922402557083</v>
+        <v>48.66691801917813</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1728,22 +1728,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1062123066911735</v>
+        <v>0.1060119767126418</v>
       </c>
       <c r="C6">
-        <v>521.1910643718221</v>
+        <v>517.4099222996538</v>
       </c>
       <c r="D6">
-        <v>531.315064371822</v>
+        <v>532.8649222996537</v>
       </c>
       <c r="E6">
-        <v>-425.976</v>
+        <v>-420.645</v>
       </c>
       <c r="F6">
-        <v>21.324</v>
+        <v>26.655</v>
       </c>
       <c r="G6">
         <v>11.2</v>
@@ -1764,28 +1764,28 @@
         <v>52.2</v>
       </c>
       <c r="M6">
-        <v>1.0725972</v>
+        <v>1.3407465</v>
       </c>
       <c r="N6">
-        <v>51.12740280000001</v>
+        <v>50.8592535</v>
       </c>
       <c r="O6">
-        <v>11.248028616</v>
+        <v>11.18903577</v>
       </c>
       <c r="P6">
-        <v>39.87937418400001</v>
+        <v>39.67021773</v>
       </c>
       <c r="Q6">
-        <v>59.17937418400001</v>
+        <v>58.97021773</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1090030694699723</v>
+        <v>0.1095266070659387</v>
       </c>
       <c r="T6">
-        <v>0.9196816713860432</v>
+        <v>0.9272997813185134</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>48.66691801917813</v>
+        <v>38.9335344153425</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1810,22 +1810,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1060119767126418</v>
+        <v>0.1058116467341101</v>
       </c>
       <c r="C7">
-        <v>517.4099222996538</v>
+        <v>513.6378486206801</v>
       </c>
       <c r="D7">
-        <v>532.8649222996537</v>
+        <v>534.42384862068</v>
       </c>
       <c r="E7">
-        <v>-420.645</v>
+        <v>-415.314</v>
       </c>
       <c r="F7">
-        <v>26.655</v>
+        <v>31.986</v>
       </c>
       <c r="G7">
         <v>11.2</v>
@@ -1846,28 +1846,28 @@
         <v>52.2</v>
       </c>
       <c r="M7">
-        <v>1.3407465</v>
+        <v>1.6088958</v>
       </c>
       <c r="N7">
-        <v>50.8592535</v>
+        <v>50.5911042</v>
       </c>
       <c r="O7">
-        <v>11.18903577</v>
+        <v>11.130042924</v>
       </c>
       <c r="P7">
-        <v>39.67021773</v>
+        <v>39.461061276</v>
       </c>
       <c r="Q7">
-        <v>58.97021773</v>
+        <v>58.76106127600001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1095266070659387</v>
+        <v>0.1100612837596916</v>
       </c>
       <c r="T7">
-        <v>0.9272997813185134</v>
+        <v>0.9350799786963551</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.9335344153425</v>
+        <v>32.44461201278541</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1892,22 +1892,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1058116467341101</v>
+        <v>0.1056113167555784</v>
       </c>
       <c r="C8">
-        <v>513.6378486206801</v>
+        <v>509.8749231587144</v>
       </c>
       <c r="D8">
-        <v>534.42384862068</v>
+        <v>535.9919231587144</v>
       </c>
       <c r="E8">
-        <v>-415.314</v>
+        <v>-409.983</v>
       </c>
       <c r="F8">
-        <v>31.986</v>
+        <v>37.317</v>
       </c>
       <c r="G8">
         <v>11.2</v>
@@ -1928,28 +1928,28 @@
         <v>52.2</v>
       </c>
       <c r="M8">
-        <v>1.6088958</v>
+        <v>1.8770451</v>
       </c>
       <c r="N8">
-        <v>50.5911042</v>
+        <v>50.32295490000001</v>
       </c>
       <c r="O8">
-        <v>11.130042924</v>
+        <v>11.071050078</v>
       </c>
       <c r="P8">
-        <v>39.461061276</v>
+        <v>39.25190482200001</v>
       </c>
       <c r="Q8">
-        <v>58.76106127600001</v>
+        <v>58.55190482200001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1100612837596916</v>
+        <v>0.1106074588769661</v>
       </c>
       <c r="T8">
-        <v>0.9350799786963551</v>
+        <v>0.9430274921468386</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.44461201278541</v>
+        <v>27.80966743953036</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1974,22 +1974,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1056113167555785</v>
+        <v>0.1054109867770468</v>
       </c>
       <c r="C9">
-        <v>509.8749231587142</v>
+        <v>506.1212266771832</v>
       </c>
       <c r="D9">
-        <v>535.9919231587141</v>
+        <v>537.5692266771832</v>
       </c>
       <c r="E9">
-        <v>-409.983</v>
+        <v>-404.652</v>
       </c>
       <c r="F9">
-        <v>37.31700000000001</v>
+        <v>42.648</v>
       </c>
       <c r="G9">
         <v>11.2</v>
@@ -2010,28 +2010,28 @@
         <v>52.2</v>
       </c>
       <c r="M9">
-        <v>1.8770451</v>
+        <v>2.1451944</v>
       </c>
       <c r="N9">
-        <v>50.3229549</v>
+        <v>50.0548056</v>
       </c>
       <c r="O9">
-        <v>11.071050078</v>
+        <v>11.012057232</v>
       </c>
       <c r="P9">
-        <v>39.251904822</v>
+        <v>39.04274836800001</v>
       </c>
       <c r="Q9">
-        <v>58.551904822</v>
+        <v>58.342748368</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1106074588769661</v>
+        <v>0.1111655073663552</v>
       </c>
       <c r="T9">
-        <v>0.9430274921468388</v>
+        <v>0.9511477776288544</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.80966743953035</v>
+        <v>24.33345900958906</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2056,22 +2056,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1054109867770468</v>
+        <v>0.1052106567985152</v>
       </c>
       <c r="C10">
-        <v>506.1212266771832</v>
+        <v>502.3768408929945</v>
       </c>
       <c r="D10">
-        <v>537.5692266771832</v>
+        <v>539.1558408929944</v>
       </c>
       <c r="E10">
-        <v>-404.652</v>
+        <v>-399.321</v>
       </c>
       <c r="F10">
-        <v>42.648</v>
+        <v>47.979</v>
       </c>
       <c r="G10">
         <v>11.2</v>
@@ -2092,28 +2092,28 @@
         <v>52.2</v>
       </c>
       <c r="M10">
-        <v>2.1451944</v>
+        <v>2.4133437</v>
       </c>
       <c r="N10">
-        <v>50.0548056</v>
+        <v>49.7866563</v>
       </c>
       <c r="O10">
-        <v>11.012057232</v>
+        <v>10.953064386</v>
       </c>
       <c r="P10">
-        <v>39.04274836800001</v>
+        <v>38.833591914</v>
       </c>
       <c r="Q10">
-        <v>58.342748368</v>
+        <v>58.13359191400001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1111655073663552</v>
+        <v>0.111735820657709</v>
       </c>
       <c r="T10">
-        <v>0.9511477776288544</v>
+        <v>0.9594465309236618</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.33345900958906</v>
+        <v>21.62974134185695</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2138,22 +2138,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1052106567985152</v>
+        <v>0.1050103268199835</v>
       </c>
       <c r="C11">
-        <v>502.3768408929945</v>
+        <v>498.641848490648</v>
       </c>
       <c r="D11">
-        <v>539.1558408929944</v>
+        <v>540.7518484906479</v>
       </c>
       <c r="E11">
-        <v>-399.321</v>
+        <v>-393.99</v>
       </c>
       <c r="F11">
-        <v>47.979</v>
+        <v>53.31</v>
       </c>
       <c r="G11">
         <v>11.2</v>
@@ -2174,28 +2174,28 @@
         <v>52.2</v>
       </c>
       <c r="M11">
-        <v>2.4133437</v>
+        <v>2.681493</v>
       </c>
       <c r="N11">
-        <v>49.7866563</v>
+        <v>49.518507</v>
       </c>
       <c r="O11">
-        <v>10.953064386</v>
+        <v>10.89407154</v>
       </c>
       <c r="P11">
-        <v>38.833591914</v>
+        <v>38.62443546</v>
       </c>
       <c r="Q11">
-        <v>58.13359191400001</v>
+        <v>57.92443546</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.111735820657709</v>
+        <v>0.1123188075777594</v>
       </c>
       <c r="T11">
-        <v>0.9594465309236618</v>
+        <v>0.9679297009583538</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.62974134185695</v>
+        <v>19.46676720767125</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2220,22 +2220,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1050103268199835</v>
+        <v>0.1048099968414518</v>
       </c>
       <c r="C12">
-        <v>498.641848490648</v>
+        <v>494.9163331366001</v>
       </c>
       <c r="D12">
-        <v>540.7518484906479</v>
+        <v>542.3573331366001</v>
       </c>
       <c r="E12">
-        <v>-393.99</v>
+        <v>-388.659</v>
       </c>
       <c r="F12">
-        <v>53.31</v>
+        <v>58.64100000000001</v>
       </c>
       <c r="G12">
         <v>11.2</v>
@@ -2256,28 +2256,28 @@
         <v>52.2</v>
       </c>
       <c r="M12">
-        <v>2.681493</v>
+        <v>2.9496423</v>
       </c>
       <c r="N12">
-        <v>49.518507</v>
+        <v>49.2503577</v>
       </c>
       <c r="O12">
-        <v>10.89407154</v>
+        <v>10.835078694</v>
       </c>
       <c r="P12">
-        <v>38.62443546</v>
+        <v>38.41527900600001</v>
       </c>
       <c r="Q12">
-        <v>57.92443546</v>
+        <v>57.715279006</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1123188075777594</v>
+        <v>0.112914895327474</v>
       </c>
       <c r="T12">
-        <v>0.9679297009583538</v>
+        <v>0.9766035040275334</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2294,7 +2294,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.46676720767125</v>
+        <v>17.69706109788295</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2302,22 +2302,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1048099968414518</v>
+        <v>0.1046096668629202</v>
       </c>
       <c r="C13">
-        <v>494.9163331366001</v>
+        <v>491.2003794938844</v>
       </c>
       <c r="D13">
-        <v>542.3573331366001</v>
+        <v>543.9723794938843</v>
       </c>
       <c r="E13">
-        <v>-388.659</v>
+        <v>-383.328</v>
       </c>
       <c r="F13">
-        <v>58.64100000000001</v>
+        <v>63.972</v>
       </c>
       <c r="G13">
         <v>11.2</v>
@@ -2338,28 +2338,28 @@
         <v>52.2</v>
       </c>
       <c r="M13">
-        <v>2.9496423</v>
+        <v>3.2177916</v>
       </c>
       <c r="N13">
-        <v>49.2503577</v>
+        <v>48.9822084</v>
       </c>
       <c r="O13">
-        <v>10.835078694</v>
+        <v>10.776085848</v>
       </c>
       <c r="P13">
-        <v>38.41527900600001</v>
+        <v>38.206122552</v>
       </c>
       <c r="Q13">
-        <v>57.715279006</v>
+        <v>57.50612255200001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.112914895327474</v>
+        <v>0.1135245305260456</v>
       </c>
       <c r="T13">
-        <v>0.9766035040275334</v>
+        <v>0.9854744389846486</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.69706109788295</v>
+        <v>16.22230600639271</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2384,22 +2384,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1046096668629202</v>
+        <v>0.1044093368843885</v>
       </c>
       <c r="C14">
-        <v>491.2003794938844</v>
+        <v>487.4940732369935</v>
       </c>
       <c r="D14">
-        <v>543.9723794938843</v>
+        <v>545.5970732369934</v>
       </c>
       <c r="E14">
-        <v>-383.328</v>
+        <v>-377.997</v>
       </c>
       <c r="F14">
-        <v>63.972</v>
+        <v>69.30300000000001</v>
       </c>
       <c r="G14">
         <v>11.2</v>
@@ -2420,28 +2420,28 @@
         <v>52.2</v>
       </c>
       <c r="M14">
-        <v>3.2177916</v>
+        <v>3.485940900000001</v>
       </c>
       <c r="N14">
-        <v>48.9822084</v>
+        <v>48.7140591</v>
       </c>
       <c r="O14">
-        <v>10.776085848</v>
+        <v>10.717093002</v>
       </c>
       <c r="P14">
-        <v>38.206122552</v>
+        <v>37.996966098</v>
       </c>
       <c r="Q14">
-        <v>57.50612255200001</v>
+        <v>57.296966098</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1135245305260456</v>
+        <v>0.1141481803268833</v>
       </c>
       <c r="T14">
-        <v>0.9854744389846486</v>
+        <v>0.9945493034810079</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.22230600639271</v>
+        <v>14.97443631359327</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2466,22 +2466,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1044093368843885</v>
+        <v>0.1042090069058569</v>
       </c>
       <c r="C15">
-        <v>487.4940732369935</v>
+        <v>483.7975010670292</v>
       </c>
       <c r="D15">
-        <v>545.5970732369934</v>
+        <v>547.2315010670292</v>
       </c>
       <c r="E15">
-        <v>-377.997</v>
+        <v>-372.666</v>
       </c>
       <c r="F15">
-        <v>69.30300000000001</v>
+        <v>74.63400000000001</v>
       </c>
       <c r="G15">
         <v>11.2</v>
@@ -2502,28 +2502,28 @@
         <v>52.2</v>
       </c>
       <c r="M15">
-        <v>3.485940900000001</v>
+        <v>3.754090200000001</v>
       </c>
       <c r="N15">
-        <v>48.7140591</v>
+        <v>48.4459098</v>
       </c>
       <c r="O15">
-        <v>10.717093002</v>
+        <v>10.658100156</v>
       </c>
       <c r="P15">
-        <v>37.996966098</v>
+        <v>37.787809644</v>
       </c>
       <c r="Q15">
-        <v>57.296966098</v>
+        <v>57.087809644</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1141481803268833</v>
+        <v>0.1147863336114615</v>
       </c>
       <c r="T15">
-        <v>0.9945493034810079</v>
+        <v>1.003835211337748</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.97443631359327</v>
+        <v>13.90483371976518</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2548,22 +2548,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1042090069058569</v>
+        <v>0.1040086769273252</v>
       </c>
       <c r="C16">
-        <v>483.7975010670292</v>
+        <v>480.1107507271271</v>
       </c>
       <c r="D16">
-        <v>547.2315010670292</v>
+        <v>548.8757507271271</v>
       </c>
       <c r="E16">
-        <v>-372.666</v>
+        <v>-367.335</v>
       </c>
       <c r="F16">
-        <v>74.63400000000001</v>
+        <v>79.96500000000002</v>
       </c>
       <c r="G16">
         <v>11.2</v>
@@ -2584,28 +2584,28 @@
         <v>52.2</v>
       </c>
       <c r="M16">
-        <v>3.754090200000001</v>
+        <v>4.0222395</v>
       </c>
       <c r="N16">
-        <v>48.4459098</v>
+        <v>48.17776050000001</v>
       </c>
       <c r="O16">
-        <v>10.658100156</v>
+        <v>10.59910731</v>
       </c>
       <c r="P16">
-        <v>37.787809644</v>
+        <v>37.57865319</v>
       </c>
       <c r="Q16">
-        <v>57.087809644</v>
+        <v>56.87865319000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1147863336114615</v>
+        <v>0.1154395022674414</v>
       </c>
       <c r="T16">
-        <v>1.003835211337748</v>
+        <v>1.013339611144058</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2622,7 +2622,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>13.90483371976518</v>
+        <v>12.97784480511417</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2630,22 +2630,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1040086769273252</v>
+        <v>0.1039955469487935</v>
       </c>
       <c r="C17">
-        <v>480.1107507271271</v>
+        <v>474.8878628316947</v>
       </c>
       <c r="D17">
-        <v>548.8757507271271</v>
+        <v>548.9838628316946</v>
       </c>
       <c r="E17">
-        <v>-367.335</v>
+        <v>-362.004</v>
       </c>
       <c r="F17">
-        <v>79.965</v>
+        <v>85.29600000000001</v>
       </c>
       <c r="G17">
         <v>11.2</v>
@@ -2666,45 +2666,45 @@
         <v>52.2</v>
       </c>
       <c r="M17">
-        <v>4.0222395</v>
+        <v>4.4183328</v>
       </c>
       <c r="N17">
-        <v>48.17776050000001</v>
+        <v>47.7816672</v>
       </c>
       <c r="O17">
-        <v>10.59910731</v>
+        <v>10.511966784</v>
       </c>
       <c r="P17">
-        <v>37.57865319</v>
+        <v>37.269700416</v>
       </c>
       <c r="Q17">
-        <v>56.87865319000001</v>
+        <v>56.569700416</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1154395022674414</v>
+        <v>0.1161082225580875</v>
       </c>
       <c r="T17">
-        <v>1.013339611144058</v>
+        <v>1.023070306183852</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.22</v>
       </c>
       <c r="W17">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>12.97784480511417</v>
+        <v>11.81441108284102</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2712,22 +2712,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1039955469487935</v>
+        <v>0.1038069169702619</v>
       </c>
       <c r="C18">
-        <v>474.8878628316947</v>
+        <v>471.1147544450196</v>
       </c>
       <c r="D18">
-        <v>548.9838628316946</v>
+        <v>550.5417544450196</v>
       </c>
       <c r="E18">
-        <v>-362.004</v>
+        <v>-356.673</v>
       </c>
       <c r="F18">
-        <v>85.29600000000001</v>
+        <v>90.62700000000001</v>
       </c>
       <c r="G18">
         <v>11.2</v>
@@ -2748,28 +2748,28 @@
         <v>52.2</v>
       </c>
       <c r="M18">
-        <v>4.4183328</v>
+        <v>4.6944786</v>
       </c>
       <c r="N18">
-        <v>47.7816672</v>
+        <v>47.50552140000001</v>
       </c>
       <c r="O18">
-        <v>10.511966784</v>
+        <v>10.451214708</v>
       </c>
       <c r="P18">
-        <v>37.269700416</v>
+        <v>37.054306692</v>
       </c>
       <c r="Q18">
-        <v>56.569700416</v>
+        <v>56.35430669200001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1161082225580875</v>
+        <v>0.116793056590677</v>
       </c>
       <c r="T18">
-        <v>1.023070306183852</v>
+        <v>1.033035475802918</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.81441108284102</v>
+        <v>11.11944572502684</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2794,22 +2794,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1038069169702619</v>
+        <v>0.1036182869917302</v>
       </c>
       <c r="C19">
-        <v>471.1147544450196</v>
+        <v>467.3505131067001</v>
       </c>
       <c r="D19">
-        <v>550.5417544450196</v>
+        <v>552.1085131067001</v>
       </c>
       <c r="E19">
-        <v>-356.673</v>
+        <v>-351.342</v>
       </c>
       <c r="F19">
-        <v>90.62700000000001</v>
+        <v>95.95800000000001</v>
       </c>
       <c r="G19">
         <v>11.2</v>
@@ -2830,28 +2830,28 @@
         <v>52.2</v>
       </c>
       <c r="M19">
-        <v>4.6944786</v>
+        <v>4.9706244</v>
       </c>
       <c r="N19">
-        <v>47.50552140000001</v>
+        <v>47.2293756</v>
       </c>
       <c r="O19">
-        <v>10.451214708</v>
+        <v>10.390462632</v>
       </c>
       <c r="P19">
-        <v>37.054306692</v>
+        <v>36.838912968</v>
       </c>
       <c r="Q19">
-        <v>56.35430669200001</v>
+        <v>56.138912968</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.116793056590677</v>
+        <v>0.1174945938923539</v>
       </c>
       <c r="T19">
-        <v>1.033035475802918</v>
+        <v>1.043243698339522</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.11944572502684</v>
+        <v>10.50169874030313</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2876,22 +2876,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1036182869917302</v>
+        <v>0.1034296570131985</v>
       </c>
       <c r="C20">
-        <v>467.3505131067002</v>
+        <v>463.5952147356297</v>
       </c>
       <c r="D20">
-        <v>552.1085131067001</v>
+        <v>553.6842147356297</v>
       </c>
       <c r="E20">
-        <v>-351.342</v>
+        <v>-346.011</v>
       </c>
       <c r="F20">
-        <v>95.958</v>
+        <v>101.289</v>
       </c>
       <c r="G20">
         <v>11.2</v>
@@ -2912,28 +2912,28 @@
         <v>52.2</v>
       </c>
       <c r="M20">
-        <v>4.9706244</v>
+        <v>5.2467702</v>
       </c>
       <c r="N20">
-        <v>47.2293756</v>
+        <v>46.9532298</v>
       </c>
       <c r="O20">
-        <v>10.390462632</v>
+        <v>10.329710556</v>
       </c>
       <c r="P20">
-        <v>36.838912968</v>
+        <v>36.623519244</v>
       </c>
       <c r="Q20">
-        <v>56.138912968</v>
+        <v>55.923519244</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1174945938923539</v>
+        <v>0.1182134531027142</v>
       </c>
       <c r="T20">
-        <v>1.043243698339521</v>
+        <v>1.053703975753573</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.50169874030313</v>
+        <v>9.948977753971386</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2958,22 +2958,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1034296570131985</v>
+        <v>0.1035062270346669</v>
       </c>
       <c r="C21">
-        <v>463.5952147356297</v>
+        <v>457.6235115324343</v>
       </c>
       <c r="D21">
-        <v>553.6842147356297</v>
+        <v>553.0435115324343</v>
       </c>
       <c r="E21">
-        <v>-346.011</v>
+        <v>-340.68</v>
       </c>
       <c r="F21">
-        <v>101.289</v>
+        <v>106.62</v>
       </c>
       <c r="G21">
         <v>11.2</v>
@@ -2994,45 +2994,45 @@
         <v>52.2</v>
       </c>
       <c r="M21">
-        <v>5.2467702</v>
+        <v>5.70417</v>
       </c>
       <c r="N21">
-        <v>46.9532298</v>
+        <v>46.49583000000001</v>
       </c>
       <c r="O21">
-        <v>10.329710556</v>
+        <v>10.2290826</v>
       </c>
       <c r="P21">
-        <v>36.623519244</v>
+        <v>36.2667474</v>
       </c>
       <c r="Q21">
-        <v>55.923519244</v>
+        <v>55.5667474</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1182134531027142</v>
+        <v>0.1189502837933336</v>
       </c>
       <c r="T21">
-        <v>1.053703975753573</v>
+        <v>1.064425760102975</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.22</v>
       </c>
       <c r="W21">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>9.948977753971386</v>
+        <v>9.151199911643587</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3040,22 +3040,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1035062270346669</v>
+        <v>0.1033308570561352</v>
       </c>
       <c r="C22">
-        <v>457.6235115324343</v>
+        <v>453.7621247962334</v>
       </c>
       <c r="D22">
-        <v>553.0435115324343</v>
+        <v>554.5131247962333</v>
       </c>
       <c r="E22">
-        <v>-340.68</v>
+        <v>-335.349</v>
       </c>
       <c r="F22">
-        <v>106.62</v>
+        <v>111.951</v>
       </c>
       <c r="G22">
         <v>11.2</v>
@@ -3076,28 +3076,28 @@
         <v>52.2</v>
       </c>
       <c r="M22">
-        <v>5.70417</v>
+        <v>5.989378500000001</v>
       </c>
       <c r="N22">
-        <v>46.49583000000001</v>
+        <v>46.2106215</v>
       </c>
       <c r="O22">
-        <v>10.2290826</v>
+        <v>10.16633673</v>
       </c>
       <c r="P22">
-        <v>36.2667474</v>
+        <v>36.04428477</v>
       </c>
       <c r="Q22">
-        <v>55.5667474</v>
+        <v>55.34428477</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1189502837933336</v>
+        <v>0.1197057684254876</v>
       </c>
       <c r="T22">
-        <v>1.064425760102975</v>
+        <v>1.075418982030843</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.151199911643587</v>
+        <v>8.715428487279606</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3122,22 +3122,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1033308570561352</v>
+        <v>0.1031554870776036</v>
       </c>
       <c r="C23">
-        <v>453.7621247962335</v>
+        <v>449.9085693339629</v>
       </c>
       <c r="D23">
-        <v>554.5131247962335</v>
+        <v>555.9905693339629</v>
       </c>
       <c r="E23">
-        <v>-335.349</v>
+        <v>-330.018</v>
       </c>
       <c r="F23">
-        <v>111.951</v>
+        <v>117.282</v>
       </c>
       <c r="G23">
         <v>11.2</v>
@@ -3158,28 +3158,28 @@
         <v>52.2</v>
       </c>
       <c r="M23">
-        <v>5.9893785</v>
+        <v>6.274587</v>
       </c>
       <c r="N23">
-        <v>46.2106215</v>
+        <v>45.92541300000001</v>
       </c>
       <c r="O23">
-        <v>10.16633673</v>
+        <v>10.10359086</v>
       </c>
       <c r="P23">
-        <v>36.04428477</v>
+        <v>35.82182214000001</v>
       </c>
       <c r="Q23">
-        <v>55.34428477</v>
+        <v>55.12182214000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1197057684254876</v>
+        <v>0.1204806244584661</v>
       </c>
       <c r="T23">
-        <v>1.075418982030843</v>
+        <v>1.086694081444041</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.715428487279606</v>
+        <v>8.319272646948715</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3204,22 +3204,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1031554870776036</v>
+        <v>0.1029801170990719</v>
       </c>
       <c r="C24">
-        <v>449.9085693339629</v>
+        <v>446.0629079097804</v>
       </c>
       <c r="D24">
-        <v>555.9905693339629</v>
+        <v>557.4759079097804</v>
       </c>
       <c r="E24">
-        <v>-330.018</v>
+        <v>-324.687</v>
       </c>
       <c r="F24">
-        <v>117.282</v>
+        <v>122.613</v>
       </c>
       <c r="G24">
         <v>11.2</v>
@@ -3240,28 +3240,28 @@
         <v>52.2</v>
       </c>
       <c r="M24">
-        <v>6.274587</v>
+        <v>6.559795500000001</v>
       </c>
       <c r="N24">
-        <v>45.92541300000001</v>
+        <v>45.6402045</v>
       </c>
       <c r="O24">
-        <v>10.10359086</v>
+        <v>10.04084499</v>
       </c>
       <c r="P24">
-        <v>35.82182214000001</v>
+        <v>35.59935951</v>
       </c>
       <c r="Q24">
-        <v>55.12182214000001</v>
+        <v>54.89935951</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1204806244584661</v>
+        <v>0.1212756066221713</v>
       </c>
       <c r="T24">
-        <v>1.086694081444041</v>
+        <v>1.098262040582258</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.319272646948715</v>
+        <v>7.95756514055964</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3286,22 +3286,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1029801170990719</v>
+        <v>0.1028047471205402</v>
       </c>
       <c r="C25">
-        <v>446.0629079097804</v>
+        <v>442.2252039603432</v>
       </c>
       <c r="D25">
-        <v>557.4759079097804</v>
+        <v>558.9692039603432</v>
       </c>
       <c r="E25">
-        <v>-324.687</v>
+        <v>-319.356</v>
       </c>
       <c r="F25">
-        <v>122.613</v>
+        <v>127.944</v>
       </c>
       <c r="G25">
         <v>11.2</v>
@@ -3322,28 +3322,28 @@
         <v>52.2</v>
       </c>
       <c r="M25">
-        <v>6.559795500000001</v>
+        <v>6.845004000000001</v>
       </c>
       <c r="N25">
-        <v>45.6402045</v>
+        <v>45.354996</v>
       </c>
       <c r="O25">
-        <v>10.04084499</v>
+        <v>9.97809912</v>
       </c>
       <c r="P25">
-        <v>35.59935951</v>
+        <v>35.37689688</v>
       </c>
       <c r="Q25">
-        <v>54.89935951</v>
+        <v>54.67689688</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1212756066221713</v>
+        <v>0.1220915093691319</v>
       </c>
       <c r="T25">
-        <v>1.098262040582258</v>
+        <v>1.110134419697796</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.95756514055964</v>
+        <v>7.625999926369655</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3368,22 +3368,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1028047471205402</v>
+        <v>0.1027853771420086</v>
       </c>
       <c r="C26">
-        <v>442.2252039603432</v>
+        <v>437.0596323706993</v>
       </c>
       <c r="D26">
-        <v>558.9692039603432</v>
+        <v>559.1346323706993</v>
       </c>
       <c r="E26">
-        <v>-319.356</v>
+        <v>-314.025</v>
       </c>
       <c r="F26">
-        <v>127.944</v>
+        <v>133.275</v>
       </c>
       <c r="G26">
         <v>11.2</v>
@@ -3404,45 +3404,45 @@
         <v>52.2</v>
       </c>
       <c r="M26">
-        <v>6.845004</v>
+        <v>7.2368325</v>
       </c>
       <c r="N26">
-        <v>45.354996</v>
+        <v>44.9631675</v>
       </c>
       <c r="O26">
-        <v>9.97809912</v>
+        <v>9.89189685</v>
       </c>
       <c r="P26">
-        <v>35.37689688</v>
+        <v>35.07127065</v>
       </c>
       <c r="Q26">
-        <v>54.67689688</v>
+        <v>54.37127065</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1220915093691319</v>
+        <v>0.1229291695226781</v>
       </c>
       <c r="T26">
-        <v>1.110134419697796</v>
+        <v>1.122323395589748</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.22</v>
       </c>
       <c r="W26">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.625999926369656</v>
+        <v>7.213100482842459</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3450,22 +3450,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1027853771420086</v>
+        <v>0.1026162471634769</v>
       </c>
       <c r="C27">
-        <v>437.0596323706993</v>
+        <v>433.1772500683296</v>
       </c>
       <c r="D27">
-        <v>559.1346323706993</v>
+        <v>560.5832500683296</v>
       </c>
       <c r="E27">
-        <v>-314.025</v>
+        <v>-308.694</v>
       </c>
       <c r="F27">
-        <v>133.275</v>
+        <v>138.606</v>
       </c>
       <c r="G27">
         <v>11.2</v>
@@ -3486,28 +3486,28 @@
         <v>52.2</v>
       </c>
       <c r="M27">
-        <v>7.2368325</v>
+        <v>7.526305800000001</v>
       </c>
       <c r="N27">
-        <v>44.9631675</v>
+        <v>44.6736942</v>
       </c>
       <c r="O27">
-        <v>9.89189685</v>
+        <v>9.828212724</v>
       </c>
       <c r="P27">
-        <v>35.07127065</v>
+        <v>34.845481476</v>
       </c>
       <c r="Q27">
-        <v>54.37127065</v>
+        <v>54.145481476</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1229291695226781</v>
+        <v>0.1237894691398337</v>
       </c>
       <c r="T27">
-        <v>1.122323395589748</v>
+        <v>1.134841803262563</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.213100482842459</v>
+        <v>6.935673541194671</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3532,22 +3532,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1026162471634769</v>
+        <v>0.1024471171849453</v>
       </c>
       <c r="C28">
-        <v>433.1772500683296</v>
+        <v>429.3023934817883</v>
       </c>
       <c r="D28">
-        <v>560.5832500683296</v>
+        <v>562.0393934817882</v>
       </c>
       <c r="E28">
-        <v>-308.694</v>
+        <v>-303.363</v>
       </c>
       <c r="F28">
-        <v>138.606</v>
+        <v>143.937</v>
       </c>
       <c r="G28">
         <v>11.2</v>
@@ -3568,28 +3568,28 @@
         <v>52.2</v>
       </c>
       <c r="M28">
-        <v>7.526305800000001</v>
+        <v>7.815779100000001</v>
       </c>
       <c r="N28">
-        <v>44.6736942</v>
+        <v>44.3842209</v>
       </c>
       <c r="O28">
-        <v>9.828212724</v>
+        <v>9.764528598</v>
       </c>
       <c r="P28">
-        <v>34.845481476</v>
+        <v>34.619692302</v>
       </c>
       <c r="Q28">
-        <v>54.145481476</v>
+        <v>53.919692302</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1237894691398337</v>
+        <v>0.124673338609514</v>
       </c>
       <c r="T28">
-        <v>1.134841803262563</v>
+        <v>1.147703181008607</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.935673541194671</v>
+        <v>6.678796743372646</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3614,22 +3614,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1024471171849453</v>
+        <v>0.1022779872064136</v>
       </c>
       <c r="C29">
-        <v>429.3023934817883</v>
+        <v>425.435121409091</v>
       </c>
       <c r="D29">
-        <v>562.0393934817882</v>
+        <v>563.503121409091</v>
       </c>
       <c r="E29">
-        <v>-303.363</v>
+        <v>-298.032</v>
       </c>
       <c r="F29">
-        <v>143.937</v>
+        <v>149.268</v>
       </c>
       <c r="G29">
         <v>11.2</v>
@@ -3650,28 +3650,28 @@
         <v>52.2</v>
       </c>
       <c r="M29">
-        <v>7.815779100000001</v>
+        <v>8.105252400000001</v>
       </c>
       <c r="N29">
-        <v>44.3842209</v>
+        <v>44.09474760000001</v>
       </c>
       <c r="O29">
-        <v>9.764528598</v>
+        <v>9.700844472000002</v>
       </c>
       <c r="P29">
-        <v>34.619692302</v>
+        <v>34.39390312800001</v>
       </c>
       <c r="Q29">
-        <v>53.919692302</v>
+        <v>53.693903128</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.124673338609514</v>
+        <v>0.1255817600089078</v>
       </c>
       <c r="T29">
-        <v>1.147703181008607</v>
+        <v>1.160921819247596</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.678796743372646</v>
+        <v>6.440268288252195</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3696,22 +3696,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1022779872064136</v>
+        <v>0.1021088572278819</v>
       </c>
       <c r="C30">
-        <v>425.435121409091</v>
+        <v>421.5754932623678</v>
       </c>
       <c r="D30">
-        <v>563.503121409091</v>
+        <v>564.9744932623678</v>
       </c>
       <c r="E30">
-        <v>-298.032</v>
+        <v>-292.701</v>
       </c>
       <c r="F30">
-        <v>149.268</v>
+        <v>154.599</v>
       </c>
       <c r="G30">
         <v>11.2</v>
@@ -3732,28 +3732,28 @@
         <v>52.2</v>
       </c>
       <c r="M30">
-        <v>8.105252400000001</v>
+        <v>8.3947257</v>
       </c>
       <c r="N30">
-        <v>44.09474760000001</v>
+        <v>43.8052743</v>
       </c>
       <c r="O30">
-        <v>9.700844472000002</v>
+        <v>9.637160346</v>
       </c>
       <c r="P30">
-        <v>34.39390312800001</v>
+        <v>34.168113954</v>
       </c>
       <c r="Q30">
-        <v>53.693903128</v>
+        <v>53.468113954</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1255817600089078</v>
+        <v>0.1265157707434957</v>
       </c>
       <c r="T30">
-        <v>1.160921819247596</v>
+        <v>1.174512813493317</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3770,7 +3770,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.440268288252195</v>
+        <v>6.218190071415913</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3778,22 +3778,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1021088572278819</v>
+        <v>0.1021737272493503</v>
       </c>
       <c r="C31">
-        <v>421.5754932623678</v>
+        <v>415.6792392156744</v>
       </c>
       <c r="D31">
-        <v>564.9744932623678</v>
+        <v>564.4092392156743</v>
       </c>
       <c r="E31">
-        <v>-292.701</v>
+        <v>-287.37</v>
       </c>
       <c r="F31">
-        <v>154.599</v>
+        <v>159.93</v>
       </c>
       <c r="G31">
         <v>11.2</v>
@@ -3814,45 +3814,45 @@
         <v>52.2</v>
       </c>
       <c r="M31">
-        <v>8.3947257</v>
+        <v>8.844129000000001</v>
       </c>
       <c r="N31">
-        <v>43.8052743</v>
+        <v>43.355871</v>
       </c>
       <c r="O31">
-        <v>9.637160346</v>
+        <v>9.538291620000001</v>
       </c>
       <c r="P31">
-        <v>34.168113954</v>
+        <v>33.81757938</v>
       </c>
       <c r="Q31">
-        <v>53.468113954</v>
+        <v>53.11757938</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1265157707434957</v>
+        <v>0.1274764674990718</v>
       </c>
       <c r="T31">
-        <v>1.174512813493317</v>
+        <v>1.188492121860345</v>
       </c>
       <c r="U31">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0.22</v>
       </c>
       <c r="W31">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>6.218190071415913</v>
+        <v>5.902220557841252</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3860,22 +3860,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1021737272493503</v>
+        <v>0.1020123972708186</v>
       </c>
       <c r="C32">
-        <v>415.6792392156744</v>
+        <v>411.7561072463957</v>
       </c>
       <c r="D32">
-        <v>564.4092392156743</v>
+        <v>565.8171072463956</v>
       </c>
       <c r="E32">
-        <v>-287.37</v>
+        <v>-282.039</v>
       </c>
       <c r="F32">
-        <v>159.93</v>
+        <v>165.261</v>
       </c>
       <c r="G32">
         <v>11.2</v>
@@ -3896,28 +3896,28 @@
         <v>52.2</v>
       </c>
       <c r="M32">
-        <v>8.844129000000001</v>
+        <v>9.1389333</v>
       </c>
       <c r="N32">
-        <v>43.355871</v>
+        <v>43.0610667</v>
       </c>
       <c r="O32">
-        <v>9.538291620000001</v>
+        <v>9.473434674000002</v>
       </c>
       <c r="P32">
-        <v>33.81757938</v>
+        <v>33.587632026</v>
       </c>
       <c r="Q32">
-        <v>53.11757938</v>
+        <v>52.88763202600001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1274764674990718</v>
+        <v>0.1284650105374183</v>
       </c>
       <c r="T32">
-        <v>1.188492121860345</v>
+        <v>1.202876627571345</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.902220557841252</v>
+        <v>5.711826346297987</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3942,22 +3942,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1020123972708186</v>
+        <v>0.101851067292287</v>
       </c>
       <c r="C33">
-        <v>411.7561072463957</v>
+        <v>407.8400164407567</v>
       </c>
       <c r="D33">
-        <v>565.8171072463956</v>
+        <v>567.2320164407566</v>
       </c>
       <c r="E33">
-        <v>-282.039</v>
+        <v>-276.708</v>
       </c>
       <c r="F33">
-        <v>165.261</v>
+        <v>170.592</v>
       </c>
       <c r="G33">
         <v>11.2</v>
@@ -3978,28 +3978,28 @@
         <v>52.2</v>
       </c>
       <c r="M33">
-        <v>9.1389333</v>
+        <v>9.433737600000001</v>
       </c>
       <c r="N33">
-        <v>43.0610667</v>
+        <v>42.7662624</v>
       </c>
       <c r="O33">
-        <v>9.473434674000002</v>
+        <v>9.408577728000001</v>
       </c>
       <c r="P33">
-        <v>33.587632026</v>
+        <v>33.357684672</v>
       </c>
       <c r="Q33">
-        <v>52.88763202600001</v>
+        <v>52.657684672</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1284650105374183</v>
+        <v>0.1294826283710102</v>
       </c>
       <c r="T33">
-        <v>1.202876627571345</v>
+        <v>1.217684206979726</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4016,7 +4016,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.711826346297987</v>
+        <v>5.533331772976174</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4024,22 +4024,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.101851067292287</v>
+        <v>0.1016897373137553</v>
       </c>
       <c r="C34">
-        <v>407.8400164407567</v>
+        <v>403.9310197535856</v>
       </c>
       <c r="D34">
-        <v>567.2320164407566</v>
+        <v>568.6540197535855</v>
       </c>
       <c r="E34">
-        <v>-276.708</v>
+        <v>-271.377</v>
       </c>
       <c r="F34">
-        <v>170.592</v>
+        <v>175.923</v>
       </c>
       <c r="G34">
         <v>11.2</v>
@@ -4060,28 +4060,28 @@
         <v>52.2</v>
       </c>
       <c r="M34">
-        <v>9.433737600000001</v>
+        <v>9.7285419</v>
       </c>
       <c r="N34">
-        <v>42.7662624</v>
+        <v>42.47145810000001</v>
       </c>
       <c r="O34">
-        <v>9.408577728000001</v>
+        <v>9.343720782000002</v>
       </c>
       <c r="P34">
-        <v>33.357684672</v>
+        <v>33.127737318</v>
       </c>
       <c r="Q34">
-        <v>52.657684672</v>
+        <v>52.427737318</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1294826283710102</v>
+        <v>0.1305306228563512</v>
       </c>
       <c r="T34">
-        <v>1.217684206979726</v>
+        <v>1.232933803683881</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4098,7 +4098,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.533331772976174</v>
+        <v>5.365655052582958</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4106,22 +4106,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1016897373137553</v>
+        <v>0.1015284073352236</v>
       </c>
       <c r="C35">
-        <v>403.9310197535856</v>
+        <v>400.0291706720589</v>
       </c>
       <c r="D35">
-        <v>568.6540197535855</v>
+        <v>570.0831706720588</v>
       </c>
       <c r="E35">
-        <v>-271.377</v>
+        <v>-266.046</v>
       </c>
       <c r="F35">
-        <v>175.923</v>
+        <v>181.254</v>
       </c>
       <c r="G35">
         <v>11.2</v>
@@ -4142,28 +4142,28 @@
         <v>52.2</v>
       </c>
       <c r="M35">
-        <v>9.7285419</v>
+        <v>10.0233462</v>
       </c>
       <c r="N35">
-        <v>42.47145810000001</v>
+        <v>42.1766538</v>
       </c>
       <c r="O35">
-        <v>9.343720782000002</v>
+        <v>9.278863836000001</v>
       </c>
       <c r="P35">
-        <v>33.127737318</v>
+        <v>32.897789964</v>
       </c>
       <c r="Q35">
-        <v>52.427737318</v>
+        <v>52.19778996400001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1305306228563512</v>
+        <v>0.1316103747503388</v>
       </c>
       <c r="T35">
-        <v>1.232933803683881</v>
+        <v>1.24864550937907</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.365655052582958</v>
+        <v>5.207841668683458</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4188,22 +4188,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1015284073352236</v>
+        <v>0.101367077356692</v>
       </c>
       <c r="C36">
-        <v>400.0291706720589</v>
+        <v>396.1345232224068</v>
       </c>
       <c r="D36">
-        <v>570.0831706720588</v>
+        <v>571.5195232224067</v>
       </c>
       <c r="E36">
-        <v>-266.046</v>
+        <v>-260.715</v>
       </c>
       <c r="F36">
-        <v>181.254</v>
+        <v>186.585</v>
       </c>
       <c r="G36">
         <v>11.2</v>
@@ -4224,28 +4224,28 @@
         <v>52.2</v>
       </c>
       <c r="M36">
-        <v>10.0233462</v>
+        <v>10.3181505</v>
       </c>
       <c r="N36">
-        <v>42.1766538</v>
+        <v>41.8818495</v>
       </c>
       <c r="O36">
-        <v>9.278863836000001</v>
+        <v>9.21400689</v>
       </c>
       <c r="P36">
-        <v>32.897789964</v>
+        <v>32.66784261</v>
       </c>
       <c r="Q36">
-        <v>52.19778996400001</v>
+        <v>51.96784261000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1316103747503388</v>
+        <v>0.1327233497795261</v>
       </c>
       <c r="T36">
-        <v>1.24864550937907</v>
+        <v>1.264840652172573</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.207841668683458</v>
+        <v>5.059046192435359</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4270,22 +4270,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.101367077356692</v>
+        <v>0.1012057473781603</v>
       </c>
       <c r="C37">
-        <v>396.1345232224068</v>
+        <v>392.2471319767222</v>
       </c>
       <c r="D37">
-        <v>571.5195232224067</v>
+        <v>572.9631319767223</v>
       </c>
       <c r="E37">
-        <v>-260.715</v>
+        <v>-255.384</v>
       </c>
       <c r="F37">
-        <v>186.585</v>
+        <v>191.916</v>
       </c>
       <c r="G37">
         <v>11.2</v>
@@ -4306,28 +4306,28 @@
         <v>52.2</v>
       </c>
       <c r="M37">
-        <v>10.3181505</v>
+        <v>10.6129548</v>
       </c>
       <c r="N37">
-        <v>41.8818495</v>
+        <v>41.5870452</v>
       </c>
       <c r="O37">
-        <v>9.21400689</v>
+        <v>9.149149943999999</v>
       </c>
       <c r="P37">
-        <v>32.66784261</v>
+        <v>32.437895256</v>
       </c>
       <c r="Q37">
-        <v>51.96784261000001</v>
+        <v>51.737895256</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1327233497795261</v>
+        <v>0.1338711052783755</v>
       </c>
       <c r="T37">
-        <v>1.264840652172573</v>
+        <v>1.281541893178373</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4344,7 +4344,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.059046192435359</v>
+        <v>4.918517131534376</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4352,22 +4352,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1012057473781603</v>
+        <v>0.1010444173996287</v>
       </c>
       <c r="C38">
-        <v>392.2471319767223</v>
+        <v>388.3670520598718</v>
       </c>
       <c r="D38">
-        <v>572.9631319767223</v>
+        <v>574.4140520598718</v>
       </c>
       <c r="E38">
-        <v>-255.384</v>
+        <v>-250.053</v>
       </c>
       <c r="F38">
-        <v>191.916</v>
+        <v>197.247</v>
       </c>
       <c r="G38">
         <v>11.2</v>
@@ -4388,28 +4388,28 @@
         <v>52.2</v>
       </c>
       <c r="M38">
-        <v>10.6129548</v>
+        <v>10.9077591</v>
       </c>
       <c r="N38">
-        <v>41.58704520000001</v>
+        <v>41.2922409</v>
       </c>
       <c r="O38">
-        <v>9.149149944000001</v>
+        <v>9.084292998</v>
       </c>
       <c r="P38">
-        <v>32.437895256</v>
+        <v>32.207947902</v>
       </c>
       <c r="Q38">
-        <v>51.737895256</v>
+        <v>51.507947902</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1338711052783755</v>
+        <v>0.135055297459728</v>
       </c>
       <c r="T38">
-        <v>1.281541893178373</v>
+        <v>1.298773332311341</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4426,7 +4426,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.918517131534378</v>
+        <v>4.785584236087502</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4434,22 +4434,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1010444173996287</v>
+        <v>0.100883087421097</v>
       </c>
       <c r="C39">
-        <v>388.3670520598718</v>
+        <v>384.4943391565125</v>
       </c>
       <c r="D39">
-        <v>574.4140520598718</v>
+        <v>575.8723391565125</v>
       </c>
       <c r="E39">
-        <v>-250.053</v>
+        <v>-244.722</v>
       </c>
       <c r="F39">
-        <v>197.247</v>
+        <v>202.578</v>
       </c>
       <c r="G39">
         <v>11.2</v>
@@ -4470,28 +4470,28 @@
         <v>52.2</v>
       </c>
       <c r="M39">
-        <v>10.9077591</v>
+        <v>11.2025634</v>
       </c>
       <c r="N39">
-        <v>41.2922409</v>
+        <v>40.9974366</v>
       </c>
       <c r="O39">
-        <v>9.084292998</v>
+        <v>9.019436052</v>
       </c>
       <c r="P39">
-        <v>32.207947902</v>
+        <v>31.978000548</v>
       </c>
       <c r="Q39">
-        <v>51.507947902</v>
+        <v>51.278000548</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.135055297459728</v>
+        <v>0.1362776893888661</v>
       </c>
       <c r="T39">
-        <v>1.298773332311341</v>
+        <v>1.316560624319566</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4508,7 +4508,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.785584236087502</v>
+        <v>4.659647808822042</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4516,22 +4516,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.100883087421097</v>
+        <v>0.1007217574425653</v>
       </c>
       <c r="C40">
-        <v>384.4943391565125</v>
+        <v>380.6290495182159</v>
       </c>
       <c r="D40">
-        <v>575.8723391565125</v>
+        <v>577.3380495182158</v>
       </c>
       <c r="E40">
-        <v>-244.722</v>
+        <v>-239.391</v>
       </c>
       <c r="F40">
-        <v>202.578</v>
+        <v>207.909</v>
       </c>
       <c r="G40">
         <v>11.2</v>
@@ -4552,28 +4552,28 @@
         <v>52.2</v>
       </c>
       <c r="M40">
-        <v>11.2025634</v>
+        <v>11.4973677</v>
       </c>
       <c r="N40">
-        <v>40.9974366</v>
+        <v>40.7026323</v>
       </c>
       <c r="O40">
-        <v>9.019436052</v>
+        <v>8.954579106000001</v>
       </c>
       <c r="P40">
-        <v>31.978000548</v>
+        <v>31.748053194</v>
       </c>
       <c r="Q40">
-        <v>51.278000548</v>
+        <v>51.048053194</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1362776893888661</v>
+        <v>0.1375401597419104</v>
       </c>
       <c r="T40">
-        <v>1.316560624319566</v>
+        <v>1.3349311062297</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4590,7 +4590,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.659647808822042</v>
+        <v>4.540169659877886</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4598,22 +4598,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1007217574425653</v>
+        <v>0.1013404274640337</v>
       </c>
       <c r="C41">
-        <v>380.6290495182159</v>
+        <v>369.717489314981</v>
       </c>
       <c r="D41">
-        <v>577.3380495182158</v>
+        <v>571.7574893149809</v>
       </c>
       <c r="E41">
-        <v>-239.391</v>
+        <v>-234.06</v>
       </c>
       <c r="F41">
-        <v>207.909</v>
+        <v>213.24</v>
       </c>
       <c r="G41">
         <v>11.2</v>
@@ -4634,45 +4634,45 @@
         <v>52.2</v>
       </c>
       <c r="M41">
-        <v>11.4973677</v>
+        <v>12.325272</v>
       </c>
       <c r="N41">
-        <v>40.7026323</v>
+        <v>39.874728</v>
       </c>
       <c r="O41">
-        <v>8.954579106000001</v>
+        <v>8.77244016</v>
       </c>
       <c r="P41">
-        <v>31.748053194</v>
+        <v>31.10228784</v>
       </c>
       <c r="Q41">
-        <v>51.048053194</v>
+        <v>50.40228784</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1375401597419104</v>
+        <v>0.1388447124400561</v>
       </c>
       <c r="T41">
-        <v>1.3349311062297</v>
+        <v>1.353913937536839</v>
       </c>
       <c r="U41">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V41">
         <v>0.22</v>
       </c>
       <c r="W41">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.540169659877886</v>
+        <v>4.235200651149929</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4680,22 +4680,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1013404274640337</v>
+        <v>0.101198597485502</v>
       </c>
       <c r="C42">
-        <v>369.717489314981</v>
+        <v>365.6562792469026</v>
       </c>
       <c r="D42">
-        <v>571.7574893149809</v>
+        <v>573.0272792469026</v>
       </c>
       <c r="E42">
-        <v>-234.06</v>
+        <v>-228.729</v>
       </c>
       <c r="F42">
-        <v>213.24</v>
+        <v>218.571</v>
       </c>
       <c r="G42">
         <v>11.2</v>
@@ -4716,28 +4716,28 @@
         <v>52.2</v>
       </c>
       <c r="M42">
-        <v>12.325272</v>
+        <v>12.6334038</v>
       </c>
       <c r="N42">
-        <v>39.874728</v>
+        <v>39.5665962</v>
       </c>
       <c r="O42">
-        <v>8.77244016</v>
+        <v>8.704651163999999</v>
       </c>
       <c r="P42">
-        <v>31.10228784</v>
+        <v>30.861945036</v>
       </c>
       <c r="Q42">
-        <v>50.40228784</v>
+        <v>50.16194503600001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1388447124400561</v>
+        <v>0.1401934872635627</v>
       </c>
       <c r="T42">
-        <v>1.353913937536839</v>
+        <v>1.373540254650999</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4754,7 +4754,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.235200651149929</v>
+        <v>4.131903074292614</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4762,22 +4762,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.101198597485502</v>
+        <v>0.1010567675069703</v>
       </c>
       <c r="C43">
-        <v>365.6562792469026</v>
+        <v>361.6007217686099</v>
       </c>
       <c r="D43">
-        <v>573.0272792469026</v>
+        <v>574.3027217686099</v>
       </c>
       <c r="E43">
-        <v>-228.729</v>
+        <v>-223.398</v>
       </c>
       <c r="F43">
-        <v>218.571</v>
+        <v>223.902</v>
       </c>
       <c r="G43">
         <v>11.2</v>
@@ -4798,28 +4798,28 @@
         <v>52.2</v>
       </c>
       <c r="M43">
-        <v>12.6334038</v>
+        <v>12.9415356</v>
       </c>
       <c r="N43">
-        <v>39.5665962</v>
+        <v>39.2584644</v>
       </c>
       <c r="O43">
-        <v>8.704651163999999</v>
+        <v>8.636862168</v>
       </c>
       <c r="P43">
-        <v>30.861945036</v>
+        <v>30.621602232</v>
       </c>
       <c r="Q43">
-        <v>50.16194503600001</v>
+        <v>49.921602232</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1401934872635627</v>
+        <v>0.141588771563742</v>
       </c>
       <c r="T43">
-        <v>1.373540254650999</v>
+        <v>1.39384334132082</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.131903074292614</v>
+        <v>4.033524429666599</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4844,22 +4844,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1010567675069704</v>
+        <v>0.1020888375284387</v>
       </c>
       <c r="C44">
-        <v>361.6007217686097</v>
+        <v>347.1161664189335</v>
       </c>
       <c r="D44">
-        <v>574.3027217686097</v>
+        <v>565.1491664189334</v>
       </c>
       <c r="E44">
-        <v>-223.398</v>
+        <v>-218.067</v>
       </c>
       <c r="F44">
-        <v>223.902</v>
+        <v>229.233</v>
       </c>
       <c r="G44">
         <v>11.2</v>
@@ -4880,45 +4880,45 @@
         <v>52.2</v>
       </c>
       <c r="M44">
-        <v>12.9415356</v>
+        <v>14.0519829</v>
       </c>
       <c r="N44">
-        <v>39.2584644</v>
+        <v>38.1480171</v>
       </c>
       <c r="O44">
-        <v>8.636862168</v>
+        <v>8.392563762000002</v>
       </c>
       <c r="P44">
-        <v>30.621602232</v>
+        <v>29.755453338</v>
       </c>
       <c r="Q44">
-        <v>49.921602232</v>
+        <v>49.05545333800001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.141588771563742</v>
+        <v>0.1430330132077872</v>
       </c>
       <c r="T44">
-        <v>1.39384334132082</v>
+        <v>1.414858816996599</v>
       </c>
       <c r="U44">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V44">
         <v>0.22</v>
       </c>
       <c r="W44">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.033524429666599</v>
+        <v>3.714778218239933</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4926,22 +4926,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1020888375284387</v>
+        <v>0.101974307549907</v>
       </c>
       <c r="C45">
-        <v>347.1161664189335</v>
+        <v>342.7865278734695</v>
       </c>
       <c r="D45">
-        <v>565.1491664189334</v>
+        <v>566.1505278734695</v>
       </c>
       <c r="E45">
-        <v>-218.067</v>
+        <v>-212.736</v>
       </c>
       <c r="F45">
-        <v>229.233</v>
+        <v>234.564</v>
       </c>
       <c r="G45">
         <v>11.2</v>
@@ -4962,28 +4962,28 @@
         <v>52.2</v>
       </c>
       <c r="M45">
-        <v>14.0519829</v>
+        <v>14.3787732</v>
       </c>
       <c r="N45">
-        <v>38.1480171</v>
+        <v>37.82122680000001</v>
       </c>
       <c r="O45">
-        <v>8.392563762000002</v>
+        <v>8.320669896000002</v>
       </c>
       <c r="P45">
-        <v>29.755453338</v>
+        <v>29.500556904</v>
       </c>
       <c r="Q45">
-        <v>49.05545333800001</v>
+        <v>48.800556904</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1430330132077872</v>
+        <v>0.1445288349105483</v>
       </c>
       <c r="T45">
-        <v>1.414858816996599</v>
+        <v>1.436624845375085</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5000,7 +5000,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.714778218239933</v>
+        <v>3.630351440552662</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5008,22 +5008,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.101974307549907</v>
+        <v>0.1018597775713754</v>
       </c>
       <c r="C46">
-        <v>342.7865278734695</v>
+        <v>338.4604441579766</v>
       </c>
       <c r="D46">
-        <v>566.1505278734695</v>
+        <v>567.1554441579765</v>
       </c>
       <c r="E46">
-        <v>-212.736</v>
+        <v>-207.405</v>
       </c>
       <c r="F46">
-        <v>234.564</v>
+        <v>239.895</v>
       </c>
       <c r="G46">
         <v>11.2</v>
@@ -5044,28 +5044,28 @@
         <v>52.2</v>
       </c>
       <c r="M46">
-        <v>14.3787732</v>
+        <v>14.7055635</v>
       </c>
       <c r="N46">
-        <v>37.82122680000001</v>
+        <v>37.49443650000001</v>
       </c>
       <c r="O46">
-        <v>8.320669896000002</v>
+        <v>8.248776030000002</v>
       </c>
       <c r="P46">
-        <v>29.500556904</v>
+        <v>29.24566047</v>
       </c>
       <c r="Q46">
-        <v>48.800556904</v>
+        <v>48.54566047</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1445288349105483</v>
+        <v>0.1460790501297734</v>
       </c>
       <c r="T46">
-        <v>1.436624845375085</v>
+        <v>1.459182365694607</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.630351440552662</v>
+        <v>3.549676964095936</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5090,22 +5090,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1018597775713754</v>
+        <v>0.1027498875928437</v>
       </c>
       <c r="C47">
-        <v>338.4604441579766</v>
+        <v>325.4119834244706</v>
       </c>
       <c r="D47">
-        <v>567.1554441579765</v>
+        <v>559.4379834244705</v>
       </c>
       <c r="E47">
-        <v>-207.405</v>
+        <v>-202.074</v>
       </c>
       <c r="F47">
-        <v>239.895</v>
+        <v>245.226</v>
       </c>
       <c r="G47">
         <v>11.2</v>
@@ -5126,45 +5126,45 @@
         <v>52.2</v>
       </c>
       <c r="M47">
-        <v>14.7055635</v>
+        <v>15.7189866</v>
       </c>
       <c r="N47">
-        <v>37.49443650000001</v>
+        <v>36.4810134</v>
       </c>
       <c r="O47">
-        <v>8.248776030000002</v>
+        <v>8.025822948</v>
       </c>
       <c r="P47">
-        <v>29.24566047</v>
+        <v>28.455190452</v>
       </c>
       <c r="Q47">
-        <v>48.54566047</v>
+        <v>47.75519045200001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1460790501297734</v>
+        <v>0.1476866807274884</v>
       </c>
       <c r="T47">
-        <v>1.459182365694607</v>
+        <v>1.482575349729667</v>
       </c>
       <c r="U47">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V47">
         <v>0.22</v>
       </c>
       <c r="W47">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.549676964095936</v>
+        <v>3.320824766146184</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5172,22 +5172,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1027498875928437</v>
+        <v>0.1026571976143121</v>
       </c>
       <c r="C48">
-        <v>325.4119834244706</v>
+        <v>320.8748164881763</v>
       </c>
       <c r="D48">
-        <v>559.4379834244705</v>
+        <v>560.2318164881763</v>
       </c>
       <c r="E48">
-        <v>-202.074</v>
+        <v>-196.743</v>
       </c>
       <c r="F48">
-        <v>245.226</v>
+        <v>250.557</v>
       </c>
       <c r="G48">
         <v>11.2</v>
@@ -5208,28 +5208,28 @@
         <v>52.2</v>
       </c>
       <c r="M48">
-        <v>15.7189866</v>
+        <v>16.0607037</v>
       </c>
       <c r="N48">
-        <v>36.4810134</v>
+        <v>36.1392963</v>
       </c>
       <c r="O48">
-        <v>8.025822948</v>
+        <v>7.950645186</v>
       </c>
       <c r="P48">
-        <v>28.455190452</v>
+        <v>28.188651114</v>
       </c>
       <c r="Q48">
-        <v>47.75519045200001</v>
+        <v>47.488651114</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1476866807274884</v>
+        <v>0.1493549766307775</v>
       </c>
       <c r="T48">
-        <v>1.482575349729667</v>
+        <v>1.506851087879257</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.320824766146184</v>
+        <v>3.250168920057967</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5254,22 +5254,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1026571976143121</v>
+        <v>0.1025645076357804</v>
       </c>
       <c r="C49">
-        <v>320.8748164881763</v>
+        <v>316.3399056246705</v>
       </c>
       <c r="D49">
-        <v>560.2318164881763</v>
+        <v>561.0279056246704</v>
       </c>
       <c r="E49">
-        <v>-196.743</v>
+        <v>-191.412</v>
       </c>
       <c r="F49">
-        <v>250.557</v>
+        <v>255.888</v>
       </c>
       <c r="G49">
         <v>11.2</v>
@@ -5290,28 +5290,28 @@
         <v>52.2</v>
       </c>
       <c r="M49">
-        <v>16.0607037</v>
+        <v>16.4024208</v>
       </c>
       <c r="N49">
-        <v>36.1392963</v>
+        <v>35.7975792</v>
       </c>
       <c r="O49">
-        <v>7.950645186</v>
+        <v>7.875467424</v>
       </c>
       <c r="P49">
-        <v>28.188651114</v>
+        <v>27.922111776</v>
       </c>
       <c r="Q49">
-        <v>47.488651114</v>
+        <v>47.22211177600001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1493549766307775</v>
+        <v>0.1510874377611162</v>
       </c>
       <c r="T49">
-        <v>1.506851087879257</v>
+        <v>1.53206050826537</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.250168920057967</v>
+        <v>3.18245706755676</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5336,22 +5336,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1025645076357804</v>
+        <v>0.1024718176572487</v>
       </c>
       <c r="C50">
-        <v>316.3399056246706</v>
+        <v>311.8072604652742</v>
       </c>
       <c r="D50">
-        <v>561.0279056246706</v>
+        <v>561.8262604652741</v>
       </c>
       <c r="E50">
-        <v>-191.412</v>
+        <v>-186.081</v>
       </c>
       <c r="F50">
-        <v>255.888</v>
+        <v>261.219</v>
       </c>
       <c r="G50">
         <v>11.2</v>
@@ -5372,28 +5372,28 @@
         <v>52.2</v>
       </c>
       <c r="M50">
-        <v>16.4024208</v>
+        <v>16.7441379</v>
       </c>
       <c r="N50">
-        <v>35.7975792</v>
+        <v>35.4558621</v>
       </c>
       <c r="O50">
-        <v>7.875467424</v>
+        <v>7.800289662000001</v>
       </c>
       <c r="P50">
-        <v>27.922111776</v>
+        <v>27.655572438</v>
       </c>
       <c r="Q50">
-        <v>47.22211177600001</v>
+        <v>46.955572438</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1510874377611161</v>
+        <v>0.152887838543625</v>
       </c>
       <c r="T50">
-        <v>1.53206050826537</v>
+        <v>1.558258533372507</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5410,7 +5410,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.18245706755676</v>
+        <v>3.117508964137234</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5418,22 +5418,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1024718176572487</v>
+        <v>0.1023791276787171</v>
       </c>
       <c r="C51">
-        <v>311.8072604652742</v>
+        <v>307.276890696209</v>
       </c>
       <c r="D51">
-        <v>561.8262604652741</v>
+        <v>562.626890696209</v>
       </c>
       <c r="E51">
-        <v>-186.081</v>
+        <v>-180.75</v>
       </c>
       <c r="F51">
-        <v>261.219</v>
+        <v>266.55</v>
       </c>
       <c r="G51">
         <v>11.2</v>
@@ -5454,28 +5454,28 @@
         <v>52.2</v>
       </c>
       <c r="M51">
-        <v>16.7441379</v>
+        <v>17.085855</v>
       </c>
       <c r="N51">
-        <v>35.4558621</v>
+        <v>35.114145</v>
       </c>
       <c r="O51">
-        <v>7.800289662000001</v>
+        <v>7.7251119</v>
       </c>
       <c r="P51">
-        <v>27.655572438</v>
+        <v>27.3890331</v>
       </c>
       <c r="Q51">
-        <v>46.955572438</v>
+        <v>46.6890331</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.152887838543625</v>
+        <v>0.1547602553574342</v>
       </c>
       <c r="T51">
-        <v>1.558258533372507</v>
+        <v>1.585504479483929</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.117508964137234</v>
+        <v>3.055158784854489</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5500,22 +5500,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1023791276787171</v>
+        <v>0.1053892777001854</v>
       </c>
       <c r="C52">
-        <v>307.276890696209</v>
+        <v>277.0597113684409</v>
       </c>
       <c r="D52">
-        <v>562.626890696209</v>
+        <v>537.7407113684409</v>
       </c>
       <c r="E52">
-        <v>-180.75</v>
+        <v>-175.419</v>
       </c>
       <c r="F52">
-        <v>266.55</v>
+        <v>271.881</v>
       </c>
       <c r="G52">
         <v>11.2</v>
@@ -5536,45 +5536,45 @@
         <v>52.2</v>
       </c>
       <c r="M52">
-        <v>17.085855</v>
+        <v>19.5482439</v>
       </c>
       <c r="N52">
-        <v>35.114145</v>
+        <v>32.6517561</v>
       </c>
       <c r="O52">
-        <v>7.7251119</v>
+        <v>7.183386342</v>
       </c>
       <c r="P52">
-        <v>27.3890331</v>
+        <v>25.468369758</v>
       </c>
       <c r="Q52">
-        <v>46.6890331</v>
+        <v>44.76836975800001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1547602553574342</v>
+        <v>0.1567090973473172</v>
       </c>
       <c r="T52">
-        <v>1.585504479483929</v>
+        <v>1.613862505028471</v>
       </c>
       <c r="U52">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V52">
         <v>0.22</v>
       </c>
       <c r="W52">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>3.055158784854489</v>
+        <v>2.670316590432964</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5582,22 +5582,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1053892777001854</v>
+        <v>0.1053574277216538</v>
       </c>
       <c r="C53">
-        <v>277.0597113684409</v>
+        <v>271.9804993317634</v>
       </c>
       <c r="D53">
-        <v>537.7407113684409</v>
+        <v>537.9924993317634</v>
       </c>
       <c r="E53">
-        <v>-175.419</v>
+        <v>-170.088</v>
       </c>
       <c r="F53">
-        <v>271.881</v>
+        <v>277.212</v>
       </c>
       <c r="G53">
         <v>11.2</v>
@@ -5618,28 +5618,28 @@
         <v>52.2</v>
       </c>
       <c r="M53">
-        <v>19.5482439</v>
+        <v>19.93154280000001</v>
       </c>
       <c r="N53">
-        <v>32.6517561</v>
+        <v>32.2684572</v>
       </c>
       <c r="O53">
-        <v>7.183386342</v>
+        <v>7.099060584</v>
       </c>
       <c r="P53">
-        <v>25.468369758</v>
+        <v>25.169396616</v>
       </c>
       <c r="Q53">
-        <v>44.76836975800001</v>
+        <v>44.469396616</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1567090973473172</v>
+        <v>0.1587391410867787</v>
       </c>
       <c r="T53">
-        <v>1.613862505028471</v>
+        <v>1.643402114970702</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5656,7 +5656,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.670316590432964</v>
+        <v>2.618964348309254</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5664,22 +5664,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1053574277216538</v>
+        <v>0.1053255777431221</v>
       </c>
       <c r="C54">
-        <v>271.9804993317634</v>
+        <v>266.9015231964253</v>
       </c>
       <c r="D54">
-        <v>537.9924993317634</v>
+        <v>538.2445231964252</v>
       </c>
       <c r="E54">
-        <v>-170.088</v>
+        <v>-164.757</v>
       </c>
       <c r="F54">
-        <v>277.212</v>
+        <v>282.543</v>
       </c>
       <c r="G54">
         <v>11.2</v>
@@ -5700,28 +5700,28 @@
         <v>52.2</v>
       </c>
       <c r="M54">
-        <v>19.93154280000001</v>
+        <v>20.3148417</v>
       </c>
       <c r="N54">
-        <v>32.2684572</v>
+        <v>31.8851583</v>
       </c>
       <c r="O54">
-        <v>7.099060584</v>
+        <v>7.014734826</v>
       </c>
       <c r="P54">
-        <v>25.169396616</v>
+        <v>24.870423474</v>
       </c>
       <c r="Q54">
-        <v>44.469396616</v>
+        <v>44.170423474</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1587391410867787</v>
+        <v>0.1608555696662173</v>
       </c>
       <c r="T54">
-        <v>1.643402114970702</v>
+        <v>1.674198729591326</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.618964348309254</v>
+        <v>2.569549926643041</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5746,22 +5746,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1053255777431221</v>
+        <v>0.1052937277645905</v>
       </c>
       <c r="C55">
-        <v>266.9015231964253</v>
+        <v>261.8227832941076</v>
       </c>
       <c r="D55">
-        <v>538.2445231964252</v>
+        <v>538.4967832941076</v>
       </c>
       <c r="E55">
-        <v>-164.757</v>
+        <v>-159.426</v>
       </c>
       <c r="F55">
-        <v>282.543</v>
+        <v>287.874</v>
       </c>
       <c r="G55">
         <v>11.2</v>
@@ -5782,28 +5782,28 @@
         <v>52.2</v>
       </c>
       <c r="M55">
-        <v>20.3148417</v>
+        <v>20.6981406</v>
       </c>
       <c r="N55">
-        <v>31.8851583</v>
+        <v>31.5018594</v>
       </c>
       <c r="O55">
-        <v>7.014734826</v>
+        <v>6.930409068</v>
       </c>
       <c r="P55">
-        <v>24.870423474</v>
+        <v>24.571450332</v>
       </c>
       <c r="Q55">
-        <v>44.170423474</v>
+        <v>43.871450332</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1608555696662173</v>
+        <v>0.1630640168795444</v>
       </c>
       <c r="T55">
-        <v>1.674198729591326</v>
+        <v>1.706334327456325</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.569549926643041</v>
+        <v>2.521965668742244</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5828,22 +5828,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1052937277645905</v>
+        <v>0.1069349777860588</v>
       </c>
       <c r="C56">
-        <v>261.8227832941076</v>
+        <v>243.7932467076989</v>
       </c>
       <c r="D56">
-        <v>538.4967832941076</v>
+        <v>525.7982467076989</v>
       </c>
       <c r="E56">
-        <v>-159.426</v>
+        <v>-154.095</v>
       </c>
       <c r="F56">
-        <v>287.874</v>
+        <v>293.205</v>
       </c>
       <c r="G56">
         <v>11.2</v>
@@ -5864,45 +5864,45 @@
         <v>52.2</v>
       </c>
       <c r="M56">
-        <v>20.6981406</v>
+        <v>22.22493900000001</v>
       </c>
       <c r="N56">
-        <v>31.5018594</v>
+        <v>29.975061</v>
       </c>
       <c r="O56">
-        <v>6.930409068</v>
+        <v>6.594513419999999</v>
       </c>
       <c r="P56">
-        <v>24.571450332</v>
+        <v>23.38054758</v>
       </c>
       <c r="Q56">
-        <v>43.871450332</v>
+        <v>42.68054758</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1630640168795444</v>
+        <v>0.1653706173023528</v>
       </c>
       <c r="T56">
-        <v>1.706334327456325</v>
+        <v>1.739898174115323</v>
       </c>
       <c r="U56">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V56">
         <v>0.22</v>
       </c>
       <c r="W56">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.521965668742244</v>
+        <v>2.348712858109531</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5910,22 +5910,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1069349777860588</v>
+        <v>0.1069335478075271</v>
       </c>
       <c r="C57">
-        <v>243.7932467076989</v>
+        <v>238.4730499319331</v>
       </c>
       <c r="D57">
-        <v>525.7982467076989</v>
+        <v>525.8090499319331</v>
       </c>
       <c r="E57">
-        <v>-154.095</v>
+        <v>-148.764</v>
       </c>
       <c r="F57">
-        <v>293.205</v>
+        <v>298.5360000000001</v>
       </c>
       <c r="G57">
         <v>11.2</v>
@@ -5946,28 +5946,28 @@
         <v>52.2</v>
       </c>
       <c r="M57">
-        <v>22.22493900000001</v>
+        <v>22.62902880000001</v>
       </c>
       <c r="N57">
-        <v>29.975061</v>
+        <v>29.5709712</v>
       </c>
       <c r="O57">
-        <v>6.594513419999999</v>
+        <v>6.505613663999999</v>
       </c>
       <c r="P57">
-        <v>23.38054758</v>
+        <v>23.065357536</v>
       </c>
       <c r="Q57">
-        <v>42.68054758</v>
+        <v>42.365357536</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1653706173023528</v>
+        <v>0.1677820631989253</v>
       </c>
       <c r="T57">
-        <v>1.739898174115323</v>
+        <v>1.774987650167913</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.348712858109531</v>
+        <v>2.306771557071861</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5992,22 +5992,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1069335478075271</v>
+        <v>0.1069321178289955</v>
       </c>
       <c r="C58">
-        <v>238.4730499319331</v>
+        <v>233.1528536001099</v>
       </c>
       <c r="D58">
-        <v>525.8090499319331</v>
+        <v>525.8198536001099</v>
       </c>
       <c r="E58">
-        <v>-148.764</v>
+        <v>-143.433</v>
       </c>
       <c r="F58">
-        <v>298.5360000000001</v>
+        <v>303.867</v>
       </c>
       <c r="G58">
         <v>11.2</v>
@@ -6028,28 +6028,28 @@
         <v>52.2</v>
       </c>
       <c r="M58">
-        <v>22.62902880000001</v>
+        <v>23.0331186</v>
       </c>
       <c r="N58">
-        <v>29.5709712</v>
+        <v>29.1668814</v>
       </c>
       <c r="O58">
-        <v>6.505613663999999</v>
+        <v>6.416713908</v>
       </c>
       <c r="P58">
-        <v>23.065357536</v>
+        <v>22.750167492</v>
       </c>
       <c r="Q58">
-        <v>42.365357536</v>
+        <v>42.050167492</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1677820631989253</v>
+        <v>0.1703056693697569</v>
       </c>
       <c r="T58">
-        <v>1.774987650167913</v>
+        <v>1.811709194874111</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.306771557071861</v>
+        <v>2.266301880632004</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6074,22 +6074,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1069321178289955</v>
+        <v>0.1069306878504638</v>
       </c>
       <c r="C59">
-        <v>233.1528536001099</v>
+        <v>227.8326577122562</v>
       </c>
       <c r="D59">
-        <v>525.8198536001099</v>
+        <v>525.8306577122562</v>
       </c>
       <c r="E59">
-        <v>-143.433</v>
+        <v>-138.102</v>
       </c>
       <c r="F59">
-        <v>303.867</v>
+        <v>309.198</v>
       </c>
       <c r="G59">
         <v>11.2</v>
@@ -6110,28 +6110,28 @@
         <v>52.2</v>
       </c>
       <c r="M59">
-        <v>23.0331186</v>
+        <v>23.4372084</v>
       </c>
       <c r="N59">
-        <v>29.1668814</v>
+        <v>28.7627916</v>
       </c>
       <c r="O59">
-        <v>6.416713908</v>
+        <v>6.327814152</v>
       </c>
       <c r="P59">
-        <v>22.750167492</v>
+        <v>22.434977448</v>
       </c>
       <c r="Q59">
-        <v>42.050167492</v>
+        <v>41.734977448</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1703056693697569</v>
+        <v>0.172949447263009</v>
       </c>
       <c r="T59">
-        <v>1.811709194874111</v>
+        <v>1.850179384566319</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6148,7 +6148,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.266301880632004</v>
+        <v>2.22722771027628</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6156,22 +6156,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1069306878504638</v>
+        <v>0.1069292578719321</v>
       </c>
       <c r="C60">
-        <v>227.8326577122563</v>
+        <v>222.5124622683998</v>
       </c>
       <c r="D60">
-        <v>525.8306577122562</v>
+        <v>525.8414622683997</v>
       </c>
       <c r="E60">
-        <v>-138.102</v>
+        <v>-132.771</v>
       </c>
       <c r="F60">
-        <v>309.198</v>
+        <v>314.529</v>
       </c>
       <c r="G60">
         <v>11.2</v>
@@ -6192,28 +6192,28 @@
         <v>52.2</v>
       </c>
       <c r="M60">
-        <v>23.4372084</v>
+        <v>23.8412982</v>
       </c>
       <c r="N60">
-        <v>28.7627916</v>
+        <v>28.3587018</v>
       </c>
       <c r="O60">
-        <v>6.327814152000001</v>
+        <v>6.238914396</v>
       </c>
       <c r="P60">
-        <v>22.434977448</v>
+        <v>22.119787404</v>
       </c>
       <c r="Q60">
-        <v>41.734977448</v>
+        <v>41.419787404</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.172949447263009</v>
+        <v>0.1757221899315418</v>
       </c>
       <c r="T60">
-        <v>1.850179384566319</v>
+        <v>1.890526168877658</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.227227710276281</v>
+        <v>2.189478088068208</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6238,22 +6238,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1069292578719321</v>
+        <v>0.1069278278934005</v>
       </c>
       <c r="C61">
-        <v>222.5124622683998</v>
+        <v>217.1922672685677</v>
       </c>
       <c r="D61">
-        <v>525.8414622683997</v>
+        <v>525.8522672685676</v>
       </c>
       <c r="E61">
-        <v>-132.771</v>
+        <v>-127.44</v>
       </c>
       <c r="F61">
-        <v>314.529</v>
+        <v>319.86</v>
       </c>
       <c r="G61">
         <v>11.2</v>
@@ -6274,28 +6274,28 @@
         <v>52.2</v>
       </c>
       <c r="M61">
-        <v>23.8412982</v>
+        <v>24.245388</v>
       </c>
       <c r="N61">
-        <v>28.3587018</v>
+        <v>27.954612</v>
       </c>
       <c r="O61">
-        <v>6.238914396</v>
+        <v>6.15001464</v>
       </c>
       <c r="P61">
-        <v>22.119787404</v>
+        <v>21.80459736</v>
       </c>
       <c r="Q61">
-        <v>41.419787404</v>
+        <v>41.10459736</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1757221899315418</v>
+        <v>0.1786335697335012</v>
       </c>
       <c r="T61">
-        <v>1.890526168877658</v>
+        <v>1.932890292404565</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6312,7 +6312,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.189478088068208</v>
+        <v>2.152986786600404</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6320,22 +6320,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1069278278934005</v>
+        <v>0.1069263979148688</v>
       </c>
       <c r="C62">
-        <v>217.1922672685677</v>
+        <v>211.8720727127873</v>
       </c>
       <c r="D62">
-        <v>525.8522672685676</v>
+        <v>525.8630727127872</v>
       </c>
       <c r="E62">
-        <v>-127.44</v>
+        <v>-122.109</v>
       </c>
       <c r="F62">
-        <v>319.86</v>
+        <v>325.191</v>
       </c>
       <c r="G62">
         <v>11.2</v>
@@ -6356,28 +6356,28 @@
         <v>52.2</v>
       </c>
       <c r="M62">
-        <v>24.245388</v>
+        <v>24.6494778</v>
       </c>
       <c r="N62">
-        <v>27.954612</v>
+        <v>27.5505222</v>
       </c>
       <c r="O62">
-        <v>6.15001464</v>
+        <v>6.061114884</v>
       </c>
       <c r="P62">
-        <v>21.80459736</v>
+        <v>21.489407316</v>
       </c>
       <c r="Q62">
-        <v>41.10459736</v>
+        <v>40.78940731599999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1786335697335012</v>
+        <v>0.1816942510637662</v>
       </c>
       <c r="T62">
-        <v>1.932890292404565</v>
+        <v>1.977426935086698</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.152986786600404</v>
+        <v>2.117691921246299</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6402,22 +6402,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1069263979148688</v>
+        <v>0.1069249679363372</v>
       </c>
       <c r="C63">
-        <v>211.8720727127873</v>
+        <v>206.5518786010861</v>
       </c>
       <c r="D63">
-        <v>525.8630727127872</v>
+        <v>525.8738786010861</v>
       </c>
       <c r="E63">
-        <v>-122.109</v>
+        <v>-116.778</v>
       </c>
       <c r="F63">
-        <v>325.191</v>
+        <v>330.522</v>
       </c>
       <c r="G63">
         <v>11.2</v>
@@ -6438,28 +6438,28 @@
         <v>52.2</v>
       </c>
       <c r="M63">
-        <v>24.6494778</v>
+        <v>25.0535676</v>
       </c>
       <c r="N63">
-        <v>27.5505222</v>
+        <v>27.1464324</v>
       </c>
       <c r="O63">
-        <v>6.061114884</v>
+        <v>5.972215128</v>
       </c>
       <c r="P63">
-        <v>21.489407316</v>
+        <v>21.174217272</v>
       </c>
       <c r="Q63">
-        <v>40.78940731599999</v>
+        <v>40.474217272</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1816942510637662</v>
+        <v>0.1849160208850978</v>
       </c>
       <c r="T63">
-        <v>1.977426935086698</v>
+        <v>2.024307611594206</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6476,7 +6476,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.117691921246299</v>
+        <v>2.083535599935875</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6484,22 +6484,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1069249679363372</v>
+        <v>0.1069235379578055</v>
       </c>
       <c r="C64">
-        <v>206.5518786010861</v>
+        <v>201.2316849334915</v>
       </c>
       <c r="D64">
-        <v>525.8738786010861</v>
+        <v>525.8846849334915</v>
       </c>
       <c r="E64">
-        <v>-116.778</v>
+        <v>-111.447</v>
       </c>
       <c r="F64">
-        <v>330.522</v>
+        <v>335.853</v>
       </c>
       <c r="G64">
         <v>11.2</v>
@@ -6520,28 +6520,28 @@
         <v>52.2</v>
       </c>
       <c r="M64">
-        <v>25.0535676</v>
+        <v>25.4576574</v>
       </c>
       <c r="N64">
-        <v>27.1464324</v>
+        <v>26.7423426</v>
       </c>
       <c r="O64">
-        <v>5.972215128</v>
+        <v>5.883315372</v>
       </c>
       <c r="P64">
-        <v>21.174217272</v>
+        <v>20.859027228</v>
       </c>
       <c r="Q64">
-        <v>40.474217272</v>
+        <v>40.159027228</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1849160208850978</v>
+        <v>0.1883119404265013</v>
       </c>
       <c r="T64">
-        <v>2.024307611594206</v>
+        <v>2.073722378723742</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.083535599935875</v>
+        <v>2.050463606286099</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6566,22 +6566,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1069235379578055</v>
+        <v>0.1069221079792738</v>
       </c>
       <c r="C65">
-        <v>201.2316849334915</v>
+        <v>195.9114917100308</v>
       </c>
       <c r="D65">
-        <v>525.8846849334915</v>
+        <v>525.8954917100308</v>
       </c>
       <c r="E65">
-        <v>-111.447</v>
+        <v>-106.116</v>
       </c>
       <c r="F65">
-        <v>335.853</v>
+        <v>341.184</v>
       </c>
       <c r="G65">
         <v>11.2</v>
@@ -6602,28 +6602,28 @@
         <v>52.2</v>
       </c>
       <c r="M65">
-        <v>25.4576574</v>
+        <v>25.8617472</v>
       </c>
       <c r="N65">
-        <v>26.7423426</v>
+        <v>26.3382528</v>
       </c>
       <c r="O65">
-        <v>5.883315372</v>
+        <v>5.794415616</v>
       </c>
       <c r="P65">
-        <v>20.859027228</v>
+        <v>20.543837184</v>
       </c>
       <c r="Q65">
-        <v>40.159027228</v>
+        <v>39.84383718399999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1883119404265013</v>
+        <v>0.1918965221646495</v>
       </c>
       <c r="T65">
-        <v>2.073722378723742</v>
+        <v>2.125882410693808</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.050463606286099</v>
+        <v>2.018425112437879</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6648,22 +6648,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1069221079792738</v>
+        <v>0.1141200780007422</v>
       </c>
       <c r="C66">
-        <v>195.9114917100308</v>
+        <v>141.2816053545969</v>
       </c>
       <c r="D66">
-        <v>525.8954917100308</v>
+        <v>476.5966053545969</v>
       </c>
       <c r="E66">
-        <v>-106.116</v>
+        <v>-100.785</v>
       </c>
       <c r="F66">
-        <v>341.184</v>
+        <v>346.515</v>
       </c>
       <c r="G66">
         <v>11.2</v>
@@ -6684,45 +6684,45 @@
         <v>52.2</v>
       </c>
       <c r="M66">
-        <v>25.8617472</v>
+        <v>31.18635</v>
       </c>
       <c r="N66">
-        <v>26.3382528</v>
+        <v>21.01365</v>
       </c>
       <c r="O66">
-        <v>5.794415616</v>
+        <v>4.623003</v>
       </c>
       <c r="P66">
-        <v>20.543837184</v>
+        <v>16.390647</v>
       </c>
       <c r="Q66">
-        <v>39.84383718399999</v>
+        <v>35.690647</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1918965221646495</v>
+        <v>0.1956859371449776</v>
       </c>
       <c r="T66">
-        <v>2.125882410693808</v>
+        <v>2.181023015919306</v>
       </c>
       <c r="U66">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V66">
         <v>0.22</v>
       </c>
       <c r="W66">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.018425112437879</v>
+        <v>1.673809214608314</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6730,22 +6730,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1141200780007422</v>
+        <v>0.1142294080222105</v>
       </c>
       <c r="C67">
-        <v>141.2816053545969</v>
+        <v>135.2729637359602</v>
       </c>
       <c r="D67">
-        <v>476.5966053545969</v>
+        <v>475.9189637359602</v>
       </c>
       <c r="E67">
-        <v>-100.785</v>
+        <v>-95.45400000000001</v>
       </c>
       <c r="F67">
-        <v>346.515</v>
+        <v>351.846</v>
       </c>
       <c r="G67">
         <v>11.2</v>
@@ -6766,28 +6766,28 @@
         <v>52.2</v>
       </c>
       <c r="M67">
-        <v>31.18635</v>
+        <v>31.66614</v>
       </c>
       <c r="N67">
-        <v>21.01365</v>
+        <v>20.53386</v>
       </c>
       <c r="O67">
-        <v>4.623003</v>
+        <v>4.517449200000001</v>
       </c>
       <c r="P67">
-        <v>16.390647</v>
+        <v>16.0164108</v>
       </c>
       <c r="Q67">
-        <v>35.690647</v>
+        <v>35.3164108</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1956859371449776</v>
+        <v>0.1996982588888545</v>
       </c>
       <c r="T67">
-        <v>2.181023015919306</v>
+        <v>2.239407186158068</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6804,7 +6804,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.673809214608314</v>
+        <v>1.648448468932431</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6812,22 +6812,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1142294080222105</v>
+        <v>0.1143387380436789</v>
       </c>
       <c r="C68">
-        <v>135.2729637359602</v>
+        <v>129.2662463701666</v>
       </c>
       <c r="D68">
-        <v>475.9189637359602</v>
+        <v>475.2432463701667</v>
       </c>
       <c r="E68">
-        <v>-95.45400000000001</v>
+        <v>-90.12299999999999</v>
       </c>
       <c r="F68">
-        <v>351.846</v>
+        <v>357.177</v>
       </c>
       <c r="G68">
         <v>11.2</v>
@@ -6848,28 +6848,28 @@
         <v>52.2</v>
       </c>
       <c r="M68">
-        <v>31.66614</v>
+        <v>32.14593</v>
       </c>
       <c r="N68">
-        <v>20.53386</v>
+        <v>20.05407</v>
       </c>
       <c r="O68">
-        <v>4.517449200000001</v>
+        <v>4.411895400000001</v>
       </c>
       <c r="P68">
-        <v>16.0164108</v>
+        <v>15.6421746</v>
       </c>
       <c r="Q68">
-        <v>35.3164108</v>
+        <v>34.9421746</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1996982588888545</v>
+        <v>0.2039537516475117</v>
       </c>
       <c r="T68">
-        <v>2.239407186158068</v>
+        <v>2.301329790956756</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.648448468932431</v>
+        <v>1.623844760440902</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6894,22 +6894,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1143387380436789</v>
+        <v>0.1144480680651472</v>
       </c>
       <c r="C69">
-        <v>129.2662463701666</v>
+        <v>123.2614450725818</v>
       </c>
       <c r="D69">
-        <v>475.2432463701667</v>
+        <v>474.5694450725818</v>
       </c>
       <c r="E69">
-        <v>-90.12299999999999</v>
+        <v>-84.79199999999997</v>
       </c>
       <c r="F69">
-        <v>357.177</v>
+        <v>362.508</v>
       </c>
       <c r="G69">
         <v>11.2</v>
@@ -6930,28 +6930,28 @@
         <v>52.2</v>
       </c>
       <c r="M69">
-        <v>32.14593</v>
+        <v>32.62572</v>
       </c>
       <c r="N69">
-        <v>20.05407</v>
+        <v>19.57428</v>
       </c>
       <c r="O69">
-        <v>4.411895400000001</v>
+        <v>4.306341600000001</v>
       </c>
       <c r="P69">
-        <v>15.6421746</v>
+        <v>15.2679384</v>
       </c>
       <c r="Q69">
-        <v>34.9421746</v>
+        <v>34.5679384</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2039537516475117</v>
+        <v>0.208475212703585</v>
       </c>
       <c r="T69">
-        <v>2.301329790956756</v>
+        <v>2.367122558555361</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.623844760440902</v>
+        <v>1.599964690434418</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6976,22 +6976,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1144480680651472</v>
+        <v>0.1145573980866155</v>
       </c>
       <c r="C70">
-        <v>123.2614450725818</v>
+        <v>117.2585517049222</v>
       </c>
       <c r="D70">
-        <v>474.5694450725818</v>
+        <v>473.8975517049223</v>
       </c>
       <c r="E70">
-        <v>-84.79199999999997</v>
+        <v>-79.46099999999996</v>
       </c>
       <c r="F70">
-        <v>362.508</v>
+        <v>367.8390000000001</v>
       </c>
       <c r="G70">
         <v>11.2</v>
@@ -7012,28 +7012,28 @@
         <v>52.2</v>
       </c>
       <c r="M70">
-        <v>32.62572</v>
+        <v>33.10551</v>
       </c>
       <c r="N70">
-        <v>19.57428</v>
+        <v>19.09449</v>
       </c>
       <c r="O70">
-        <v>4.306341600000001</v>
+        <v>4.200787800000001</v>
       </c>
       <c r="P70">
-        <v>15.2679384</v>
+        <v>14.8937022</v>
       </c>
       <c r="Q70">
-        <v>34.5679384</v>
+        <v>34.1937022</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.208475212703585</v>
+        <v>0.2132883809245663</v>
       </c>
       <c r="T70">
-        <v>2.367122558555361</v>
+        <v>2.437160020837748</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.599964690434418</v>
+        <v>1.576776796370151</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7058,22 +7058,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1145573980866155</v>
+        <v>0.1146667281080839</v>
       </c>
       <c r="C71">
-        <v>117.2585517049222</v>
+        <v>111.2575581749282</v>
       </c>
       <c r="D71">
-        <v>473.8975517049223</v>
+        <v>473.2275581749283</v>
       </c>
       <c r="E71">
-        <v>-79.46099999999996</v>
+        <v>-74.12999999999994</v>
       </c>
       <c r="F71">
-        <v>367.8390000000001</v>
+        <v>373.1700000000001</v>
       </c>
       <c r="G71">
         <v>11.2</v>
@@ -7094,28 +7094,28 @@
         <v>52.2</v>
       </c>
       <c r="M71">
-        <v>33.10551</v>
+        <v>33.5853</v>
       </c>
       <c r="N71">
-        <v>19.09449</v>
+        <v>18.6147</v>
       </c>
       <c r="O71">
-        <v>4.200787800000001</v>
+        <v>4.095234</v>
       </c>
       <c r="P71">
-        <v>14.8937022</v>
+        <v>14.519466</v>
       </c>
       <c r="Q71">
-        <v>34.1937022</v>
+        <v>33.819466</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2132883809245663</v>
+        <v>0.2184224270269463</v>
       </c>
       <c r="T71">
-        <v>2.437160020837748</v>
+        <v>2.511866647272293</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7132,7 +7132,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.576776796370151</v>
+        <v>1.554251413564863</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7140,22 +7140,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1146667281080839</v>
+        <v>0.1147760581295522</v>
       </c>
       <c r="C72">
-        <v>111.2575581749282</v>
+        <v>105.2584564360386</v>
       </c>
       <c r="D72">
-        <v>473.2275581749283</v>
+        <v>472.5594564360386</v>
       </c>
       <c r="E72">
-        <v>-74.12999999999994</v>
+        <v>-68.79899999999998</v>
       </c>
       <c r="F72">
-        <v>373.1700000000001</v>
+        <v>378.501</v>
       </c>
       <c r="G72">
         <v>11.2</v>
@@ -7176,28 +7176,28 @@
         <v>52.2</v>
       </c>
       <c r="M72">
-        <v>33.5853</v>
+        <v>34.06509</v>
       </c>
       <c r="N72">
-        <v>18.6147</v>
+        <v>18.13491</v>
       </c>
       <c r="O72">
-        <v>4.095234</v>
+        <v>3.9896802</v>
       </c>
       <c r="P72">
-        <v>14.519466</v>
+        <v>14.1452298</v>
       </c>
       <c r="Q72">
-        <v>33.819466</v>
+        <v>33.4452298</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2184224270269463</v>
+        <v>0.223910545274318</v>
       </c>
       <c r="T72">
-        <v>2.511866647272293</v>
+        <v>2.591725454840256</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7214,7 +7214,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.554251413564863</v>
+        <v>1.532360548585076</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7222,22 +7222,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1147760581295522</v>
+        <v>0.1148853881510206</v>
       </c>
       <c r="C73">
-        <v>105.2584564360386</v>
+        <v>99.26123848706834</v>
       </c>
       <c r="D73">
-        <v>472.5594564360386</v>
+        <v>471.8932384870683</v>
       </c>
       <c r="E73">
-        <v>-68.79900000000004</v>
+        <v>-63.46800000000002</v>
       </c>
       <c r="F73">
-        <v>378.501</v>
+        <v>383.832</v>
       </c>
       <c r="G73">
         <v>11.2</v>
@@ -7258,28 +7258,28 @@
         <v>52.2</v>
       </c>
       <c r="M73">
-        <v>34.06509</v>
+        <v>34.54488</v>
       </c>
       <c r="N73">
-        <v>18.13491</v>
+        <v>17.65512</v>
       </c>
       <c r="O73">
-        <v>3.989680200000001</v>
+        <v>3.884126400000001</v>
       </c>
       <c r="P73">
-        <v>14.1452298</v>
+        <v>13.7709936</v>
       </c>
       <c r="Q73">
-        <v>33.44522980000001</v>
+        <v>33.0709936</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.223910545274318</v>
+        <v>0.2297906719679305</v>
       </c>
       <c r="T73">
-        <v>2.591725454840255</v>
+        <v>2.677288462948786</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.532360548585077</v>
+        <v>1.511077763188061</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7304,22 +7304,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1148853881510206</v>
+        <v>0.1502190090409834</v>
       </c>
       <c r="C74">
-        <v>99.26123848706834</v>
+        <v>-53.77724756880593</v>
       </c>
       <c r="D74">
-        <v>471.8932384870683</v>
+        <v>324.1857524311941</v>
       </c>
       <c r="E74">
-        <v>-63.46800000000002</v>
+        <v>-58.137</v>
       </c>
       <c r="F74">
-        <v>383.832</v>
+        <v>389.163</v>
       </c>
       <c r="G74">
         <v>11.2</v>
@@ -7340,45 +7340,45 @@
         <v>52.2</v>
       </c>
       <c r="M74">
-        <v>34.54488</v>
+        <v>57.12912840000001</v>
       </c>
       <c r="N74">
-        <v>17.65512</v>
+        <v>-4.929128400000003</v>
       </c>
       <c r="O74">
-        <v>3.884126400000001</v>
+        <v>-1.084408248000001</v>
       </c>
       <c r="P74">
-        <v>13.7709936</v>
+        <v>-3.844720152000002</v>
       </c>
       <c r="Q74">
-        <v>33.0709936</v>
+        <v>15.455279848</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2297906719679305</v>
+        <v>0.2392479023444162</v>
       </c>
       <c r="T74">
-        <v>2.677288462948786</v>
+        <v>2.814902688211396</v>
       </c>
       <c r="U74">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.22</v>
+        <v>0.2010182952484883</v>
       </c>
       <c r="W74">
-        <v>0.0702</v>
+        <v>0.1172905142575219</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y74">
-        <v>1.511077763188061</v>
+        <v>0.9137195238567651</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7386,22 +7386,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1502190090409834</v>
+        <v>0.1512290090409834</v>
       </c>
       <c r="C75">
-        <v>-53.77724756880593</v>
+        <v>-61.98311235119127</v>
       </c>
       <c r="D75">
-        <v>324.1857524311941</v>
+        <v>321.3108876488088</v>
       </c>
       <c r="E75">
-        <v>-58.137</v>
+        <v>-52.80599999999998</v>
       </c>
       <c r="F75">
-        <v>389.163</v>
+        <v>394.494</v>
       </c>
       <c r="G75">
         <v>11.2</v>
@@ -7422,37 +7422,37 @@
         <v>52.2</v>
       </c>
       <c r="M75">
-        <v>57.12912840000001</v>
+        <v>57.91171920000001</v>
       </c>
       <c r="N75">
-        <v>-4.929128400000003</v>
+        <v>-5.711719200000005</v>
       </c>
       <c r="O75">
-        <v>-1.084408248000001</v>
+        <v>-1.256578224000001</v>
       </c>
       <c r="P75">
-        <v>-3.844720152000002</v>
+        <v>-4.455140976000004</v>
       </c>
       <c r="Q75">
-        <v>15.455279848</v>
+        <v>14.844859024</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2392479023444162</v>
+        <v>0.2466882062807399</v>
       </c>
       <c r="T75">
-        <v>2.814902688211396</v>
+        <v>2.923168176219527</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2010182952484883</v>
+        <v>0.1983018317991844</v>
       </c>
       <c r="W75">
-        <v>0.1172905142575219</v>
+        <v>0.1176892910918797</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.9137195238567651</v>
+        <v>0.9013719627235656</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7468,22 +7468,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1512290090409834</v>
+        <v>0.1522390090409834</v>
       </c>
       <c r="C76">
-        <v>-61.98311235119127</v>
+        <v>-70.13843697629704</v>
       </c>
       <c r="D76">
-        <v>321.3108876488088</v>
+        <v>318.486563023703</v>
       </c>
       <c r="E76">
-        <v>-52.80599999999998</v>
+        <v>-47.47499999999997</v>
       </c>
       <c r="F76">
-        <v>394.494</v>
+        <v>399.825</v>
       </c>
       <c r="G76">
         <v>11.2</v>
@@ -7504,37 +7504,37 @@
         <v>52.2</v>
       </c>
       <c r="M76">
-        <v>57.91171920000001</v>
+        <v>58.69431000000002</v>
       </c>
       <c r="N76">
-        <v>-5.711719200000005</v>
+        <v>-6.494310000000013</v>
       </c>
       <c r="O76">
-        <v>-1.256578224000001</v>
+        <v>-1.428748200000003</v>
       </c>
       <c r="P76">
-        <v>-4.455140976000004</v>
+        <v>-5.06556180000001</v>
       </c>
       <c r="Q76">
-        <v>14.844859024</v>
+        <v>14.23443819999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2466882062807399</v>
+        <v>0.2547237345319695</v>
       </c>
       <c r="T76">
-        <v>2.923168176219527</v>
+        <v>3.040094903268308</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1983018317991844</v>
+        <v>0.1956578073751953</v>
       </c>
       <c r="W76">
-        <v>0.1176892910918797</v>
+        <v>0.1180774338773213</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.9013719627235656</v>
+        <v>0.8893536698872513</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7550,22 +7550,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1522390090409834</v>
+        <v>0.1532490090409834</v>
       </c>
       <c r="C77">
-        <v>-70.13843697629704</v>
+        <v>-78.24454257621875</v>
       </c>
       <c r="D77">
-        <v>318.486563023703</v>
+        <v>315.7114574237813</v>
       </c>
       <c r="E77">
-        <v>-47.47499999999997</v>
+        <v>-42.14400000000001</v>
       </c>
       <c r="F77">
-        <v>399.825</v>
+        <v>405.156</v>
       </c>
       <c r="G77">
         <v>11.2</v>
@@ -7586,37 +7586,37 @@
         <v>52.2</v>
       </c>
       <c r="M77">
-        <v>58.69431000000002</v>
+        <v>59.47690080000001</v>
       </c>
       <c r="N77">
-        <v>-6.494310000000013</v>
+        <v>-7.276900800000007</v>
       </c>
       <c r="O77">
-        <v>-1.428748200000003</v>
+        <v>-1.600918176000002</v>
       </c>
       <c r="P77">
-        <v>-5.06556180000001</v>
+        <v>-5.675982624000006</v>
       </c>
       <c r="Q77">
-        <v>14.23443819999999</v>
+        <v>13.62401737599999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2547237345319695</v>
+        <v>0.2634288901374683</v>
       </c>
       <c r="T77">
-        <v>3.040094903268308</v>
+        <v>3.166765524237821</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1956578073751953</v>
+        <v>0.1930833625413111</v>
       </c>
       <c r="W77">
-        <v>0.1180774338773213</v>
+        <v>0.1184553623789355</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8893536698872513</v>
+        <v>0.8776516479150507</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7632,22 +7632,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1532490090409834</v>
+        <v>0.1542590090409834</v>
       </c>
       <c r="C78">
-        <v>-78.24454257621875</v>
+        <v>-86.30270463451762</v>
       </c>
       <c r="D78">
-        <v>315.7114574237813</v>
+        <v>312.9842953654824</v>
       </c>
       <c r="E78">
-        <v>-42.14400000000001</v>
+        <v>-36.81299999999999</v>
       </c>
       <c r="F78">
-        <v>405.156</v>
+        <v>410.487</v>
       </c>
       <c r="G78">
         <v>11.2</v>
@@ -7668,37 +7668,37 @@
         <v>52.2</v>
       </c>
       <c r="M78">
-        <v>59.47690080000001</v>
+        <v>60.25949160000001</v>
       </c>
       <c r="N78">
-        <v>-7.276900800000007</v>
+        <v>-8.059491600000008</v>
       </c>
       <c r="O78">
-        <v>-1.600918176000002</v>
+        <v>-1.773088152000002</v>
       </c>
       <c r="P78">
-        <v>-5.675982624000006</v>
+        <v>-6.286403448000007</v>
       </c>
       <c r="Q78">
-        <v>13.62401737599999</v>
+        <v>13.01359655199999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2634288901374683</v>
+        <v>0.2728910157956191</v>
       </c>
       <c r="T78">
-        <v>3.166765524237821</v>
+        <v>3.304450981813379</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1930833625413111</v>
+        <v>0.190575786404411</v>
       </c>
       <c r="W78">
-        <v>0.1184553623789355</v>
+        <v>0.1188234745558325</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8776516479150507</v>
+        <v>0.8662535745655046</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7714,22 +7714,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1542590090409834</v>
+        <v>0.1552690090409834</v>
       </c>
       <c r="C79">
-        <v>-86.30270463451762</v>
+        <v>-94.31415494092971</v>
       </c>
       <c r="D79">
-        <v>312.9842953654824</v>
+        <v>310.3038450590703</v>
       </c>
       <c r="E79">
-        <v>-36.81299999999999</v>
+        <v>-31.48199999999997</v>
       </c>
       <c r="F79">
-        <v>410.487</v>
+        <v>415.818</v>
       </c>
       <c r="G79">
         <v>11.2</v>
@@ -7750,37 +7750,37 @@
         <v>52.2</v>
       </c>
       <c r="M79">
-        <v>60.25949160000001</v>
+        <v>61.04208240000001</v>
       </c>
       <c r="N79">
-        <v>-8.059491600000008</v>
+        <v>-8.84208240000001</v>
       </c>
       <c r="O79">
-        <v>-1.773088152000002</v>
+        <v>-1.945258128000002</v>
       </c>
       <c r="P79">
-        <v>-6.286403448000007</v>
+        <v>-6.896824272000007</v>
       </c>
       <c r="Q79">
-        <v>13.01359655199999</v>
+        <v>12.40317572799999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2728910157956191</v>
+        <v>0.2832133346954199</v>
       </c>
       <c r="T79">
-        <v>3.304450981813379</v>
+        <v>3.454653299168533</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.190575786404411</v>
+        <v>0.1881325070915339</v>
       </c>
       <c r="W79">
-        <v>0.1188234745558325</v>
+        <v>0.1191821479589628</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8662535745655046</v>
+        <v>0.8551477595069724</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7796,22 +7796,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1552690090409834</v>
+        <v>0.1562790090409834</v>
       </c>
       <c r="C80">
-        <v>-94.31415494092971</v>
+        <v>-102.280083446484</v>
       </c>
       <c r="D80">
-        <v>310.3038450590703</v>
+        <v>307.6689165535161</v>
       </c>
       <c r="E80">
-        <v>-31.48199999999997</v>
+        <v>-26.15099999999995</v>
       </c>
       <c r="F80">
-        <v>415.818</v>
+        <v>421.1490000000001</v>
       </c>
       <c r="G80">
         <v>11.2</v>
@@ -7832,37 +7832,37 @@
         <v>52.2</v>
       </c>
       <c r="M80">
-        <v>61.04208240000001</v>
+        <v>61.82467320000001</v>
       </c>
       <c r="N80">
-        <v>-8.84208240000001</v>
+        <v>-9.624673200000011</v>
       </c>
       <c r="O80">
-        <v>-1.945258128000002</v>
+        <v>-2.117428104000002</v>
       </c>
       <c r="P80">
-        <v>-6.896824272000007</v>
+        <v>-7.507245096000009</v>
       </c>
       <c r="Q80">
-        <v>12.40317572799999</v>
+        <v>11.79275490399999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2832133346954199</v>
+        <v>0.294518731585678</v>
       </c>
       <c r="T80">
-        <v>3.454653299168533</v>
+        <v>3.619160599128939</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1881325070915339</v>
+        <v>0.1857510829511348</v>
       </c>
       <c r="W80">
-        <v>0.1191821479589628</v>
+        <v>0.1195317410227734</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8551477595069724</v>
+        <v>0.8443231043233398</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7878,22 +7878,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1562790090409834</v>
+        <v>0.1572890090409834</v>
       </c>
       <c r="C81">
-        <v>-102.280083446484</v>
+        <v>-110.2016400249018</v>
       </c>
       <c r="D81">
-        <v>307.6689165535161</v>
+        <v>305.0783599750982</v>
       </c>
       <c r="E81">
-        <v>-26.15099999999995</v>
+        <v>-20.81999999999999</v>
       </c>
       <c r="F81">
-        <v>421.1490000000001</v>
+        <v>426.48</v>
       </c>
       <c r="G81">
         <v>11.2</v>
@@ -7914,37 +7914,37 @@
         <v>52.2</v>
       </c>
       <c r="M81">
-        <v>61.82467320000001</v>
+        <v>62.60726400000001</v>
       </c>
       <c r="N81">
-        <v>-9.624673200000011</v>
+        <v>-10.407264</v>
       </c>
       <c r="O81">
-        <v>-2.117428104000002</v>
+        <v>-2.289598080000001</v>
       </c>
       <c r="P81">
-        <v>-7.507245096000009</v>
+        <v>-8.117665920000004</v>
       </c>
       <c r="Q81">
-        <v>11.79275490399999</v>
+        <v>11.18233408</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.294518731585678</v>
+        <v>0.306954668164962</v>
       </c>
       <c r="T81">
-        <v>3.619160599128939</v>
+        <v>3.800118629085386</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1857510829511348</v>
+        <v>0.1834291944142456</v>
       </c>
       <c r="W81">
-        <v>0.1195317410227734</v>
+        <v>0.1198725942599888</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8443231043233398</v>
+        <v>0.8337690655192982</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7960,22 +7960,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1572890090409834</v>
+        <v>0.1582990090409834</v>
       </c>
       <c r="C82">
-        <v>-110.2016400249018</v>
+        <v>-118.0799361457535</v>
       </c>
       <c r="D82">
-        <v>305.0783599750982</v>
+        <v>302.5310638542466</v>
       </c>
       <c r="E82">
-        <v>-20.81999999999999</v>
+        <v>-15.48899999999998</v>
       </c>
       <c r="F82">
-        <v>426.48</v>
+        <v>431.811</v>
       </c>
       <c r="G82">
         <v>11.2</v>
@@ -7996,37 +7996,37 @@
         <v>52.2</v>
       </c>
       <c r="M82">
-        <v>62.60726400000001</v>
+        <v>63.38985480000001</v>
       </c>
       <c r="N82">
-        <v>-10.407264</v>
+        <v>-11.18985480000001</v>
       </c>
       <c r="O82">
-        <v>-2.289598080000001</v>
+        <v>-2.461768056000001</v>
       </c>
       <c r="P82">
-        <v>-8.117665920000004</v>
+        <v>-8.728086744000006</v>
       </c>
       <c r="Q82">
-        <v>11.18233408</v>
+        <v>10.57191325599999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.306954668164962</v>
+        <v>0.32069965069996</v>
       </c>
       <c r="T82">
-        <v>3.800118629085386</v>
+        <v>4.000124872721459</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1834291944142456</v>
+        <v>0.1811646364585142</v>
       </c>
       <c r="W82">
-        <v>0.1198725942599888</v>
+        <v>0.1202050313678901</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8337690655192982</v>
+        <v>0.8234756202659734</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8042,22 +8042,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1582990090409834</v>
+        <v>0.1593090090409834</v>
       </c>
       <c r="C83">
-        <v>-118.0799361457535</v>
+        <v>-125.9160464644866</v>
       </c>
       <c r="D83">
-        <v>302.5310638542466</v>
+        <v>300.0259535355135</v>
       </c>
       <c r="E83">
-        <v>-15.48899999999998</v>
+        <v>-10.15799999999996</v>
       </c>
       <c r="F83">
-        <v>431.811</v>
+        <v>437.1420000000001</v>
       </c>
       <c r="G83">
         <v>11.2</v>
@@ -8078,37 +8078,37 @@
         <v>52.2</v>
       </c>
       <c r="M83">
-        <v>63.38985480000001</v>
+        <v>64.17244560000002</v>
       </c>
       <c r="N83">
-        <v>-11.18985480000001</v>
+        <v>-11.97244560000001</v>
       </c>
       <c r="O83">
-        <v>-2.461768056000001</v>
+        <v>-2.633938032000003</v>
       </c>
       <c r="P83">
-        <v>-8.728086744000006</v>
+        <v>-9.338507568000011</v>
       </c>
       <c r="Q83">
-        <v>10.57191325599999</v>
+        <v>9.961492431999989</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.32069965069996</v>
+        <v>0.3359718535166244</v>
       </c>
       <c r="T83">
-        <v>4.000124872721459</v>
+        <v>4.222354032317096</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1811646364585142</v>
+        <v>0.1789553116236542</v>
       </c>
       <c r="W83">
-        <v>0.1202050313678901</v>
+        <v>0.1205293602536476</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8234756202659734</v>
+        <v>0.8134332346529737</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8124,22 +8124,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1593090090409834</v>
+        <v>0.1603190090409834</v>
       </c>
       <c r="C84">
-        <v>-125.9160464644866</v>
+        <v>-133.7110103341074</v>
       </c>
       <c r="D84">
-        <v>300.0259535355135</v>
+        <v>297.5619896658927</v>
       </c>
       <c r="E84">
-        <v>-10.15799999999996</v>
+        <v>-4.826999999999941</v>
       </c>
       <c r="F84">
-        <v>437.1420000000001</v>
+        <v>442.4730000000001</v>
       </c>
       <c r="G84">
         <v>11.2</v>
@@ -8160,37 +8160,37 @@
         <v>52.2</v>
       </c>
       <c r="M84">
-        <v>64.17244560000002</v>
+        <v>64.95503640000001</v>
       </c>
       <c r="N84">
-        <v>-11.97244560000001</v>
+        <v>-12.75503640000001</v>
       </c>
       <c r="O84">
-        <v>-2.633938032000003</v>
+        <v>-2.806108008000002</v>
       </c>
       <c r="P84">
-        <v>-9.338507568000011</v>
+        <v>-9.948928392000006</v>
       </c>
       <c r="Q84">
-        <v>9.961492431999989</v>
+        <v>9.351071607999994</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3359718535166244</v>
+        <v>0.3530407860764259</v>
       </c>
       <c r="T84">
-        <v>4.222354032317096</v>
+        <v>4.470727798923985</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1789553116236542</v>
+        <v>0.176799223531803</v>
       </c>
       <c r="W84">
-        <v>0.1205293602536476</v>
+        <v>0.1208458739855313</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8134332346529737</v>
+        <v>0.8036328342354681</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8206,22 +8206,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1603190090409834</v>
+        <v>0.2091046734857275</v>
       </c>
       <c r="C85">
-        <v>-133.7110103341074</v>
+        <v>-223.5553338224042</v>
       </c>
       <c r="D85">
-        <v>297.5619896658927</v>
+        <v>213.0486661775959</v>
       </c>
       <c r="E85">
-        <v>-4.826999999999941</v>
+        <v>0.5040000000000759</v>
       </c>
       <c r="F85">
-        <v>442.4730000000001</v>
+        <v>447.8040000000001</v>
       </c>
       <c r="G85">
         <v>11.2</v>
@@ -8242,45 +8242,45 @@
         <v>52.2</v>
       </c>
       <c r="M85">
-        <v>64.95503640000001</v>
+        <v>89.91904320000002</v>
       </c>
       <c r="N85">
-        <v>-12.75503640000001</v>
+        <v>-37.71904320000002</v>
       </c>
       <c r="O85">
-        <v>-2.806108008000002</v>
+        <v>-8.298189504000003</v>
       </c>
       <c r="P85">
-        <v>-9.948928392000006</v>
+        <v>-29.42085369600001</v>
       </c>
       <c r="Q85">
-        <v>9.351071607999994</v>
+        <v>-10.12085369600001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3530407860764259</v>
+        <v>0.3873412379858532</v>
       </c>
       <c r="T85">
-        <v>4.470727798923985</v>
+        <v>4.969841168035685</v>
       </c>
       <c r="U85">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.176799223531803</v>
+        <v>0.1277148820907383</v>
       </c>
       <c r="W85">
-        <v>0.1208458739855313</v>
+        <v>0.1751548516761798</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.8036328342354681</v>
+        <v>0.5805221913215375</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8288,22 +8288,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2091046734857275</v>
+        <v>0.2106546734857275</v>
       </c>
       <c r="C86">
-        <v>-223.5553338224041</v>
+        <v>-230.7916393623107</v>
       </c>
       <c r="D86">
-        <v>213.048666177596</v>
+        <v>211.1433606376893</v>
       </c>
       <c r="E86">
-        <v>0.5040000000000191</v>
+        <v>5.83499999999998</v>
       </c>
       <c r="F86">
-        <v>447.804</v>
+        <v>453.135</v>
       </c>
       <c r="G86">
         <v>11.2</v>
@@ -8324,37 +8324,37 @@
         <v>52.2</v>
       </c>
       <c r="M86">
-        <v>89.9190432</v>
+        <v>90.989508</v>
       </c>
       <c r="N86">
-        <v>-37.7190432</v>
+        <v>-38.789508</v>
       </c>
       <c r="O86">
-        <v>-8.298189504</v>
+        <v>-8.53369176</v>
       </c>
       <c r="P86">
-        <v>-29.420853696</v>
+        <v>-30.25581624</v>
       </c>
       <c r="Q86">
-        <v>-10.120853696</v>
+        <v>-10.95581624</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.387341237985853</v>
+        <v>0.4101106538515766</v>
       </c>
       <c r="T86">
-        <v>4.969841168035681</v>
+        <v>5.301163912571394</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1277148820907383</v>
+        <v>0.1262123540661413</v>
       </c>
       <c r="W86">
-        <v>0.1751548516761798</v>
+        <v>0.1754565593035188</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5805221913215375</v>
+        <v>0.5736925184824606</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8370,22 +8370,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2106546734857275</v>
+        <v>0.2122046734857275</v>
       </c>
       <c r="C87">
-        <v>-230.7916393623107</v>
+        <v>-237.9941684693242</v>
       </c>
       <c r="D87">
-        <v>211.1433606376893</v>
+        <v>209.2718315306758</v>
       </c>
       <c r="E87">
-        <v>5.83499999999998</v>
+        <v>11.166</v>
       </c>
       <c r="F87">
-        <v>453.135</v>
+        <v>458.466</v>
       </c>
       <c r="G87">
         <v>11.2</v>
@@ -8406,37 +8406,37 @@
         <v>52.2</v>
       </c>
       <c r="M87">
-        <v>90.989508</v>
+        <v>92.05997280000001</v>
       </c>
       <c r="N87">
-        <v>-38.789508</v>
+        <v>-39.85997280000001</v>
       </c>
       <c r="O87">
-        <v>-8.53369176</v>
+        <v>-8.769194016000002</v>
       </c>
       <c r="P87">
-        <v>-30.25581624</v>
+        <v>-31.09077878400001</v>
       </c>
       <c r="Q87">
-        <v>-10.95581624</v>
+        <v>-11.79077878400001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4101106538515766</v>
+        <v>0.4361328434124034</v>
       </c>
       <c r="T87">
-        <v>5.301163912571394</v>
+        <v>5.679818477755064</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1262123540661413</v>
+        <v>0.1247447685537443</v>
       </c>
       <c r="W87">
-        <v>0.1754565593035188</v>
+        <v>0.1757512504744081</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5736925184824606</v>
+        <v>0.5670216752442925</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8452,22 +8452,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2122046734857275</v>
+        <v>0.2137546734857275</v>
       </c>
       <c r="C88">
-        <v>-237.9941684693242</v>
+        <v>-245.1638114132851</v>
       </c>
       <c r="D88">
-        <v>209.2718315306758</v>
+        <v>207.4331885867149</v>
       </c>
       <c r="E88">
-        <v>11.166</v>
+        <v>16.49700000000001</v>
       </c>
       <c r="F88">
-        <v>458.466</v>
+        <v>463.797</v>
       </c>
       <c r="G88">
         <v>11.2</v>
@@ -8488,37 +8488,37 @@
         <v>52.2</v>
       </c>
       <c r="M88">
-        <v>92.05997280000001</v>
+        <v>93.13043760000001</v>
       </c>
       <c r="N88">
-        <v>-39.85997280000001</v>
+        <v>-40.9304376</v>
       </c>
       <c r="O88">
-        <v>-8.769194016000002</v>
+        <v>-9.004696272</v>
       </c>
       <c r="P88">
-        <v>-31.09077878400001</v>
+        <v>-31.925741328</v>
       </c>
       <c r="Q88">
-        <v>-11.79077878400001</v>
+        <v>-12.625741328</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4361328434124034</v>
+        <v>0.4661584467518191</v>
       </c>
       <c r="T88">
-        <v>5.679818477755064</v>
+        <v>6.116727591428531</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1247447685537443</v>
+        <v>0.1233109206393335</v>
       </c>
       <c r="W88">
-        <v>0.1757512504744081</v>
+        <v>0.1760391671356218</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5670216752442925</v>
+        <v>0.5605041847242431</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8534,22 +8534,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2137546734857275</v>
+        <v>0.2153046734857275</v>
       </c>
       <c r="C89">
-        <v>-245.1638114132851</v>
+        <v>-252.3014274492133</v>
       </c>
       <c r="D89">
-        <v>207.4331885867149</v>
+        <v>205.6265725507867</v>
       </c>
       <c r="E89">
-        <v>16.49700000000001</v>
+        <v>21.82800000000003</v>
       </c>
       <c r="F89">
-        <v>463.797</v>
+        <v>469.128</v>
       </c>
       <c r="G89">
         <v>11.2</v>
@@ -8570,37 +8570,37 @@
         <v>52.2</v>
       </c>
       <c r="M89">
-        <v>93.13043760000001</v>
+        <v>94.20090240000002</v>
       </c>
       <c r="N89">
-        <v>-40.9304376</v>
+        <v>-42.00090240000002</v>
       </c>
       <c r="O89">
-        <v>-9.004696272</v>
+        <v>-9.240198528000004</v>
       </c>
       <c r="P89">
-        <v>-31.925741328</v>
+        <v>-32.76070387200001</v>
       </c>
       <c r="Q89">
-        <v>-12.625741328</v>
+        <v>-13.46070387200001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4661584467518191</v>
+        <v>0.5011883173144707</v>
       </c>
       <c r="T89">
-        <v>6.116727591428531</v>
+        <v>6.626454890714243</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1233109206393335</v>
+        <v>0.1219096601775229</v>
       </c>
       <c r="W89">
-        <v>0.1760391671356218</v>
+        <v>0.1763205402363534</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5605041847242431</v>
+        <v>0.5541348189887403</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8616,22 +8616,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2153046734857275</v>
+        <v>0.2168546734857275</v>
       </c>
       <c r="C90">
-        <v>-252.3014274492133</v>
+        <v>-259.4078461562473</v>
       </c>
       <c r="D90">
-        <v>205.6265725507867</v>
+        <v>203.8511538437527</v>
       </c>
       <c r="E90">
-        <v>21.82800000000003</v>
+        <v>27.15899999999999</v>
       </c>
       <c r="F90">
-        <v>469.128</v>
+        <v>474.459</v>
       </c>
       <c r="G90">
         <v>11.2</v>
@@ -8652,37 +8652,37 @@
         <v>52.2</v>
       </c>
       <c r="M90">
-        <v>94.20090240000002</v>
+        <v>95.2713672</v>
       </c>
       <c r="N90">
-        <v>-42.00090240000002</v>
+        <v>-43.0713672</v>
       </c>
       <c r="O90">
-        <v>-9.240198528000004</v>
+        <v>-9.475700783999999</v>
       </c>
       <c r="P90">
-        <v>-32.76070387200001</v>
+        <v>-33.595666416</v>
       </c>
       <c r="Q90">
-        <v>-13.46070387200001</v>
+        <v>-14.295666416</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5011883173144707</v>
+        <v>0.5425872552521499</v>
       </c>
       <c r="T90">
-        <v>6.626454890714243</v>
+        <v>7.228859880779174</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1219096601775229</v>
+        <v>0.1205398887148541</v>
       </c>
       <c r="W90">
-        <v>0.1763205402363534</v>
+        <v>0.1765955903460573</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5541348189887403</v>
+        <v>0.5479085850675186</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8698,22 +8698,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2168546734857275</v>
+        <v>0.2184046734857275</v>
       </c>
       <c r="C91">
-        <v>-259.4078461562473</v>
+        <v>-266.4838687078137</v>
       </c>
       <c r="D91">
-        <v>203.8511538437527</v>
+        <v>202.1061312921863</v>
       </c>
       <c r="E91">
-        <v>27.15899999999999</v>
+        <v>32.49000000000001</v>
       </c>
       <c r="F91">
-        <v>474.459</v>
+        <v>479.79</v>
       </c>
       <c r="G91">
         <v>11.2</v>
@@ -8734,37 +8734,37 @@
         <v>52.2</v>
       </c>
       <c r="M91">
-        <v>95.2713672</v>
+        <v>96.34183200000001</v>
       </c>
       <c r="N91">
-        <v>-43.0713672</v>
+        <v>-44.14183200000001</v>
       </c>
       <c r="O91">
-        <v>-9.475700783999999</v>
+        <v>-9.711203040000003</v>
       </c>
       <c r="P91">
-        <v>-33.595666416</v>
+        <v>-34.43062896000001</v>
       </c>
       <c r="Q91">
-        <v>-14.295666416</v>
+        <v>-15.13062896000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5425872552521499</v>
+        <v>0.5922659807773649</v>
       </c>
       <c r="T91">
-        <v>7.228859880779174</v>
+        <v>7.951745868857092</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1205398887148541</v>
+        <v>0.1192005566180224</v>
       </c>
       <c r="W91">
-        <v>0.1765955903460573</v>
+        <v>0.1768645282311011</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5479085850675186</v>
+        <v>0.5418207119001017</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8780,22 +8780,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2184046734857275</v>
+        <v>0.2199546734857275</v>
       </c>
       <c r="C92">
-        <v>-266.4838687078137</v>
+        <v>-273.5302690771113</v>
       </c>
       <c r="D92">
-        <v>202.1061312921863</v>
+        <v>200.3907309228888</v>
       </c>
       <c r="E92">
-        <v>32.49000000000001</v>
+        <v>37.82100000000003</v>
       </c>
       <c r="F92">
-        <v>479.79</v>
+        <v>485.121</v>
       </c>
       <c r="G92">
         <v>11.2</v>
@@ -8816,37 +8816,37 @@
         <v>52.2</v>
       </c>
       <c r="M92">
-        <v>96.34183200000001</v>
+        <v>97.41229680000001</v>
       </c>
       <c r="N92">
-        <v>-44.14183200000001</v>
+        <v>-45.2122968</v>
       </c>
       <c r="O92">
-        <v>-9.711203040000003</v>
+        <v>-9.946705296000001</v>
       </c>
       <c r="P92">
-        <v>-34.43062896000001</v>
+        <v>-35.265591504</v>
       </c>
       <c r="Q92">
-        <v>-15.13062896000001</v>
+        <v>-15.965591504</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5922659807773649</v>
+        <v>0.6529844230859612</v>
       </c>
       <c r="T92">
-        <v>7.951745868857092</v>
+        <v>8.835273187618993</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1192005566180224</v>
+        <v>0.1178906603914507</v>
       </c>
       <c r="W92">
-        <v>0.1768645282311011</v>
+        <v>0.1771275553933967</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5418207119001017</v>
+        <v>0.5358666381429578</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8862,22 +8862,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2199546734857275</v>
+        <v>0.2215046734857275</v>
       </c>
       <c r="C93">
-        <v>-273.5302690771113</v>
+        <v>-280.5477951817226</v>
       </c>
       <c r="D93">
-        <v>200.3907309228888</v>
+        <v>198.7042048182775</v>
       </c>
       <c r="E93">
-        <v>37.82100000000003</v>
+        <v>43.15200000000004</v>
       </c>
       <c r="F93">
-        <v>485.121</v>
+        <v>490.4520000000001</v>
       </c>
       <c r="G93">
         <v>11.2</v>
@@ -8898,37 +8898,37 @@
         <v>52.2</v>
       </c>
       <c r="M93">
-        <v>97.41229680000001</v>
+        <v>98.48276160000002</v>
       </c>
       <c r="N93">
-        <v>-45.2122968</v>
+        <v>-46.28276160000001</v>
       </c>
       <c r="O93">
-        <v>-9.946705296000001</v>
+        <v>-10.182207552</v>
       </c>
       <c r="P93">
-        <v>-35.265591504</v>
+        <v>-36.10055404800001</v>
       </c>
       <c r="Q93">
-        <v>-15.965591504</v>
+        <v>-16.80055404800001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6529844230859612</v>
+        <v>0.7288824759717065</v>
       </c>
       <c r="T93">
-        <v>8.835273187618993</v>
+        <v>9.939682336071371</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1178906603914507</v>
+        <v>0.1166092401698045</v>
       </c>
       <c r="W93">
-        <v>0.1771275553933967</v>
+        <v>0.1773848645739033</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5358666381429578</v>
+        <v>0.5300420007718385</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8944,22 +8944,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2215046734857275</v>
+        <v>0.2230546734857275</v>
       </c>
       <c r="C94">
-        <v>-280.5477951817226</v>
+        <v>-287.5371699709075</v>
       </c>
       <c r="D94">
-        <v>198.7042048182775</v>
+        <v>197.0458300290926</v>
       </c>
       <c r="E94">
-        <v>43.15200000000004</v>
+        <v>48.48300000000006</v>
       </c>
       <c r="F94">
-        <v>490.4520000000001</v>
+        <v>495.7830000000001</v>
       </c>
       <c r="G94">
         <v>11.2</v>
@@ -8980,37 +8980,37 @@
         <v>52.2</v>
       </c>
       <c r="M94">
-        <v>98.48276160000002</v>
+        <v>99.55322640000001</v>
       </c>
       <c r="N94">
-        <v>-46.28276160000001</v>
+        <v>-47.35322640000001</v>
       </c>
       <c r="O94">
-        <v>-10.182207552</v>
+        <v>-10.417709808</v>
       </c>
       <c r="P94">
-        <v>-36.10055404800001</v>
+        <v>-36.93551659200001</v>
       </c>
       <c r="Q94">
-        <v>-16.80055404800001</v>
+        <v>-17.63551659200001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7288824759717065</v>
+        <v>0.8264656868248075</v>
       </c>
       <c r="T94">
-        <v>9.939682336071371</v>
+        <v>11.35963695551014</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1166092401698045</v>
+        <v>0.1153553773722797</v>
       </c>
       <c r="W94">
-        <v>0.1773848645739033</v>
+        <v>0.1776366402236462</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5300420007718385</v>
+        <v>0.5243426244194532</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9026,22 +9026,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2230546734857275</v>
+        <v>0.2246046734857275</v>
       </c>
       <c r="C95">
-        <v>-287.5371699709075</v>
+        <v>-294.4990924589013</v>
       </c>
       <c r="D95">
-        <v>197.0458300290926</v>
+        <v>195.4149075410988</v>
       </c>
       <c r="E95">
-        <v>48.48300000000006</v>
+        <v>53.81400000000002</v>
       </c>
       <c r="F95">
-        <v>495.7830000000001</v>
+        <v>501.114</v>
       </c>
       <c r="G95">
         <v>11.2</v>
@@ -9062,37 +9062,37 @@
         <v>52.2</v>
       </c>
       <c r="M95">
-        <v>99.55322640000001</v>
+        <v>100.6236912</v>
       </c>
       <c r="N95">
-        <v>-47.35322640000001</v>
+        <v>-48.42369120000001</v>
       </c>
       <c r="O95">
-        <v>-10.417709808</v>
+        <v>-10.653212064</v>
       </c>
       <c r="P95">
-        <v>-36.93551659200001</v>
+        <v>-37.77047913600001</v>
       </c>
       <c r="Q95">
-        <v>-17.63551659200001</v>
+        <v>-18.47047913600001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8264656868248075</v>
+        <v>0.9565766346289422</v>
       </c>
       <c r="T95">
-        <v>11.35963695551014</v>
+        <v>13.2529097814285</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1153553773722797</v>
+        <v>0.1141281925066172</v>
       </c>
       <c r="W95">
-        <v>0.1776366402236462</v>
+        <v>0.1778830589446713</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5243426244194532</v>
+        <v>0.5187645113937144</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9108,22 +9108,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2246046734857275</v>
+        <v>0.2261546734857275</v>
       </c>
       <c r="C96">
-        <v>-294.4990924589013</v>
+        <v>-301.4342387073185</v>
       </c>
       <c r="D96">
-        <v>195.4149075410988</v>
+        <v>193.8107612926815</v>
       </c>
       <c r="E96">
-        <v>53.81400000000002</v>
+        <v>59.14500000000004</v>
       </c>
       <c r="F96">
-        <v>501.114</v>
+        <v>506.4450000000001</v>
       </c>
       <c r="G96">
         <v>11.2</v>
@@ -9144,37 +9144,37 @@
         <v>52.2</v>
       </c>
       <c r="M96">
-        <v>100.6236912</v>
+        <v>101.694156</v>
       </c>
       <c r="N96">
-        <v>-48.42369120000001</v>
+        <v>-49.494156</v>
       </c>
       <c r="O96">
-        <v>-10.653212064</v>
+        <v>-10.88871432</v>
       </c>
       <c r="P96">
-        <v>-37.77047913600001</v>
+        <v>-38.60544168000001</v>
       </c>
       <c r="Q96">
-        <v>-18.47047913600001</v>
+        <v>-19.30544168</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9565766346289422</v>
+        <v>1.138731961554731</v>
       </c>
       <c r="T96">
-        <v>13.2529097814285</v>
+        <v>15.90349173771421</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1141281925066172</v>
+        <v>0.1129268431118107</v>
       </c>
       <c r="W96">
-        <v>0.1778830589446713</v>
+        <v>0.1781242899031484</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5187645113937144</v>
+        <v>0.5133038323264121</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9190,22 +9190,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2261546734857275</v>
+        <v>0.2277046734857275</v>
       </c>
       <c r="C97">
-        <v>-301.4342387073185</v>
+        <v>-308.3432627595643</v>
       </c>
       <c r="D97">
-        <v>193.8107612926815</v>
+        <v>192.2327372404358</v>
       </c>
       <c r="E97">
-        <v>59.14500000000004</v>
+        <v>64.47600000000006</v>
       </c>
       <c r="F97">
-        <v>506.4450000000001</v>
+        <v>511.7760000000001</v>
       </c>
       <c r="G97">
         <v>11.2</v>
@@ -9226,37 +9226,37 @@
         <v>52.2</v>
       </c>
       <c r="M97">
-        <v>101.694156</v>
+        <v>102.7646208</v>
       </c>
       <c r="N97">
-        <v>-49.494156</v>
+        <v>-50.56462080000001</v>
       </c>
       <c r="O97">
-        <v>-10.88871432</v>
+        <v>-11.124216576</v>
       </c>
       <c r="P97">
-        <v>-38.60544168000001</v>
+        <v>-39.44040422400001</v>
       </c>
       <c r="Q97">
-        <v>-19.30544168</v>
+        <v>-20.14040422400001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.138731961554731</v>
+        <v>1.411964951943415</v>
       </c>
       <c r="T97">
-        <v>15.90349173771421</v>
+        <v>19.87936467214277</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1129268431118107</v>
+        <v>0.111750521829396</v>
       </c>
       <c r="W97">
-        <v>0.1781242899031484</v>
+        <v>0.1783604952166573</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5133038323264121</v>
+        <v>0.5079569174063453</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9272,22 +9272,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2277046734857275</v>
+        <v>0.2292546734857275</v>
       </c>
       <c r="C98">
-        <v>-308.3432627595642</v>
+        <v>-315.2267975299653</v>
       </c>
       <c r="D98">
-        <v>192.2327372404358</v>
+        <v>190.6802024700347</v>
       </c>
       <c r="E98">
-        <v>64.476</v>
+        <v>69.80699999999996</v>
       </c>
       <c r="F98">
-        <v>511.776</v>
+        <v>517.107</v>
       </c>
       <c r="G98">
         <v>11.2</v>
@@ -9308,37 +9308,37 @@
         <v>52.2</v>
       </c>
       <c r="M98">
-        <v>102.7646208</v>
+        <v>103.8350856</v>
       </c>
       <c r="N98">
-        <v>-50.5646208</v>
+        <v>-51.6350856</v>
       </c>
       <c r="O98">
-        <v>-11.124216576</v>
+        <v>-11.359718832</v>
       </c>
       <c r="P98">
-        <v>-39.440404224</v>
+        <v>-40.275366768</v>
       </c>
       <c r="Q98">
-        <v>-20.140404224</v>
+        <v>-20.975366768</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.411964951943411</v>
+        <v>1.867353269257882</v>
       </c>
       <c r="T98">
-        <v>19.87936467214271</v>
+        <v>26.50581956285695</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.111750521829396</v>
+        <v>0.1105984545940414</v>
       </c>
       <c r="W98">
-        <v>0.1783604952166573</v>
+        <v>0.1785918303175165</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5079569174063454</v>
+        <v>0.5027202481547336</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9354,22 +9354,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2292546734857275</v>
+        <v>0.2660794232671725</v>
       </c>
       <c r="C99">
-        <v>-315.2267975299653</v>
+        <v>-351.2548297679252</v>
       </c>
       <c r="D99">
-        <v>190.6802024700347</v>
+        <v>159.9831702320747</v>
       </c>
       <c r="E99">
-        <v>69.80699999999996</v>
+        <v>75.13799999999998</v>
       </c>
       <c r="F99">
-        <v>517.107</v>
+        <v>522.438</v>
       </c>
       <c r="G99">
         <v>11.2</v>
@@ -9390,45 +9390,45 @@
         <v>52.2</v>
       </c>
       <c r="M99">
-        <v>103.8350856</v>
+        <v>123.1908804</v>
       </c>
       <c r="N99">
-        <v>-51.6350856</v>
+        <v>-70.99088039999999</v>
       </c>
       <c r="O99">
-        <v>-11.359718832</v>
+        <v>-15.617993688</v>
       </c>
       <c r="P99">
-        <v>-40.275366768</v>
+        <v>-55.372886712</v>
       </c>
       <c r="Q99">
-        <v>-20.975366768</v>
+        <v>-36.072886712</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.867353269257882</v>
+        <v>2.826867392959071</v>
       </c>
       <c r="T99">
-        <v>26.50581956285695</v>
+        <v>40.46791919511094</v>
       </c>
       <c r="U99">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1105984545940414</v>
+        <v>0.0932211862007279</v>
       </c>
       <c r="W99">
-        <v>0.1785918303175165</v>
+        <v>0.2138184442938684</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.5027202481547336</v>
+        <v>0.4237326645487631</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9436,22 +9436,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2660794232671725</v>
+        <v>0.2679794232671724</v>
       </c>
       <c r="C100">
-        <v>-351.2548297679252</v>
+        <v>-357.903741806407</v>
       </c>
       <c r="D100">
-        <v>159.9831702320747</v>
+        <v>158.665258193593</v>
       </c>
       <c r="E100">
-        <v>75.13799999999998</v>
+        <v>80.46899999999999</v>
       </c>
       <c r="F100">
-        <v>522.438</v>
+        <v>527.769</v>
       </c>
       <c r="G100">
         <v>11.2</v>
@@ -9472,37 +9472,37 @@
         <v>52.2</v>
       </c>
       <c r="M100">
-        <v>123.1908804</v>
+        <v>124.4479302</v>
       </c>
       <c r="N100">
-        <v>-70.99088039999999</v>
+        <v>-72.2479302</v>
       </c>
       <c r="O100">
-        <v>-15.617993688</v>
+        <v>-15.894544644</v>
       </c>
       <c r="P100">
-        <v>-55.372886712</v>
+        <v>-56.353385556</v>
       </c>
       <c r="Q100">
-        <v>-36.072886712</v>
+        <v>-37.05338555599999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.826867392959071</v>
+        <v>5.607934785918141</v>
       </c>
       <c r="T100">
-        <v>40.46791919511094</v>
+        <v>80.93583839022189</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0932211862007279</v>
+        <v>0.09227955805728619</v>
       </c>
       <c r="W100">
-        <v>0.2138184442938684</v>
+        <v>0.2140404802100919</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9510,91 +9510,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4237326645487631</v>
+        <v>0.4194525366240281</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2679794232671724</v>
-      </c>
-      <c r="C101">
-        <v>-357.903741806407</v>
-      </c>
-      <c r="D101">
-        <v>158.665258193593</v>
-      </c>
-      <c r="E101">
-        <v>80.46899999999999</v>
-      </c>
-      <c r="F101">
-        <v>527.769</v>
-      </c>
-      <c r="G101">
-        <v>11.2</v>
-      </c>
-      <c r="H101">
-        <v>85.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>71.5</v>
-      </c>
-      <c r="K101">
-        <v>19.3</v>
-      </c>
-      <c r="L101">
-        <v>52.2</v>
-      </c>
-      <c r="M101">
-        <v>124.4479302</v>
-      </c>
-      <c r="N101">
-        <v>-72.2479302</v>
-      </c>
-      <c r="O101">
-        <v>-15.894544644</v>
-      </c>
-      <c r="P101">
-        <v>-56.353385556</v>
-      </c>
-      <c r="Q101">
-        <v>-37.05338555599999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.607934785918141</v>
-      </c>
-      <c r="T101">
-        <v>80.93583839022189</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09227955805728619</v>
-      </c>
-      <c r="W101">
-        <v>0.2140404802100919</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4194525366240281</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
